--- a/database.xlsx
+++ b/database.xlsx
@@ -15,7 +15,6 @@
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="152511"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,86 +24,20 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="314">
-  <si>
-    <t>Глобализация — усиление взаимосвязи экономик и рынков</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> — метод сложения коэффициентов (P=ΣP×Wk), полезный только для оценки крайних значений (самых развитых или самых бедных стран).</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="388">
   <si>
     <t xml:space="preserve">Алгоритм Беннетта </t>
   </si>
   <si>
-    <t xml:space="preserve"> — метод умножения коэффициентов (P=1000×ΠPkWk), более точный для малых экономик, где единичные инновации существенно влияют на эффективность.</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Алгоритм Квинта</t>
   </si>
   <si>
-    <t xml:space="preserve"> — нестандартные решения для преимущества</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> — состояние системы</t>
-  </si>
-  <si>
-    <t>— крупнейшие аудиторские фирмы мира: PricewaterhouseCoopers (PwC), Deloitte Touche, Ernst &amp; Young (EY) и KPMG.</t>
-  </si>
-  <si>
-    <t>— представление о будущем состоянии объекта</t>
-  </si>
-  <si>
-    <t>— валовой национальный доход на человека, основа классификации Группы Всемирного банка для кредитных решений</t>
-  </si>
-  <si>
-    <t>— усиление взаимосвязи экономик и рынков</t>
-  </si>
-  <si>
-    <t>— совокупность мировых рынков</t>
-  </si>
-  <si>
-    <t>— время даёт преимущество</t>
-  </si>
-  <si>
-    <t>— реализуются только обеспеченные направления</t>
-  </si>
-  <si>
-    <t>— первый и главный закон стратегии по Квинту; фактор времени является детерминирующим в стратегии</t>
-  </si>
-  <si>
-    <t>— глобальные, национальные, региональные, корпоративные, индивидуальные</t>
-  </si>
-  <si>
-    <t>— один из пяти показателей синтезированного странового рейтинга Квинта (относительная значимость 1,0)</t>
-  </si>
-  <si>
-    <t>— один из пяти показателей синтезированного рейтинга (относительная значимость 0,7)</t>
-  </si>
-  <si>
-    <t>— объединение всех уровней</t>
-  </si>
-  <si>
-    <t>— ориентация на прошлое</t>
-  </si>
-  <si>
-    <t>— группы, составляющие классификационную систему; внутри категорий также применяется рейтинговая система</t>
-  </si>
-  <si>
-    <t>— доминирующая в России конца 2010-х модель, существенно отличающаяся как от государственного капитализма, так и от коммунизма</t>
-  </si>
-  <si>
-    <t>— одна из трёх дополнительных категорий ООН, отражающая географическую специфику развития.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Асимметрия </t>
   </si>
   <si>
     <t xml:space="preserve">Баланс </t>
   </si>
   <si>
-    <t xml:space="preserve"> — страны, квалифицированные по инициативе МВФ и Всемирного банка как неспособные выплатить свой долг.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Беднейшие страны с большой задолженностью (БСБЗ, HIPC) </t>
   </si>
   <si>
@@ -117,15 +50,9 @@
     <t xml:space="preserve">ВНД на душу населения </t>
   </si>
   <si>
-    <t>— подсистема глобального миропорядка, каркас относительно стабильного сотрудничества бизнеса с глобальными, региональными и национальными институтами. Cтимулирует преимущественно эволюционное развитие глобального рыночного пространства.</t>
-  </si>
-  <si>
     <t>Глобальный экономический миропорядок (ГЭМ)</t>
   </si>
   <si>
-    <t xml:space="preserve"> — повторяющиеся связи развития.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Глобальное рыночное пространство </t>
   </si>
   <si>
@@ -147,9 +74,6 @@
     <t>Индикаторы</t>
   </si>
   <si>
-    <t xml:space="preserve"> — основа рейтинговых систем и индексов, на которых строятся классификационные системы стран и регионов</t>
-  </si>
-  <si>
     <t xml:space="preserve">Индекс экономики знаний </t>
   </si>
   <si>
@@ -159,24 +83,12 @@
     <t>Индекс современности промышленности</t>
   </si>
   <si>
-    <t xml:space="preserve"> — показатель, разработанный Квинтом на основе базы данных ЮНИДО для синтезированного рейтинга стран</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> — источник преимуществ</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Инновации </t>
-  </si>
-  <si>
     <t xml:space="preserve">Интеграция стратегий </t>
   </si>
   <si>
     <t>Инфраструктура международного бизнеса</t>
   </si>
   <si>
-    <t xml:space="preserve"> — присутствие в стране международных банков, страховых компаний, аудиторов и юридических фирм, необходимое для входа на иностранный рынок</t>
-  </si>
-  <si>
     <t xml:space="preserve">Инерционное мышление </t>
   </si>
   <si>
@@ -186,246 +98,111 @@
     <t>Конкурентные преимущества</t>
   </si>
   <si>
-    <t xml:space="preserve"> — факторы превосходства</t>
-  </si>
-  <si>
     <t xml:space="preserve">Контролируемая государством экономика </t>
   </si>
   <si>
     <t xml:space="preserve">Малые островные развивающиеся государства </t>
   </si>
   <si>
-    <t xml:space="preserve"> — псевдопредвидение в виде пророчеств, прорицаний, «откровений» и гаданий</t>
-  </si>
-  <si>
     <t xml:space="preserve">Мантическое предвидение </t>
   </si>
   <si>
-    <t xml:space="preserve"> — фундаментальная цель и смысл существования объекта</t>
-  </si>
-  <si>
     <t xml:space="preserve">Миссия </t>
   </si>
   <si>
     <t>Морфология страны</t>
   </si>
   <si>
-    <t xml:space="preserve"> — система характеристик и внутренняя структура государства: политические, экономические, финансовые, технологические индикаторы, культурная и религиозная среда</t>
-  </si>
-  <si>
     <t>Нави</t>
   </si>
   <si>
-    <t xml:space="preserve"> — слово из Торы, ассоциирующееся с мощным и точным видением таких великих лидеров, как Моисей и Самуил</t>
-  </si>
-  <si>
     <t>Навиим</t>
   </si>
   <si>
-    <t xml:space="preserve"> — слово из Торы, отображающее пророка-провидца без лидерских качеств.</t>
-  </si>
-  <si>
     <t>Наименее развитые страны (НРС, LDC)</t>
   </si>
   <si>
-    <t xml:space="preserve"> — категория ООН с 1971 года. Критерии: низкий доход (ВНД на душу населения), слабый человеческий капитал и экономическая уязвимость.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> — быстро формирующаяся технология, которая может стать основой беспрецедентно больших систем стратегических компетенций.</t>
-  </si>
-  <si>
     <t>Нанотехнологии</t>
   </si>
   <si>
     <t xml:space="preserve">Научное предвидение </t>
   </si>
   <si>
-    <t>— информационно-познавательный аспект опережающего отражения как свойства высших форм материи.</t>
-  </si>
-  <si>
     <t>Недавно индустриализованные азиатские экономики</t>
   </si>
   <si>
-    <t xml:space="preserve"> — категория МВФ: Гонконг, Корея, Сингапур и Тайвань.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ненаучное предвидение </t>
   </si>
   <si>
-    <t>— интуитивное (связанное с подсознанием), обыденное (по народным приметам) и мантическое (пророчества, гадания) предвидение.</t>
-  </si>
-  <si>
-    <t>— категория, появившаяся благодаря европейским открытиям; несистематизированные территории, ставшие затем странами и регионами.</t>
-  </si>
-  <si>
     <t>Новый Свет</t>
   </si>
   <si>
     <t xml:space="preserve">Объективная вероятность </t>
   </si>
   <si>
-    <t>— сценарии будущего, в которых сталкиваются или кооперируют ценностные ориентиры, интересы и приоритеты субъектов стратегирования.</t>
-  </si>
-  <si>
     <t>Ожидаемые воспоминания</t>
   </si>
   <si>
-    <t xml:space="preserve"> — концепция Даниэля Канемана: «Мы думаем о нашем будущем как об ожидаемых воспоминаниях».</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ойкумена </t>
   </si>
   <si>
-    <t>— термин древних греков для описания известного им мира с центром в Элладе; одна из первых попыток системного понимания мира</t>
-  </si>
-  <si>
     <t>OTSW-анализ</t>
   </si>
   <si>
-    <t xml:space="preserve"> — метод, используемый в рамках методологии стратегирования научной школы Квинта. Расшифровывается как Opportunities (Возможности), Threats (Угрозы), Strengths (Сильные стороны) и Weaknesses (Слабые стороны).</t>
-  </si>
-  <si>
     <t>Планирование</t>
   </si>
   <si>
-    <t xml:space="preserve"> — разработка действий.</t>
-  </si>
-  <si>
     <t>Политика</t>
   </si>
   <si>
-    <t xml:space="preserve"> — интеграция стратегии и тактики</t>
-  </si>
-  <si>
     <t>Политический риск инвестиций</t>
   </si>
   <si>
-    <t xml:space="preserve"> — риск экспроприации, национализации и повреждения частной собственности иностранных лиц в странах с гражданскими волнениями.</t>
-  </si>
-  <si>
-    <t>— способность понимать будущее.</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Предвидение </t>
   </si>
   <si>
     <t xml:space="preserve">Предсказание </t>
   </si>
   <si>
-    <t>— результат понимания будущего.</t>
-  </si>
-  <si>
     <t>Предугадывание</t>
   </si>
   <si>
-    <t xml:space="preserve"> — сложное предвосхищение, вид интеллектуальной деятельности человека на основе личного опыта</t>
-  </si>
-  <si>
     <t xml:space="preserve">Предчувствие </t>
   </si>
   <si>
-    <t>— простое предвосхищение, свойственное любому организму; одна из форм конкретизации предвидения.</t>
-  </si>
-  <si>
     <t>Приоритеты</t>
   </si>
   <si>
-    <t xml:space="preserve"> — ключевые направления развития</t>
-  </si>
-  <si>
     <t xml:space="preserve">Продвинутые экономики </t>
   </si>
   <si>
-    <t>— категория МВФ с 1997 года, объединяющая развитые страны и самые зрелые СФР (Южная Корея, Сингапур, Израиль)</t>
-  </si>
-  <si>
     <t>Прогнозирование</t>
   </si>
   <si>
-    <t xml:space="preserve"> — научное определение будущего.</t>
-  </si>
-  <si>
     <t>Промышленные страны</t>
   </si>
   <si>
-    <t xml:space="preserve"> — устаревшая категория МВФ, заменённая на «продвинутые экономики» из-за сокращения занятости в индустриальном производстве.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> — интуитивное предвидение.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Пророчество </t>
   </si>
   <si>
-    <t>Провидцы.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> — люди, «видевшие» картины будущего. Их главная ценность для стратегов — традиция связывать пророчества со шкалой времени</t>
-  </si>
-  <si>
     <t>Пророк-лидер</t>
   </si>
   <si>
-    <t xml:space="preserve"> — редчайшее сочетание способностей провидца с лидерскими качествами практика (Моисей, Мухаммед)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Прямые иностранные инвестиции (ПИИ) </t>
   </si>
   <si>
-    <t>— инвестиции компаний в зарубежные экономики. Новый тренд: ПИИ из СФР направляются в наукоёмкие отрасли развитых стран.</t>
-  </si>
-  <si>
     <t>Проспективные векторные решения</t>
   </si>
   <si>
-    <t xml:space="preserve"> — решения, ведущие к далёкому будущему, всегда принимаемые на грани сознания и подсознания, рационального и иррационального.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ранги </t>
   </si>
   <si>
-    <t>— позиции, присваиваемые странам и регионам в рейтингах, индексах и внутри классификационных категорий.</t>
-  </si>
-  <si>
     <t>Расцветающие экономики (экономики в фазе расцвета)</t>
   </si>
   <si>
-    <t xml:space="preserve"> — высшая стадия СФР (Южная Корея, Сингапур, Израиль, Гонконг, Испания, Португалия, Греция). Стратегически конкурируют с развитыми странами.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> — средства для реализации стратегии.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ресурсы </t>
   </si>
   <si>
-    <t xml:space="preserve"> — вероятность потерь</t>
-  </si>
-  <si>
-    <t>— рейтинг технологического, экономического и социального развития стран на основе пяти индикаторов.</t>
-  </si>
-  <si>
-    <t>— мудрый дисциплинированный и оптимистичный профессионал, имеющий стратегическое мышление, видение будущего и интуицию, подкрепленную методологией стратегирования.</t>
-  </si>
-  <si>
-    <t>— мудрые дисциплинированные и оптимистичные профессионалы, имеющие стратегическое мышление, видение будущего и интуицию, подкрепленную методологией стратегирования.</t>
-  </si>
-  <si>
-    <t>— способность принимать долгосрочные решения.</t>
-  </si>
-  <si>
-    <t>— контроль и корректировка стратегии.</t>
-  </si>
-  <si>
-    <t>— система поиска, формулирования и развития доктрины, обеспечивающей долгосрочный успех</t>
-  </si>
-  <si>
-    <t>— концепция профессора Прахалада о заработке на беднейших слоях за счёт продажи малых упаковок товаров при высоком обороте.</t>
-  </si>
-  <si>
-    <t>— процесс разработки, реализации и обновления стратегии.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Риск </t>
   </si>
   <si>
@@ -435,9 +212,6 @@
     <t>Старый Свет</t>
   </si>
   <si>
-    <t xml:space="preserve"> — классификационная категория, ядром которой стала цивилизация ойкумены к концу XV века.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Стратег </t>
   </si>
   <si>
@@ -447,27 +221,18 @@
     <t>Стратегическая доктрина</t>
   </si>
   <si>
-    <t xml:space="preserve"> — система официальных взглядов и положений, устанавливающая направления долгосрочного развития объекта стратегирования.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Стратегическое мышление </t>
   </si>
   <si>
     <t>Стратегическое управление</t>
   </si>
   <si>
-    <t xml:space="preserve"> — процесс формирования и функционирования системы стратегического управления, обеспечивающей разработку и долгосрочную реализацию стратегии, её доктрины, в соответствии с содержащимися в них конкурентными преимуществами, приоритетами, целями и задачами.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Стратегический мониторинг </t>
   </si>
   <si>
     <t>Стратегический сценарий</t>
   </si>
   <si>
-    <t xml:space="preserve"> — один из альтернативных вариантов реализации стратегии. Как правило, разрабатывается не менее трёх сценариев, которые отличаются соотношением риска, асимметричности и общественно-экономической эффективности.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Стратегия </t>
   </si>
   <si>
@@ -477,234 +242,117 @@
     <t xml:space="preserve">Стратегирование </t>
   </si>
   <si>
-    <t>— одна из трёх дополнительных категорий ООН, отражающая географические ограничения развития.</t>
-  </si>
-  <si>
     <t>Страны без выхода к морю</t>
   </si>
   <si>
     <t xml:space="preserve">Страны с переходной экономикой </t>
   </si>
   <si>
-    <t>— категория восточноевропейских стран и СНГ. Квинт критикует её: логически все СФР и развивающиеся страны находятся в переходной стадии</t>
-  </si>
-  <si>
     <t xml:space="preserve">Страны, приступившие к формированию рынка (СПФР, frontier economies) </t>
   </si>
   <si>
-    <t>— переходная стадия от развивающихся к СФР (Тунис, Монголия, Мадагаскар, Буркина Фасо).</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> — сценарии, в которых сталкиваются или кооперируют ценностные ориентиры, интересы и приоритеты субъектов стратегирования.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Субъективная вероятность </t>
   </si>
   <si>
     <t xml:space="preserve">Тактика </t>
   </si>
   <si>
-    <t>— система текущих действий для реализации стратегии.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Таксономия </t>
   </si>
   <si>
-    <t>— теория систематизации и иерархических сфер действительности и знаний, созданная Карлом Линнеем в 1813 году.</t>
-  </si>
-  <si>
-    <t>— теория Канемана и Тверски о принятии решений в условиях высоких рисков, исключительно важная для стратегирования.</t>
-  </si>
-  <si>
     <t>Теория проспектного мышления</t>
   </si>
   <si>
     <t xml:space="preserve">Третий мир </t>
   </si>
   <si>
-    <t>— термин, ассоциировавшийся с бедными неразвитыми странами. Большинство из них отклонили принципы свободного конкурентного рынка и стали беднее.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Тренды </t>
   </si>
   <si>
-    <t>— устойчивые направления развития.</t>
-  </si>
-  <si>
-    <t>— негативные факторы.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Угрозы </t>
   </si>
   <si>
     <t>Фактор времени</t>
   </si>
   <si>
-    <t xml:space="preserve"> — ключ к стратегическому преимуществу.</t>
-  </si>
-  <si>
     <t>Фиктивная естественная убыль населения</t>
   </si>
   <si>
-    <t xml:space="preserve"> — главная стратегическая угроза для России и ещё более 20 стран в XXI веке; депопуляция, игнорируемая в большинстве стратегических документов.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Хаос будущего </t>
   </si>
   <si>
-    <t>— неопределённость среды.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Цели </t>
   </si>
   <si>
-    <t>— конкретные ориентиры, размещённые во времени.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Экологическая устойчивость </t>
   </si>
   <si>
-    <t>— показатель стратегического уровня развития. Северные страны обеспечивают наиболее устойчивую окружающую среду; страны с диктатурами замыкают рейтинг.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Экологическая цивилизация </t>
   </si>
   <si>
-    <t>— стратегия Китая «Пять в одном»: посадка деревьев на четверти территории, восстановление 30% береговой линии, сокращение потребления угля на 40%.</t>
-  </si>
-  <si>
     <t>15 правил стратегирования В.Л. Квинта</t>
   </si>
   <si>
-    <t>- Первый библейский патриарх и пророк. Отнесён к проактивным лидерам, чьё стратегическое предвидение направляло не только семью, но и целые поколения. Пример провидца, который действует, а не только созерцает.</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Авраам</t>
   </si>
   <si>
     <t>Аарон</t>
   </si>
   <si>
-    <t xml:space="preserve"> Период: XIII век до н. э. Старший брат Моисея и Первый первосвященник. Квинт проводит границу: Аарон —  Моисей — пророк и стратег. Духовный сан и стратегическое лидерство — разные.</t>
-  </si>
-  <si>
     <t>Александр Невский</t>
   </si>
   <si>
-    <t>Внёс вклад в развитие государственной и военной стратегии Руси. Прославился грамотным использованием местности, дипломатией и способностью принимать стратегические решения в сложных условиях. Его победы и политика помогли сохранить независимость русских земель.</t>
-  </si>
-  <si>
     <t>Александр Суворов</t>
   </si>
   <si>
-    <t>Один из величайших русских полководцев. Внёс вклад в развитие военной стратегии благодаря мобильности армии, быстроте принятия решений и нестандартным действиям. Его принципы подготовки войск и дисциплины стали важной частью военного стратегирования.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Амос Тверски </t>
   </si>
   <si>
-    <t>1937–1996.Психолог, соавтор Канемана. Их исследования ошибочных суждений и восприятия риска в условиях неопределённости Квинт считает критически важными для теории стратегирования.</t>
-  </si>
-  <si>
     <t>Амир Темур (Тамерлан)</t>
   </si>
   <si>
-    <t>стратег и основатель Империи Тимуридов. Владимир Квинт посвятил его лидерству отдельную книгу. Главный принцип: успех государства зависит от привлечения талантливых людей («предприимчивых, мужественных и благоразумных»), ценность которых превышает ценность тысяч безвольных работников</t>
-  </si>
-  <si>
     <t xml:space="preserve">Артур Уэлсли (Веллингтон) </t>
   </si>
   <si>
-    <t>Герцог Веллингтон. Внёс вклад в развитие военной стратегии благодаря успешному противостоянию армии Наполеона. Уделял внимание дисциплине, подготовке армии и грамотному использованию местности.</t>
-  </si>
-  <si>
     <t>Барри Гиллс</t>
   </si>
   <si>
-    <t>Современный исследователь (XX–XXI вв.).Специалист по политэкономии Восточной Азии. Квинт цитирует его работы о связи авторитарной олигархии и экономической структуры стран ЮВА.</t>
-  </si>
-  <si>
     <t>Билл Гейтс</t>
   </si>
   <si>
-    <t xml:space="preserve"> Ключевой стратег цифровой эпохи. Развивал программное обеспечение и сделал ставку на массовое распространение персональных компьютеров. Его решения сыграли большую роль в развитии мировой IT-индустрии</t>
-  </si>
-  <si>
-    <t>Создатель Общей теории стратегии и теории глобального формирующегося рынка. Под его руководством разработаны стратегии развития Санкт-Петербурга и Кузбасса до 2035 года. Иностранный член РАН, лауреат Госпремии Узбекистана. В апреле 2026 года получил звание почетного профессора Шанхайского университета.</t>
-  </si>
-  <si>
     <t>Владимир Квинт</t>
   </si>
   <si>
     <t>Георгий Жуков</t>
   </si>
   <si>
-    <t>Один из крупнейших полководцев XX века. Внёс вклад в развитие стратегического управления армией во время Второй мировой войны. Его решения в крупнейших операциях повлияли на советскую и мировую военную стратегию</t>
-  </si>
-  <si>
-    <t>Один из великих библейских пророков. Его видения охватывали века. Квинт подчёркивает уникальную глубину его предсказаний, недоступную даже современному планированию. Эталон предвидения.</t>
-  </si>
-  <si>
     <t>Даниил</t>
   </si>
   <si>
     <t>Дарел Тай Енген</t>
   </si>
   <si>
-    <t>Современный американский историк экономики (XX–XXI вв.).Исследовал античные модели: свободное предпринимательство в Древней Греции и дворцовая монополия в Египте как два изначальных стратегических пути экономики.</t>
-  </si>
-  <si>
     <t>Джек Ма</t>
   </si>
   <si>
-    <t>Внёс вклад в развитие цифровой стратегии и интернет-торговли. Создал платформу Alibaba, сделав ставку на развитие онлайн-бизнеса и глобальной электронной коммерции.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Джек Уэлч </t>
   </si>
   <si>
-    <t>Внёс вклад в развитие корпоративной стратегии. Руководя General Electric, внедрял инновации, оптимизацию процессов и долгосрочное планирование. Пример эффективного стратегического менеджмента.</t>
-  </si>
-  <si>
-    <t>Внёс вклад в развитие современной стратегической теории. Разработал концепцию OODA Loop (быстрый анализ ситуации и принятие решений). Идеи используются в военной стратегии, бизнесе и управлении.</t>
-  </si>
-  <si>
     <t>Джон Бойд</t>
   </si>
   <si>
     <t>Джон Майкл Монтиас</t>
   </si>
   <si>
-    <t>1928–2005. Историк экономики, коллега Купманса. Предложил подход к сравнению экономических систем по организационным функциям, который Квинт рассматривает как важный шаг, но с ограничениями.</t>
-  </si>
-  <si>
     <t>Джонатан Свифт</t>
   </si>
   <si>
-    <t>1667–1745.Англо-ирландский писатель. Квинт отмечает его предвидение: за полтора века до открытия Свифт описал два спутника Марса и их орбитальные параметры, почти совпавшие с реальностью.</t>
-  </si>
-  <si>
     <t>Дэн Сяопин</t>
   </si>
   <si>
-    <t>Внёс огромный вклад в развитие экономической стратегии Китая. Провёл реформы, открывшие страну для мирового рынка. Благодаря этому Китай начал быстрое экономическое развитие</t>
-  </si>
-  <si>
-    <t>1927–2015. Советский и российский учёный, социолог и футуролог. Представитель отечественной школы, начавшей осмысливать процессы научного и ненаучного познания будущего</t>
-  </si>
-  <si>
     <t>Игорь Бестужев-Лада</t>
   </si>
   <si>
-    <t>ок. XIII–XII века до н. э. Преемник Моисея, завоеватель Ханаана. Квинт описывает его как образец военного стратега и полководца, а не пророка.</t>
-  </si>
-  <si>
-    <t>Известен долгосрочным стратегическим видением и инновационным подходом. Развивает проекты в области космоса, электромобилей и ИИ. Стратегии основаны на высоких рисках и стремлении изменить будущее</t>
-  </si>
-  <si>
-    <t>ок. XIII–XII века до н. э. (мифология).Троянская царевна с даром точного предвидения, но обречённая на то, что ей никто не верил. Символ трагедии провидца, лишённого стратегического влияния.</t>
-  </si>
-  <si>
     <t>Иисус Навин</t>
   </si>
   <si>
@@ -714,31 +362,16 @@
     <t>Император Маврикий</t>
   </si>
   <si>
-    <t xml:space="preserve"> Внёс значительный вклад в развитие византийской военной стратегии. Систематизировал знания о ведении войны и организации армии. Его труды стали основой для многих военных трактатов Средневековья.</t>
-  </si>
-  <si>
     <t>Кассандра</t>
   </si>
   <si>
     <t xml:space="preserve">Карл фон Клаузевиц </t>
   </si>
   <si>
-    <t>Один из главных теоретиков стратегии. В работе «О войне» рассматривал войну как продолжение политики. Его идеи оказали огромное влияние на современную военную и государственную стратегию</t>
-  </si>
-  <si>
-    <t>Ведущий специалист в области бизнес-стратегии. Изучал глобализацию и конкурентные преимущества. Его идеи повлияли на современное корпоративное стратегирование</t>
-  </si>
-  <si>
     <t>Кеничи Омае</t>
   </si>
   <si>
     <t>Конрад Аденауэр</t>
-  </si>
-  <si>
-    <t>Сыграл важную роль в восстановлении Германии после Второй мировой войны. Использовал долгосрочное стратегическое планирование для укрепления экономики и международных отношений</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Внёс вклад в развитие экономической и транспортной стратегии. Создал крупную транспортную империю, используя долгосрочное планирование и контроль инфраструктуры</t>
   </si>
   <si>
     <r>
@@ -757,39 +390,9 @@
     </r>
   </si>
   <si>
-    <t>Развивал стратегические и тактические принципы Византии. Уделял внимание анализу военных действий и изучению опыта прошлых войн. Сохранил византийскую школу стратегирования</t>
-  </si>
-  <si>
-    <t>1927–1997.Американский писатель, автор романа «Киборг». Предвосхитил появление бионических протезов, управляемых силой мысли</t>
-  </si>
-  <si>
-    <t>Американский экономист, профессор Стэнфорда. Автор методики рейтингования стран середины XX века. Квинт критикует его алгоритм сложения показателей за неточность.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Японский стратег и мастер боевых искусств. Разработал подход, основанный на дисциплине, психологическом превосходстве и анализе противника. Автор «Книги пяти колец».</t>
-  </si>
-  <si>
-    <t>ок. 570–632. Основатель ислама и глава первого мусульманского государства. Редчайшая фигура, сочетавшая посланническую миссию и практическое стратегическое руководство</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> X век до н. э.Пророк при дворе царя Давида. Предвидел воцарение Соломона и строительство Храма. Пример стратегического совета провидца, определявшего государственные решения</t>
-  </si>
-  <si>
-    <t>1503–1566.Французский врач и астролог. Квинт восхищается точностью ряда предсказаний, но делает вывод: Нострадамус — предсказатель, а не пророк.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Мастер дипломатической стратегии. Объединил Германию благодаря продуманной политике, союзам и использованию международной обстановки. Пример долгосрочного государственного планирования.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Внёс большой вклад в развитие государственной и военной стратегии России. Провёл масштабные реформы армии, флота и управления. Укрепил международное положение России</t>
-  </si>
-  <si>
     <t>Лев VI Мудрый</t>
   </si>
   <si>
-    <t>правил 161–180. Римский император, философ-стоик. Уникальный пример сочетания императора, мудреца и стратега-провидца, не допускавшего ошибок от конфликта этих ролей.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Марк Аврелий </t>
   </si>
   <si>
@@ -805,9 +408,6 @@
     <t xml:space="preserve">Моисей </t>
   </si>
   <si>
-    <t>приблизительно XIII век до н. э.Библейский пророк и вождь. Квинт считает его величайшим провидцем-стратегом, сочетавшим дар предвидения и практическое лидерство, ведя народ сквозь хаос пустыни</t>
-  </si>
-  <si>
     <t>Мухаммед (Магомет)</t>
   </si>
   <si>
@@ -817,30 +417,12 @@
     <t xml:space="preserve">Наполеон Бонапарт </t>
   </si>
   <si>
-    <t>1769–1821.Император Франции и великий полководец. Активно использовал скорость, концентрацию сил и мобильность. Квинт анализирует поход 1812 года как трагедию выбора пути гибели без чёткого плана</t>
-  </si>
-  <si>
     <t xml:space="preserve">Нострадамус (Мишель де Нострдам) </t>
   </si>
   <si>
     <t xml:space="preserve">Олдос Хаксли </t>
   </si>
   <si>
-    <t>1894–1963. Английский писатель, автор «О дивный новый мир». Предсказал генную инженерию и вмешательство в репродукцию задолго до появления технологий</t>
-  </si>
-  <si>
-    <t>Уделял внимание реформированию армии и укреплению дисциплины. Стремился повысить эффективность вооружённых сил, что повлияло на дальнейшее развитие военной стратегии России.</t>
-  </si>
-  <si>
-    <t>XI век до н. э.Последний судья и первый крупный пророк Израиля. Путь от провидца до государственного стратега, руководившего военными действиями и помазанием царей.</t>
-  </si>
-  <si>
-    <t>Внёс вклад в развитие инновационной и технологической стратегии. Ставка на качество, дизайн и создание новых рынков. Превратил Apple в крупнейшую технологическую компанию.</t>
-  </si>
-  <si>
-    <t>Завоеватель Константинополя. Использовал новые технологии, артиллерию и стратегическое планирование. Повлиял на развитие османской стратегии.</t>
-  </si>
-  <si>
     <t>Отто фон Бисмарк</t>
   </si>
   <si>
@@ -853,54 +435,18 @@
     <t xml:space="preserve">Роберт Ауман </t>
   </si>
   <si>
-    <t>родился в 1930 году. Израильский математик, нобелевский лауреат. Вывод: в долгосрочных конфликтах выигрывает тот, кто ставит стратегию выше быстрой выгоды</t>
-  </si>
-  <si>
     <t>Роберт Брюс</t>
   </si>
   <si>
-    <t>Внёс вклад в развитие национальной и военной стратегии Шотландии. Добился независимости страны благодаря грамотному использованию ресурсов и поддержке населения</t>
-  </si>
-  <si>
-    <t>С. К. Прахалад</t>
-  </si>
-  <si>
-    <t>1941–2010.Профессор Мичиганского университета. Автор концепции «Дно пирамиды» (заработок на беднейших слоях за счёт малого товара и высокого оборота).</t>
-  </si>
-  <si>
     <t>Самсон</t>
   </si>
   <si>
-    <t>ок. XI века до н. э.Последний из великих судей Израилевых. Обладал силой, но был лишён дара видения и стратегического мышления</t>
-  </si>
-  <si>
-    <t>царствовал ок. 970–931 до н. э. Сын Давида, построил Иерусалимский Храм. Символ того, как сбывшееся стратегическое предвидение воплощается в деяниях следующего поколения.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Внёс вклад в развитие военной истории и стратегической аналитики. Изучал деятельность великих полководцев, помогая развитию стратегического образования.</t>
-  </si>
-  <si>
-    <t>1910–1985. Американский экономист, нобелевский лауреат. Предложил сравнивать экономики по оргфункциям. Квинт считает подход широким, но недостаточным для стратегической классификации.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Внёс вклад в развитие военной стратегии и управления государством. Реформировал армию Пруссии, уделяя внимание дисциплине, скорости и маневрированию.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Внёс большой вклад в развитие современной военной стратегии. Развивал идеи оперативного планирования, координации войск и использования железных дорог</t>
-  </si>
-  <si>
-    <t>правил ок. 1029–1009 до н. э. Первый царь Израиля. Его правление знаменует рубеж разделения функций правителя и пророка, важный этап в генезисе профессии стратега.</t>
-  </si>
-  <si>
     <t>Самуил (Шмуэль)</t>
   </si>
   <si>
     <t>Сергей Королёв</t>
   </si>
   <si>
-    <t>Внёс вклад в развитие научно-технологической стратегии СССР. Реализовал космические программы, позволившие СССР стать лидером космической гонки.</t>
-  </si>
-  <si>
     <t>Соломон</t>
   </si>
   <si>
@@ -913,27 +459,15 @@
     <t xml:space="preserve">Сулейман Великолепный </t>
   </si>
   <si>
-    <t>Внёс вклад в развитие государственной и военной стратегии Османской империи. Достиг максимального могущества благодаря грамотному управлению и дипломатии</t>
-  </si>
-  <si>
     <t>Тертуллиан</t>
   </si>
   <si>
-    <t>ок. 155–220.Раннехристианский теолог. Квинт цитирует его парадокс «Верую, ибо абсурдно», подчеркивая роль иррационального в принятии стратегических решений.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Теодор Аврал Додж </t>
-  </si>
-  <si>
     <t xml:space="preserve">Тьяллинг Купманс </t>
   </si>
   <si>
     <t>Уильям Коэн</t>
   </si>
   <si>
-    <t>Внёс вклад в развитие государственной и оборонной стратегии США. Занимался вопросами национальной безопасности и модернизации вооружённых сил.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Фридрих Великий </t>
   </si>
   <si>
@@ -943,37 +477,494 @@
     <t xml:space="preserve">Царь Давид </t>
   </si>
   <si>
-    <t>ок. 1035–970 до н. э. Второй царь Израиля. Успешный правитель и воин, но сам пророком не был. Приглашал провидцев в ближний круг, компенсируя отсутствие собственного дара предвидения</t>
-  </si>
-  <si>
     <t xml:space="preserve">Царь Саул </t>
   </si>
   <si>
     <t xml:space="preserve">Чингисхан </t>
   </si>
   <si>
-    <t>Один из самых успешных стратегов благодаря мобильности армии, дисциплине и управлению территориями. Использовал разведку, психологическое воздействие и неожиданные атаки.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Эрик Шмидт </t>
   </si>
   <si>
-    <t xml:space="preserve"> Внёс вклад в развитие цифровой стратегии Google. Под его руководством компания расширила направления деятельности и укрепила позиции на мировом рынке.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Жюль Верн </t>
   </si>
   <si>
-    <t xml:space="preserve"> 1828–1905.Французский писатель. Пример технического визионера: детально описал подводную лодку «Наутилус» задолго до её появления.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Генрих Жомини </t>
   </si>
   <si>
-    <t>1779–1869.Генерал и теоретик. Квинт называет его основоположником, создавшим в 1817 году первую в мире теорию стратегии и сделавшим Россию родиной этой дисциплины.</t>
-  </si>
-  <si>
-    <t>1. В стратегии нельзя полагаться только на здравый смысл
+    <t>Термин</t>
+  </si>
+  <si>
+    <t>Определение</t>
+  </si>
+  <si>
+    <t>Алгоритм Беннетта  — метод сложения коэффициентов (P=ΣP×Wk), полезный только для оценки крайних значений (самых развитых или самых бедных стран).</t>
+  </si>
+  <si>
+    <t>Алгоритм Квинта — метод умножения коэффициентов (P=1000×ΠPkWk), более точный для малых экономик, где единичные инновации существенно влияют на эффективность.</t>
+  </si>
+  <si>
+    <t>Асимметрия  — нестандартные решения для преимущества</t>
+  </si>
+  <si>
+    <t>Баланс  — состояние системы</t>
+  </si>
+  <si>
+    <t>Беднейшие страны с большой задолженностью (БСБЗ, HIPC)  — страны, квалифицированные по инициативе МВФ и Всемирного банка как неспособные выплатить свой долг.</t>
+  </si>
+  <si>
+    <t>Большая четвёрка — крупнейшие аудиторские фирмы мира: PricewaterhouseCoopers (PwC), Deloitte Touche, Ernst &amp; Young (EY) и KPMG.</t>
+  </si>
+  <si>
+    <t>Видение — представление о будущем состоянии объекта</t>
+  </si>
+  <si>
+    <t>ВНД на душу населения — валовой национальный доход на человека, основа классификации Группы Всемирного банка для кредитных решений</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Глобализация </t>
+  </si>
+  <si>
+    <t>Глобализация  — усиление взаимосвязи экономик и рынков</t>
+  </si>
+  <si>
+    <t>Глобальное рыночное пространство — совокупность мировых рынков</t>
+  </si>
+  <si>
+    <t>Глобальный экономический миропорядок (ГЭМ)— подсистема глобального миропорядка, каркас относительно стабильного сотрудничества бизнеса с глобальными, региональными и национальными институтами. Cтимулирует преимущественно эволюционное развитие глобального рыночного пространства.</t>
+  </si>
+  <si>
+    <t>Закономерности  — повторяющиеся связи развития.</t>
+  </si>
+  <si>
+    <t>Закон экономии времени — время даёт преимущество</t>
+  </si>
+  <si>
+    <t>Закон приоритетов — реализуются только обеспеченные направления</t>
+  </si>
+  <si>
+    <t>Закон своевременности — первый и главный закон стратегии по Квинту; фактор времени является детерминирующим в стратегии</t>
+  </si>
+  <si>
+    <t>Иерархия стратегий — глобальные, национальные, региональные, корпоративные, индивидуальные</t>
+  </si>
+  <si>
+    <t>Индикаторы — основа рейтинговых систем и индексов, на которых строятся классификационные системы стран и регионов</t>
+  </si>
+  <si>
+    <t>Индекс экономики знаний — один из пяти показателей синтезированного странового рейтинга Квинта (относительная значимость 1,0)</t>
+  </si>
+  <si>
+    <t>Индекс индустрии услуг — один из пяти показателей синтезированного рейтинга (относительная значимость 0,7)</t>
+  </si>
+  <si>
+    <t>Индекс современности промышленности — показатель, разработанный Квинтом на основе базы данных ЮНИДО для синтезированного рейтинга стран</t>
+  </si>
+  <si>
+    <t>Индекс современности промышленности — источник преимуществ</t>
+  </si>
+  <si>
+    <t>Интеграция стратегий — объединение всех уровней</t>
+  </si>
+  <si>
+    <t>Инфраструктура международного бизнеса — присутствие в стране международных банков, страховых компаний, аудиторов и юридических фирм, необходимое для входа на иностранный рынок</t>
+  </si>
+  <si>
+    <t>Инерционное мышление — ориентация на прошлое</t>
+  </si>
+  <si>
+    <t>Категории стран — группы, составляющие классификационную систему; внутри категорий также применяется рейтинговая система</t>
+  </si>
+  <si>
+    <t>Конкурентные преимущества — факторы превосходства</t>
+  </si>
+  <si>
+    <t>Контролируемая государством экономика — доминирующая в России конца 2010-х модель, существенно отличающаяся как от государственного капитализма, так и от коммунизма</t>
+  </si>
+  <si>
+    <t>Малые островные развивающиеся государства — одна из трёх дополнительных категорий ООН, отражающая географическую специфику развития.</t>
+  </si>
+  <si>
+    <t>Мантическое предвидение  — псевдопредвидение в виде пророчеств, прорицаний, «откровений» и гаданий</t>
+  </si>
+  <si>
+    <t>Миссия  — фундаментальная цель и смысл существования объекта</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Морфология страны— система характеристик и внутренняя структура государства: политические, экономические, финансовые, технологические индикаторы, культурная и религиозная среда</t>
+  </si>
+  <si>
+    <t>Нави — слово из Торы, ассоциирующееся с мощным и точным видением таких великих лидеров, как Моисей и Самуил</t>
+  </si>
+  <si>
+    <t>Навиим — слово из Торы, отображающее пророка-провидца без лидерских качеств.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Наименее развитые страны (НРС, LDC)— категория ООН с 1971 года. Критерии: низкий доход (ВНД на душу населения), слабый человеческий капитал и экономическая уязвимость.</t>
+  </si>
+  <si>
+    <t>Нанотехнологии — быстро формирующаяся технология, которая может стать основой беспрецедентно больших систем стратегических компетенций.</t>
+  </si>
+  <si>
+    <t>Научное предвидение — информационно-познавательный аспект опережающего отражения как свойства высших форм материи.</t>
+  </si>
+  <si>
+    <t>Недавно индустриализованные азиатские экономики — категория МВФ: Гонконг, Корея, Сингапур и Тайвань.</t>
+  </si>
+  <si>
+    <t>Ненаучное предвидение — интуитивное (связанное с подсознанием), обыденное (по народным приметам) и мантическое (пророчества, гадания) предвидение.</t>
+  </si>
+  <si>
+    <t>Новый Свет— категория, появившаяся благодаря европейским открытиям; несистематизированные территории, ставшие затем странами и регионами.</t>
+  </si>
+  <si>
+    <t>Объективная вероятность — сценарии будущего, в которых сталкиваются или кооперируют ценностные ориентиры, интересы и приоритеты субъектов стратегирования.</t>
+  </si>
+  <si>
+    <t>Ожидаемые воспоминания — концепция Даниэля Канемана: «Мы думаем о нашем будущем как об ожидаемых воспоминаниях».</t>
+  </si>
+  <si>
+    <t>Ойкумена — термин древних греков для описания известного им мира с центром в Элладе; одна из первых попыток системного понимания мира</t>
+  </si>
+  <si>
+    <t>OTSW-анализ — метод, используемый в рамках методологии стратегирования научной школы Квинта. Расшифровывается как Opportunities (Возможности), Threats (Угрозы), Strengths (Сильные стороны) и Weaknesses (Слабые стороны).</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Планирование— разработка действий.</t>
+  </si>
+  <si>
+    <t>Политика — интеграция стратегии и тактики</t>
+  </si>
+  <si>
+    <t>Политический риск инвестиций — риск экспроприации, национализации и повреждения частной собственности иностранных лиц в странах с гражданскими волнениями.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Предвидение — способность понимать будущее.</t>
+  </si>
+  <si>
+    <t>Предсказание — результат понимания будущего.</t>
+  </si>
+  <si>
+    <t>Предугадывание — сложное предвосхищение, вид интеллектуальной деятельности человека на основе личного опыта</t>
+  </si>
+  <si>
+    <t>Предчувствие — простое предвосхищение, свойственное любому организму; одна из форм конкретизации предвидения.</t>
+  </si>
+  <si>
+    <t>Приоритеты — ключевые направления развития</t>
+  </si>
+  <si>
+    <t>Продвинутые экономики — категория МВФ с 1997 года, объединяющая развитые страны и самые зрелые СФР (Южная Корея, Сингапур, Израиль)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Прогнозирование— научное определение будущего.</t>
+  </si>
+  <si>
+    <t>Промышленные страны — устаревшая категория МВФ, заменённая на «продвинутые экономики» из-за сокращения занятости в индустриальном производстве.</t>
+  </si>
+  <si>
+    <t>Пророчество  — интуитивное предвидение.</t>
+  </si>
+  <si>
+    <t>Провидцы</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Провидцы— люди, «видевшие» картины будущего. Их главная ценность для стратегов — традиция связывать пророчества со шкалой времени</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Пророк-лидер— редчайшее сочетание способностей провидца с лидерскими качествами практика (Моисей, Мухаммед)</t>
+  </si>
+  <si>
+    <t>Прямые иностранные инвестиции (ПИИ) — инвестиции компаний в зарубежные экономики. Новый тренд: ПИИ из СФР направляются в наукоёмкие отрасли развитых стран.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Проспективные векторные решения— решения, ведущие к далёкому будущему, всегда принимаемые на грани сознания и подсознания, рационального и иррационального.</t>
+  </si>
+  <si>
+    <t>Ранги — позиции, присваиваемые странам и регионам в рейтингах, индексах и внутри классификационных категорий.</t>
+  </si>
+  <si>
+    <t>Расцветающие экономики (экономики в фазе расцвета) — высшая стадия СФР (Южная Корея, Сингапур, Израиль, Гонконг, Испания, Португалия, Греция). Стратегически конкурируют с развитыми странами.</t>
+  </si>
+  <si>
+    <t>Ресурсы  — средства для реализации стратегии.</t>
+  </si>
+  <si>
+    <t>Риск  — вероятность потерь</t>
+  </si>
+  <si>
+    <t>Синтезированный страновый рейтинг — рейтинг технологического, экономического и социального развития стран на основе пяти индикаторов.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Старый Свет— классификационная категория, ядром которой стала цивилизация ойкумены к концу XV века.</t>
+  </si>
+  <si>
+    <t>Стратег — мудрый дисциплинированный и оптимистичный профессионал, имеющий стратегическое мышление, видение будущего и интуицию, подкрепленную методологией стратегирования.</t>
+  </si>
+  <si>
+    <t>Стратеги — мудрые дисциплинированные и оптимистичные профессионалы, имеющие стратегическое мышление, видение будущего и интуицию, подкрепленную методологией стратегирования.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Стратегическая доктрина— система официальных взглядов и положений, устанавливающая направления долгосрочного развития объекта стратегирования.</t>
+  </si>
+  <si>
+    <t>Стратегическое мышление — способность принимать долгосрочные решения.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Стратегическое управление— процесс формирования и функционирования системы стратегического управления, обеспечивающей разработку и долгосрочную реализацию стратегии, её доктрины, в соответствии с содержащимися в них конкурентными преимуществами, приоритетами, целями и задачами.</t>
+  </si>
+  <si>
+    <t>Стратегический мониторинг — контроль и корректировка стратегии.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Стратегический сценарий— один из альтернативных вариантов реализации стратегии. Как правило, разрабатывается не менее трёх сценариев, которые отличаются соотношением риска, асимметричности и общественно-экономической эффективности.</t>
+  </si>
+  <si>
+    <t>Стратегия — система поиска, формулирования и развития доктрины, обеспечивающей долгосрочный успех</t>
+  </si>
+  <si>
+    <t>Стратегия дна пирамиды (BOP) — концепция профессора Прахалада о заработке на беднейших слоях за счёт продажи малых упаковок товаров при высоком обороте.</t>
+  </si>
+  <si>
+    <t>Стратегирование — процесс разработки, реализации и обновления стратегии.</t>
+  </si>
+  <si>
+    <t>Страны без выхода к морю— одна из трёх дополнительных категорий ООН, отражающая географические ограничения развития.</t>
+  </si>
+  <si>
+    <t>Страны с переходной экономикой — категория восточноевропейских стран и СНГ. Квинт критикует её: логически все СФР и развивающиеся страны находятся в переходной стадии</t>
+  </si>
+  <si>
+    <t>Страны, приступившие к формированию рынка (СПФР, frontier economies) — переходная стадия от развивающихся к СФР (Тунис, Монголия, Мадагаскар, Буркина Фасо).</t>
+  </si>
+  <si>
+    <t>Субъективная вероятность  — сценарии, в которых сталкиваются или кооперируют ценностные ориентиры, интересы и приоритеты субъектов стратегирования.</t>
+  </si>
+  <si>
+    <t>Тактика — система текущих действий для реализации стратегии.</t>
+  </si>
+  <si>
+    <t>Таксономия — теория систематизации и иерархических сфер действительности и знаний, созданная Карлом Линнеем в 1813 году.</t>
+  </si>
+  <si>
+    <t>Теория проспектного мышления— теория Канемана и Тверски о принятии решений в условиях высоких рисков, исключительно важная для стратегирования.</t>
+  </si>
+  <si>
+    <t>Третий мир — термин, ассоциировавшийся с бедными неразвитыми странами. Большинство из них отклонили принципы свободного конкурентного рынка и стали беднее.</t>
+  </si>
+  <si>
+    <t>Тренды — устойчивые направления развития.</t>
+  </si>
+  <si>
+    <t>Угрозы — негативные факторы.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Фактор времени— ключ к стратегическому преимуществу.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Фиктивная естественная убыль населения— главная стратегическая угроза для России и ещё более 20 стран в XXI веке; депопуляция, игнорируемая в большинстве стратегических документов.</t>
+  </si>
+  <si>
+    <t>Хаос будущего — неопределённость среды.</t>
+  </si>
+  <si>
+    <t>Цели — конкретные ориентиры, размещённые во времени.</t>
+  </si>
+  <si>
+    <t>Экологическая устойчивость — показатель стратегического уровня развития. Северные страны обеспечивают наиболее устойчивую окружающую среду; страны с диктатурами замыкают рейтинг.</t>
+  </si>
+  <si>
+    <t>Экологическая цивилизация — стратегия Китая «Пять в одном»: посадка деревьев на четверти территории, восстановление 30% береговой линии, сокращение потребления угля на 40%.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Авраам — Первый библейский патриарх и пророк. Отнесён к проактивным лидерам, чьё стратегическое предвидение направляло не только семью, но и целые поколения. Пример провидца, который действует, а не только созерцает.</t>
+  </si>
+  <si>
+    <t>Аарон — Период: XIII век до н. э. Старший брат Моисея и Первый первосвященник. Квинт проводит границу: Аарон —  Моисей — пророк и стратег. Духовный сан и стратегическое лидерство — разные.</t>
+  </si>
+  <si>
+    <t>Александр Невский — Внёс вклад в развитие государственной и военной стратегии Руси. Прославился грамотным использованием местности, дипломатией и способностью принимать стратегические решения в сложных условиях. Его победы и политика помогли сохранить независимость русских земель.</t>
+  </si>
+  <si>
+    <t>Александр Суворов — Один из величайших русских полководцев. Внёс вклад в развитие военной стратегии благодаря мобильности армии, быстроте принятия решений и нестандартным действиям. Его принципы подготовки войск и дисциплины стали важной частью военного стратегирования.</t>
+  </si>
+  <si>
+    <t>Амос Тверски — 1937–1996.Психолог, соавтор Канемана. Их исследования ошибочных суждений и восприятия риска в условиях неопределённости Квинт считает критически важными для теории стратегирования.</t>
+  </si>
+  <si>
+    <t>Амир Темур (Тамерлан) — стратег и основатель Империи Тимуридов. Владимир Квинт посвятил его лидерству отдельную книгу. Главный принцип: успех государства зависит от привлечения талантливых людей («предприимчивых, мужественных и благоразумных»), ценность которых превышает ценность тысяч безвольных работников</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Артур Уэлсли (Веллингтон)  — Герцог Веллингтон. Внёс вклад в развитие военной стратегии благодаря успешному противостоянию армии Наполеона. Уделял внимание дисциплине, подготовке армии и грамотному использованию местности.</t>
+  </si>
+  <si>
+    <t>Барри Гиллс — современный исследователь (XX–XXI вв.).Специалист по политэкономии Восточной Азии. Квинт цитирует его работы о связи авторитарной олигархии и экономической структуры стран ЮВА.</t>
+  </si>
+  <si>
+    <t>Билл Гейтс — ключевой стратег цифровой эпохи. Развивал программное обеспечение и сделал ставку на массовое распространение персональных компьютеров. Его решения сыграли большую роль в развитии мировой IT-индустрии</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Владимир Квинт — Создатель Общей теории стратегии и теории глобального формирующегося рынка. Под его руководством разработаны стратегии развития Санкт-Петербурга и Кузбасса до 2035 года. Иностранный член РАН, лауреат Госпремии Узбекистана. В апреле 2026 года получил звание почетного профессора Шанхайского университета.</t>
+  </si>
+  <si>
+    <t>Георгий Жуков — Один из крупнейших полководцев XX века. Внёс вклад в развитие стратегического управления армией во время Второй мировой войны. Его решения в крупнейших операциях повлияли на советскую и мировую военную стратегию</t>
+  </si>
+  <si>
+    <t>Даниил — Один из великих библейских пророков. Его видения охватывали века. Квинт подчёркивает уникальную глубину его предсказаний, недоступную даже современному планированию. Эталон предвидения.</t>
+  </si>
+  <si>
+    <t>Дарел Тай Енген — Современный американский историк экономики (XX–XXI вв.).Исследовал античные модели: свободное предпринимательство в Древней Греции и дворцовая монополия в Египте как два изначальных стратегических пути экономики.</t>
+  </si>
+  <si>
+    <t>Джек Ма — Внёс вклад в развитие цифровой стратегии и интернет-торговли. Создал платформу Alibaba, сделав ставку на развитие онлайн-бизнеса и глобальной электронной коммерции.</t>
+  </si>
+  <si>
+    <t>Джек Уэлч  — Внёс вклад в развитие корпоративной стратегии. Руководя General Electric, внедрял инновации, оптимизацию процессов и долгосрочное планирование. Пример эффективного стратегического менеджмента.</t>
+  </si>
+  <si>
+    <t>Джон Бойд — Внёс вклад в развитие современной стратегической теории. Разработал концепцию OODA Loop (быстрый анализ ситуации и принятие решений). Идеи используются в военной стратегии, бизнесе и управлении.</t>
+  </si>
+  <si>
+    <t>Джон Майкл Монтиас — 1928–2005. Историк экономики, коллега Купманса. Предложил подход к сравнению экономических систем по организационным функциям, который Квинт рассматривает как важный шаг, но с ограничениями.</t>
+  </si>
+  <si>
+    <t>Джонатан Свифт — 1667–1745.Англо-ирландский писатель. Квинт отмечает его предвидение: за полтора века до открытия Свифт описал два спутника Марса и их орбитальные параметры, почти совпавшие с реальностью.</t>
+  </si>
+  <si>
+    <t>Дэн Сяопин — Внёс огромный вклад в развитие экономической стратегии Китая. Провёл реформы, открывшие страну для мирового рынка. Благодаря этому Китай начал быстрое экономическое развитие</t>
+  </si>
+  <si>
+    <t>Игорь Бестужев-Лада — 1927–2015. Советский и российский учёный, социолог и футуролог. Представитель отечественной школы, начавшей осмысливать процессы научного и ненаучного познания будущего</t>
+  </si>
+  <si>
+    <t>Иисус Навин — ок. XIII–XII века до н. э. Преемник Моисея, завоеватель Ханаана. Квинт описывает его как образец военного стратега и полководца, а не пророка.</t>
+  </si>
+  <si>
+    <t>Илон Маск — Известен долгосрочным стратегическим видением и инновационным подходом. Развивает проекты в области космоса, электромобилей и ИИ. Стратегии основаны на высоких рисках и стремлении изменить будущее</t>
+  </si>
+  <si>
+    <t>Император Маврикий — Внёс значительный вклад в развитие византийской военной стратегии. Систематизировал знания о ведении войны и организации армии. Его труды стали основой для многих военных трактатов Средневековья.</t>
+  </si>
+  <si>
+    <t>Кассандра — ок. XIII–XII века до н. э. (мифология).Троянская царевна с даром точного предвидения, но обречённая на то, что ей никто не верил. Символ трагедии провидца, лишённого стратегического влияния.</t>
+  </si>
+  <si>
+    <t>Карл фон Клаузевиц  — Один из главных теоретиков стратегии. В работе «О войне» рассматривал войну как продолжение политики. Его идеи оказали огромное влияние на современную военную и государственную стратегию</t>
+  </si>
+  <si>
+    <t>Кеничи Омае — Ведущий специалист в области бизнес-стратегии. Изучал глобализацию и конкурентные преимущества. Его идеи повлияли на современное корпоративное стратегирование</t>
+  </si>
+  <si>
+    <t>Конрад Аденауэр — Сыграл важную роль в восстановлении Германии после Второй мировой войны. Использовал долгосрочное стратегическое планирование для укрепления экономики и международных отношений</t>
+  </si>
+  <si>
+    <t>Корнелиус Вандербилт  — Внёс вклад в развитие экономической и транспортной стратегии. Создал крупную транспортную империю, используя долгосрочное планирование и контроль инфраструктуры</t>
+  </si>
+  <si>
+    <t>Лев VI Мудрый — Развивал стратегические и тактические принципы Византии. Уделял внимание анализу военных действий и изучению опыта прошлых войн. Сохранил византийскую школу стратегирования</t>
+  </si>
+  <si>
+    <t>Марк Аврелий  — правил 161–180. Римский император, философ-стоик. Уникальный пример сочетания императора, мудреца и стратега-провидца, не допускавшего ошибок от конфликта этих ролей.</t>
+  </si>
+  <si>
+    <t>Мартин Кайдин  — 1927–1997.Американский писатель, автор романа «Киборг». Предвосхитил появление бионических протезов, управляемых силой мысли</t>
+  </si>
+  <si>
+    <t>Мэрилл Келли Беннетт  — Американский экономист, профессор Стэнфорда. Автор методики рейтингования стран середины XX века. Квинт критикует его алгоритм сложения показателей за неточность.</t>
+  </si>
+  <si>
+    <t>Миямото Мусаси  — Японский стратег и мастер боевых искусств. Разработал подход, основанный на дисциплине, психологическом превосходстве и анализе противника. Автор «Книги пяти колец».</t>
+  </si>
+  <si>
+    <t>Моисей  —  приблизительно XIII век до н. э.Библейский пророк и вождь. Квинт считает его величайшим провидцем-стратегом, сочетавшим дар предвидения и практическое лидерство, ведя народ сквозь хаос пустыни</t>
+  </si>
+  <si>
+    <t>Мухаммед (Магомет) — ок. 570–632. Основатель ислама и глава первого мусульманского государства. Редчайшая фигура, сочетавшая посланническую миссию и практическое стратегическое руководство</t>
+  </si>
+  <si>
+    <t>Натан (Нафан)  — X век до н. э.Пророк при дворе царя Давида. Предвидел воцарение Соломона и строительство Храма. Пример стратегического совета провидца, определявшего государственные решения</t>
+  </si>
+  <si>
+    <t>Наполеон Бонапарт  — 1769–1821.Император Франции и великий полководец. Активно использовал скорость, концентрацию сил и мобильность. Квинт анализирует поход 1812 года как трагедию выбора пути гибели без чёткого плана</t>
+  </si>
+  <si>
+    <t>Нострадамус (Мишель де Нострдам)  — 1503–1566.Французский врач и астролог. Квинт восхищается точностью ряда предсказаний, но делает вывод: Нострадамус — предсказатель, а не пророк.</t>
+  </si>
+  <si>
+    <t>Олдос Хаксли  — 1894–1963. Английский писатель, автор «О дивный новый мир». Предсказал генную инженерию и вмешательство в репродукцию задолго до появления технологий</t>
+  </si>
+  <si>
+    <t>Отто фон Бисмарк — Мастер дипломатической стратегии. Объединил Германию благодаря продуманной политике, союзам и использованию международной обстановки. Пример долгосрочного государственного планирования.</t>
+  </si>
+  <si>
+    <t>Павел I — Уделял внимание реформированию армии и укреплению дисциплины. Стремился повысить эффективность вооружённых сил, что повлияло на дальнейшее развитие военной стратегии России.</t>
+  </si>
+  <si>
+    <t>Пётр I  — Внёс большой вклад в развитие государственной и военной стратегии России. Провёл масштабные реформы армии, флота и управления. Укрепил международное положение России</t>
+  </si>
+  <si>
+    <t>Роберт Ауман  — родился в 1930 году. Израильский математик, нобелевский лауреат. Вывод: в долгосрочных конфликтах выигрывает тот, кто ставит стратегию выше быстрой выгоды</t>
+  </si>
+  <si>
+    <t>Роберт Брюс — Внёс вклад в развитие национальной и военной стратегии Шотландии. Добился независимости страны благодаря грамотному использованию ресурсов и поддержке населения</t>
+  </si>
+  <si>
+    <t>Самсон — ок. XI века до н. э.Последний из великих судей Израилевых. Обладал силой, но был лишён дара видения и стратегического мышления</t>
+  </si>
+  <si>
+    <t>Самуил (Шмуэль) — XI век до н. э.Последний судья и первый крупный пророк Израиля. Путь от провидца до государственного стратега, руководившего военными действиями и помазанием царей.</t>
+  </si>
+  <si>
+    <t>Сергей Королёв — Внёс вклад в развитие научно-технологической стратегии СССР. Реализовал космические программы, позволившие СССР стать лидером космической гонки.</t>
+  </si>
+  <si>
+    <t>Соломон — царствовал ок. 970–931 до н. э. Сын Давида, построил Иерусалимский Храм. Символ того, как сбывшееся стратегическое предвидение воплощается в деяниях следующего поколения.</t>
+  </si>
+  <si>
+    <t>Стив Джобс  — Внёс вклад в развитие инновационной и технологической стратегии. Ставка на качество, дизайн и создание новых рынков. Превратил Apple в крупнейшую технологическую компанию.</t>
+  </si>
+  <si>
+    <t>Султан Мехмет II — Завоеватель Константинополя. Использовал новые технологии, артиллерию и стратегическое планирование. Повлиял на развитие османской стратегии.</t>
+  </si>
+  <si>
+    <t>Сулейман Великолепный  — Внёс вклад в развитие государственной и военной стратегии Османской империи. Достиг максимального могущества благодаря грамотному управлению и дипломатии</t>
+  </si>
+  <si>
+    <t>Тертуллиан — ок. 155–220.Раннехристианский теолог. Квинт цитирует его парадокс «Верую, ибо абсурдно», подчеркивая роль иррационального в принятии стратегических решений.</t>
+  </si>
+  <si>
+    <t>Тьяллинг Купманс  — 1910–1985. Американский экономист, нобелевский лауреат. Предложил сравнивать экономики по оргфункциям. Квинт считает подход широким, но недостаточным для стратегической классификации.</t>
+  </si>
+  <si>
+    <t>Уильям Коэн — Внёс вклад в развитие государственной и оборонной стратегии США. Занимался вопросами национальной безопасности и модернизации вооружённых сил.</t>
+  </si>
+  <si>
+    <t>Фридрих Великий  — Внёс вклад в развитие военной стратегии и управления государством. Реформировал армию Пруссии, уделяя внимание дисциплине, скорости и маневрированию.</t>
+  </si>
+  <si>
+    <t>Хельмут фон Мольтке  — Внёс большой вклад в развитие современной военной стратегии. Развивал идеи оперативного планирования, координации войск и использования железных дорог</t>
+  </si>
+  <si>
+    <t>Царь Давид  — ок. 1035–970 до н. э. Второй царь Израиля. Успешный правитель и воин, но сам пророком не был. Приглашал провидцев в ближний круг, компенсируя отсутствие собственного дара предвидения</t>
+  </si>
+  <si>
+    <t>Царь Саул — правил ок. 1029–1009 до н. э. Первый царь Израиля. Его правление знаменует рубеж разделения функций правителя и пророка, важный этап в генезисе профессии стратега.</t>
+  </si>
+  <si>
+    <t>Чингисхан  — Один из самых успешных стратегов благодаря мобильности армии, дисциплине и управлению территориями. Использовал разведку, психологическое воздействие и неожиданные атаки.</t>
+  </si>
+  <si>
+    <t>Эрик Шмидт  —  Внёс вклад в развитие цифровой стратегии Google. Под его руководством компания расширила направления деятельности и укрепила позиции на мировом рынке.</t>
+  </si>
+  <si>
+    <t>Жюль Верн — 1828–1905.Французский писатель. Пример технического визионера: детально описал подводную лодку «Наутилус» задолго до её появления.</t>
+  </si>
+  <si>
+    <t>Генрих Жомини  — 1779–1869.Генерал и теоретик. Квинт называет его основоположником, создавшим в 1817 году первую в мире теорию стратегии и сделавшим Россию родиной этой дисциплины.</t>
+  </si>
+  <si>
+    <t>15 правил стратегирования В.Л. Квинта
+1. В стратегии нельзя полагаться только на здравый смысл
 2. В стратегии мнение большинства обычно ошибочно
 3. Стратегически настоящее — это уже прошлое
 4. Использовать опыт успешно реализованных стратегий
@@ -990,17 +981,249 @@
 15. Стратеги должны выявлять и ориентироваться на истинные потребности организации, а не на желания руководителей</t>
   </si>
   <si>
-    <t>Термин</t>
-  </si>
-  <si>
-    <t>Определение</t>
+    <t>https://pravoslavie.wiki/prorok-avraam-praroditel-narodov.html</t>
+  </si>
+  <si>
+    <t>https://my.tretyakov.ru/app/masterpiece/47834</t>
+  </si>
+  <si>
+    <t>https://rg.ru/2020/10/06/pochemu-dlia-nas-segodnia-vazhen-aleksandr-nevskij.html</t>
+  </si>
+  <si>
+    <t>https://klincollege.ru/novosti/velikie-lyudi-rossijskoj-istorii.-aleksandr-suvorov/</t>
+  </si>
+  <si>
+    <t>https://www.psygazeta.ru/rubriki/psikhologicheskij-kalendar/4969-5-faktov-ob-amose-tverski.html</t>
+  </si>
+  <si>
+    <t>https://novotours.uz/ru/about-uzbekistan/izvestnye-lyudi-uzbekistana/amir_temur.html/</t>
+  </si>
+  <si>
+    <t>https://ru.wikipedia.org/wiki/%D0%92%D0%B5%D0%BB%D0%BB%D0%B8%D0%BD%D0%B3%D1%82%D0%BE%D0%BD,_%D0%90%D1%80%D1%82%D1%83%D1%80_%D0%A3%D1%8D%D0%BB%D1%81%D0%BB%D0%B8</t>
+  </si>
+  <si>
+    <t>https://www.tni.org/en/profile/barry-k-gills</t>
+  </si>
+  <si>
+    <t>https://ru.wikipedia.org/wiki/%D0%93%D0%B5%D0%B9%D1%82%D1%81,_%D0%91%D0%B8%D0%BB%D0%BB</t>
+  </si>
+  <si>
+    <t>https://snob.ru/news/121217/</t>
+  </si>
+  <si>
+    <t>https://virtual.uspu.ru/znamenatelnye-daty-v-istorii-rossii/zhukov-georgij-konstantinovich-1-dekabrya-1896-18-iyunya-1974</t>
+  </si>
+  <si>
+    <t>https://history.ru/read/biographies/daniil-alieksandrovich-moskovskii</t>
+  </si>
+  <si>
+    <t>https://www.wipo.int/ru/web/director-general/daren-tang/cv</t>
+  </si>
+  <si>
+    <t>https://ru.wikipedia.org/wiki/%D0%94%D0%B6%D0%B5%D0%BA_%D0%9C%D0%B0</t>
+  </si>
+  <si>
+    <t>https://ru.wikipedia.org/wiki/%D0%A3%D1%8D%D0%BB%D1%87,_%D0%94%D0%B6%D0%B5%D0%BA</t>
+  </si>
+  <si>
+    <t>https://marketer.ua/ru/history-of-the-f-16-how-the-mad-major-and-like-minded-people-created-a-revolutionary-fighter/</t>
+  </si>
+  <si>
+    <t>https://www.irwincollier.com/yale-meet-an-assistant-professor-of-economics-montias-1960/</t>
+  </si>
+  <si>
+    <t>https://historia.nationalgeographic.com.es/a/jonathan-swift-autor-los-viajes-gulliver-y-mayor-critico-ser-humano_15743</t>
+  </si>
+  <si>
+    <t>https://ria.ru/20140822/1020737967.html</t>
+  </si>
+  <si>
+    <t>https://habr.com/ru/articles/388977/</t>
+  </si>
+  <si>
+    <t>https://www.icon-art.info/detail.php?det_id=5573</t>
+  </si>
+  <si>
+    <t>https://ru.wikipedia.org/wiki/%D0%9C%D0%B0%D1%81%D0%BA,_%D0%98%D0%BB%D0%BE%D0%BD</t>
+  </si>
+  <si>
+    <t>https://azbyka.ru/days/sv-mavrikij-apamejskij</t>
+  </si>
+  <si>
+    <t>https://ru.ruwiki.ru/wiki/%D0%9A%D0%B0%D1%81%D1%81%D0%B0%D0%BD%D0%B4%D1%80%D0%B0</t>
+  </si>
+  <si>
+    <t>https://ru.wikipedia.org/wiki/%D0%A4%D0%B0%D0%B9%D0%BB:Carl_von_Clausewitz.PNG</t>
+  </si>
+  <si>
+    <t>https://alpinabook.ru/authors/omae-kenichi/?srsltid=AYCX9vJPkSutnBw2zwv7RvpqSyR55A5kufDT1nv20y5i-hF-bSUCJJFN</t>
+  </si>
+  <si>
+    <t>https://ru.wikipedia.org/wiki/%D0%90%D0%B4%D0%B5%D0%BD%D0%B0%D1%83%D1%8D%D1%80,_%D0%9A%D0%BE%D0%BD%D1%80%D0%B0%D0%B4</t>
+  </si>
+  <si>
+    <t>https://ru.wikipedia.org/wiki/%D0%92%D0%B0%D0%BD%D0%B4%D0%B5%D1%80%D0%B1%D0%B8%D0%BB%D1%8C%D1%82,_%D0%9A%D0%BE%D1%80%D0%BD%D0%B5%D0%BB%D0%B8%D1%83%D1%81</t>
+  </si>
+  <si>
+    <t>https://rus.team/people/lev-vi-filosof</t>
+  </si>
+  <si>
+    <t>https://biographe.ru/politiki/mark-avreliy/</t>
+  </si>
+  <si>
+    <t>https://en.wikipedia.org/wiki/Martin_Caidin</t>
+  </si>
+  <si>
+    <t>https://www.shogunclub.ru/faktyi-o-miyamoto-musasi</t>
+  </si>
+  <si>
+    <t>https://my.tretyakov.ru/app/masterpiece/47839</t>
+  </si>
+  <si>
+    <t>https://www.asekose.am/ru/post/ukaz-proroka-muxammeda-pro-armanskiy-narod</t>
+  </si>
+  <si>
+    <t>https://azbyka.ru/days/sv-nafan</t>
+  </si>
+  <si>
+    <t>https://udm.wikipedia.org/wiki/%D0%9D%D0%B0%D0%BF%D0%BE%D0%BB%D0%B5%D0%BE%D0%BD</t>
+  </si>
+  <si>
+    <t>https://www.kommersant.ru/doc/3826527</t>
+  </si>
+  <si>
+    <t>https://ru.wikipedia.org/wiki/%D0%A5%D0%B0%D0%BA%D1%81%D0%BB%D0%B8,_%D0%9E%D0%BB%D0%B4%D0%BE%D1%81</t>
+  </si>
+  <si>
+    <t>https://ru.wikipedia.org/wiki/%D0%91%D0%B8%D1%81%D0%BC%D0%B0%D1%80%D0%BA,_%D0%9E%D1%82%D1%82%D0%BE_%D1%84%D0%BE%D0%BD</t>
+  </si>
+  <si>
+    <t>https://ru.wikipedia.org/wiki/%D0%9F%D0%B0%D0%B2%D0%B5%D0%BB_I</t>
+  </si>
+  <si>
+    <t>https://ru.wikipedia.org/wiki/%D0%9F%D1%91%D1%82%D1%80_I</t>
+  </si>
+  <si>
+    <t>https://www.peoples.ru/science/mathematics/robert_aumann/</t>
+  </si>
+  <si>
+    <t>https://ru.wikipedia.org/wiki/%D0%A0%D0%BE%D0%B1%D0%B5%D1%80%D1%82_I_%28%D0%BA%D0%BE%D1%80%D0%BE%D0%BB%D1%8C_%D0%A8%D0%BE%D1%82%D0%BB%D0%B0%D0%BD%D0%B4%D0%B8%D0%B8%29</t>
+  </si>
+  <si>
+    <t>https://www.olbuss.ru/avtory/prakhalad-k-k</t>
+  </si>
+  <si>
+    <t>К. К. Прахалад — 1941–2010.Профессор Мичиганского университета. Автор концепции «Дно пирамиды» (заработок на беднейших слоях за счёт малого товара и высокого оборота).</t>
+  </si>
+  <si>
+    <t>К. К. Прахалад</t>
+  </si>
+  <si>
+    <t>https://ru.wikipedia.org/wiki/%D0%A1%D0%B0%D0%BC%D1%81%D0%BE%D0%BD</t>
+  </si>
+  <si>
+    <t>https://ru.wikipedia.org/wiki/%D0%A1%D0%B0%D0%BC%D1%83%D0%B8%D0%BB</t>
+  </si>
+  <si>
+    <t>https://ru.wikipedia.org/wiki/%D0%9A%D0%BE%D1%80%D0%BE%D0%BB%D1%91%D0%B2,_%D0%A1%D0%B5%D1%80%D0%B3%D0%B5%D0%B9_%D0%9F%D0%B0%D0%B2%D0%BB%D0%BE%D0%B2%D0%B8%D1%87</t>
+  </si>
+  <si>
+    <t>https://ru.wikipedia.org/wiki/%D0%A1%D0%BE%D0%BB%D0%BE%D0%BC%D0%BE%D0%BD</t>
+  </si>
+  <si>
+    <t>https://adebiportal.kz/ru/authors/view/114</t>
+  </si>
+  <si>
+    <t>https://ru.wikipedia.org/wiki/%D0%9C%D0%B5%D1%85%D0%BC%D0%B5%D0%B4_II</t>
+  </si>
+  <si>
+    <t>https://interesnyefakty.org/sulejman-velikolepnyj/</t>
+  </si>
+  <si>
+    <t>https://ru.wikipedia.org/wiki/%D0%A2%D0%B5%D1%80%D1%82%D1%83%D0%BB%D0%BB%D0%B8%D0%B0%D0%BD</t>
+  </si>
+  <si>
+    <t>Теодор Эйро Додж  — Внёс вклад в развитие военной истории и стратегической аналитики. Изучал деятельность великих полководцев, помогая развитию стратегического образования.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Теодор Эйро Додж </t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/29/Theodore_Ayrault_Dodge_1842%E2%80%931909.jpg/960px-Theodore_Ayrault_Dodge_1842%E2%80%931909.jpg</t>
+  </si>
+  <si>
+    <t>https://avatars.mds.yandex.net/i?id=0006b29a7d8254ae5ba2d6efebab01ae_l-5220706-images-thumbs&amp;n=13</t>
+  </si>
+  <si>
+    <t>https://www.mediaite.com/wp-content/uploads/2019/10/Former-defense-secretary-William-Cohen.jpg</t>
+  </si>
+  <si>
+    <t>https://avatars.mds.yandex.net/i?id=dba8ee2fecc024d669755d4d2ad969f0_l-5167251-images-thumbs&amp;n=13</t>
+  </si>
+  <si>
+    <t>https://veche-info.ru/wp-content/uploads/2023/12/helmuth_karl_bernhard_graf_von_moltke.jpg</t>
+  </si>
+  <si>
+    <t>https://www.krestilnoe.ru/userfiles/ufiles/Zhitie_svyatogo_carya_i_proroka_davida_-_pravoslavnye_molitvy_1.jpg</t>
+  </si>
+  <si>
+    <t>https://avatars.mds.yandex.net/i?id=318f33ae800e6cc51249a26949013cd1_l-5331946-images-thumbs&amp;n=13</t>
+  </si>
+  <si>
+    <t>https://istorik.ru/_next/image?url=%2Fimages%2Fpersons%2Fchingiskhan.jpg&amp;w=3840&amp;q=75</t>
+  </si>
+  <si>
+    <t>https://avatars.mds.yandex.net/i?id=6e0697160b95366e8be584048e53b3bafd2f9542-12421307-images-thumbs&amp;n=13</t>
+  </si>
+  <si>
+    <t>https://mezgore-lib.ru/wp-content/uploads/2024/02/42432-2-768x937-1.jpg</t>
+  </si>
+  <si>
+    <t>https://urss.ru/images/add_ru/$24176$_150831.jpg</t>
+  </si>
+  <si>
+    <t>Картинка</t>
+  </si>
+  <si>
+    <t>Создатели</t>
+  </si>
+  <si>
+    <t>Создателями телеграм бота "Бот статег" являются: Пинжин Кирилл и Злобин Владислав
+Напишите в чат "Кирилл" или "Влад" чтобы узнать о каждом подробнее!</t>
+  </si>
+  <si>
+    <t>Кирилл</t>
+  </si>
+  <si>
+    <t>Пинжин Кирилл - главный разработчик проекта. Отвечал за написание кода в Python, интеграцию базы данных Excel, работу с GitHub и развёртывание бота на сервере Bothost.</t>
+  </si>
+  <si>
+    <t>Влад</t>
+  </si>
+  <si>
+    <t>Злобин Влад - контент-менеджер и аналитик прооекта. Отвечал за сбор материалов, изучение трудов академика В.Квинта, структурирование терминов и ведение базы данных в Excel.</t>
+  </si>
+  <si>
+    <t>https://ibb.co/Lz3mT6Jh</t>
+  </si>
+  <si>
+    <t>https://giga.chat/files/public/generated/e36c7924-4bf2-41ca-bf1a-0a49b945dcca</t>
+  </si>
+  <si>
+    <t>Денчик Иванов</t>
+  </si>
+  <si>
+    <t>Денчик - кент Кирюхи Пинжина</t>
+  </si>
+  <si>
+    <t>https://ibb.co/mV05T4ZZ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1039,6 +1262,15 @@
       <family val="2"/>
       <charset val="204"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1057,10 +1289,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1095,8 +1328,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1375,1271 +1613,1570 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B157"/>
+  <dimension ref="A1:C161"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="255.5703125" customWidth="1"/>
     <col min="2" max="2" width="231" customWidth="1"/>
+    <col min="3" max="3" width="103.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>312</v>
+        <v>151</v>
       </c>
       <c r="B1" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+      <c r="C1" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="B4" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="B6" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="B7" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="B8" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" t="s">
+      <c r="B9" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="B10" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="8" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10" t="s">
+      <c r="B12" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="9" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="B13" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="B13" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>35</v>
-      </c>
       <c r="B14" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>36</v>
-      </c>
       <c r="B15" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="5" t="s">
-        <v>37</v>
-      </c>
       <c r="B16" t="s">
-        <v>14</v>
+        <v>168</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>15</v>
+        <v>169</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="7" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>40</v>
+        <v>170</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>16</v>
+        <v>171</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="7" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>17</v>
+        <v>172</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>44</v>
+        <v>173</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="B22" t="s">
-        <v>45</v>
+        <v>174</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="B23" t="s">
-        <v>18</v>
+        <v>175</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="B24" t="s">
-        <v>49</v>
+        <v>176</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>19</v>
+        <v>177</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>20</v>
+        <v>178</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>53</v>
+        <v>179</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>21</v>
+        <v>180</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>22</v>
+        <v>181</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>57</v>
+        <v>26</v>
       </c>
       <c r="B30" t="s">
-        <v>56</v>
+        <v>182</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="B31" t="s">
-        <v>58</v>
+        <v>183</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="B32" t="s">
-        <v>61</v>
+        <v>184</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="B33" t="s">
-        <v>63</v>
+        <v>185</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="B34" t="s">
-        <v>65</v>
+        <v>186</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="B35" t="s">
-        <v>67</v>
+        <v>187</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
-        <v>69</v>
+        <v>32</v>
       </c>
       <c r="B36" t="s">
-        <v>68</v>
+        <v>188</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" s="9" t="s">
-        <v>70</v>
+        <v>33</v>
       </c>
       <c r="B37" t="s">
-        <v>71</v>
+        <v>189</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="B38" t="s">
-        <v>73</v>
+        <v>190</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="9" t="s">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="B39" t="s">
-        <v>75</v>
+        <v>191</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="9" t="s">
-        <v>77</v>
+        <v>36</v>
       </c>
       <c r="B40" t="s">
-        <v>76</v>
+        <v>192</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="9" t="s">
-        <v>78</v>
+        <v>37</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>79</v>
+        <v>193</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="9" t="s">
-        <v>80</v>
+        <v>38</v>
       </c>
       <c r="B42" t="s">
-        <v>81</v>
+        <v>194</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="9" t="s">
-        <v>82</v>
+        <v>39</v>
       </c>
       <c r="B43" t="s">
-        <v>83</v>
+        <v>195</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="9" t="s">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="B44" t="s">
-        <v>85</v>
+        <v>196</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="9" t="s">
-        <v>86</v>
+        <v>41</v>
       </c>
       <c r="B45" t="s">
-        <v>87</v>
+        <v>197</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="7" t="s">
-        <v>88</v>
+        <v>42</v>
       </c>
       <c r="B46" t="s">
-        <v>89</v>
+        <v>198</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="9" t="s">
-        <v>90</v>
+        <v>43</v>
       </c>
       <c r="B47" t="s">
-        <v>91</v>
+        <v>199</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="9" t="s">
-        <v>93</v>
+        <v>44</v>
       </c>
       <c r="B48" t="s">
-        <v>92</v>
+        <v>200</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="9" t="s">
-        <v>94</v>
+        <v>45</v>
       </c>
       <c r="B49" t="s">
-        <v>95</v>
+        <v>201</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" s="7" t="s">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="B50" t="s">
-        <v>97</v>
+        <v>202</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="9" t="s">
-        <v>98</v>
+        <v>47</v>
       </c>
       <c r="B51" t="s">
-        <v>99</v>
+        <v>203</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
-        <v>100</v>
+        <v>48</v>
       </c>
       <c r="B52" t="s">
-        <v>101</v>
+        <v>204</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>102</v>
+        <v>49</v>
       </c>
       <c r="B53" t="s">
-        <v>103</v>
+        <v>205</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="9" t="s">
-        <v>104</v>
+        <v>50</v>
       </c>
       <c r="B54" t="s">
-        <v>105</v>
+        <v>206</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="9" t="s">
-        <v>106</v>
+        <v>51</v>
       </c>
       <c r="B55" t="s">
-        <v>107</v>
+        <v>207</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" s="9" t="s">
-        <v>109</v>
+        <v>52</v>
       </c>
       <c r="B56" t="s">
-        <v>108</v>
+        <v>208</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="9" t="s">
-        <v>110</v>
+        <v>209</v>
       </c>
       <c r="B57" t="s">
-        <v>111</v>
+        <v>210</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>112</v>
+        <v>53</v>
       </c>
       <c r="B58" t="s">
-        <v>113</v>
+        <v>211</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>114</v>
+        <v>54</v>
       </c>
       <c r="B59" t="s">
-        <v>115</v>
+        <v>212</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>116</v>
+        <v>55</v>
       </c>
       <c r="B60" t="s">
-        <v>117</v>
+        <v>213</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" s="9" t="s">
-        <v>118</v>
+        <v>56</v>
       </c>
       <c r="B61" t="s">
-        <v>119</v>
+        <v>214</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>120</v>
+        <v>57</v>
       </c>
       <c r="B62" t="s">
-        <v>121</v>
+        <v>215</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>123</v>
+        <v>58</v>
       </c>
       <c r="B63" t="s">
-        <v>122</v>
+        <v>216</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="7" t="s">
-        <v>133</v>
+        <v>59</v>
       </c>
       <c r="B64" t="s">
-        <v>124</v>
+        <v>217</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>134</v>
+        <v>60</v>
       </c>
       <c r="B65" t="s">
-        <v>125</v>
+        <v>218</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" s="9" t="s">
-        <v>135</v>
+        <v>61</v>
       </c>
       <c r="B66" t="s">
-        <v>136</v>
+        <v>219</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>137</v>
+        <v>62</v>
       </c>
       <c r="B67" t="s">
-        <v>126</v>
+        <v>220</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>138</v>
+        <v>63</v>
       </c>
       <c r="B68" t="s">
-        <v>127</v>
+        <v>221</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>139</v>
+        <v>64</v>
       </c>
       <c r="B69" t="s">
-        <v>140</v>
+        <v>222</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>141</v>
+        <v>65</v>
       </c>
       <c r="B70" t="s">
-        <v>128</v>
+        <v>223</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>142</v>
+        <v>66</v>
       </c>
       <c r="B71" t="s">
-        <v>143</v>
+        <v>224</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>144</v>
+        <v>67</v>
       </c>
       <c r="B72" t="s">
-        <v>129</v>
+        <v>225</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>145</v>
+        <v>68</v>
       </c>
       <c r="B73" t="s">
-        <v>146</v>
+        <v>226</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" s="10" t="s">
-        <v>147</v>
+        <v>69</v>
       </c>
       <c r="B74" t="s">
-        <v>130</v>
+        <v>227</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>148</v>
+        <v>70</v>
       </c>
       <c r="B75" t="s">
-        <v>131</v>
+        <v>228</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>149</v>
+        <v>71</v>
       </c>
       <c r="B76" t="s">
-        <v>132</v>
+        <v>229</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>151</v>
+        <v>72</v>
       </c>
       <c r="B77" t="s">
-        <v>150</v>
+        <v>230</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" s="10" t="s">
-        <v>152</v>
+        <v>73</v>
       </c>
       <c r="B78" t="s">
-        <v>153</v>
+        <v>231</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>154</v>
+        <v>74</v>
       </c>
       <c r="B79" t="s">
-        <v>155</v>
+        <v>232</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>157</v>
+        <v>75</v>
       </c>
       <c r="B80" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>158</v>
+        <v>76</v>
       </c>
       <c r="B81" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>160</v>
+        <v>77</v>
       </c>
       <c r="B82" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="9" t="s">
-        <v>163</v>
+        <v>78</v>
       </c>
       <c r="B83" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>164</v>
+        <v>79</v>
       </c>
       <c r="B84" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>166</v>
+        <v>80</v>
       </c>
       <c r="B85" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>169</v>
+        <v>81</v>
       </c>
       <c r="B86" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>170</v>
+        <v>82</v>
       </c>
       <c r="B87" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>172</v>
+        <v>83</v>
       </c>
       <c r="B88" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>174</v>
+        <v>84</v>
       </c>
       <c r="B89" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>176</v>
+        <v>85</v>
       </c>
       <c r="B90" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>178</v>
+        <v>86</v>
       </c>
       <c r="B91" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>180</v>
+        <v>87</v>
       </c>
       <c r="B92" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>184</v>
+        <v>89</v>
       </c>
       <c r="B93" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+        <v>246</v>
+      </c>
+      <c r="C93" s="14" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="9" t="s">
-        <v>185</v>
+        <v>90</v>
       </c>
       <c r="B94" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+      <c r="C94" s="14" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="9" t="s">
-        <v>187</v>
+        <v>91</v>
       </c>
       <c r="B95" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+        <v>248</v>
+      </c>
+      <c r="C95" s="14" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="11" t="s">
-        <v>189</v>
+        <v>92</v>
       </c>
       <c r="B96" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+        <v>249</v>
+      </c>
+      <c r="C96" s="14" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="9" t="s">
-        <v>191</v>
+        <v>93</v>
       </c>
       <c r="B97" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+        <v>250</v>
+      </c>
+      <c r="C97" s="14" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="7" t="s">
-        <v>193</v>
+        <v>94</v>
       </c>
       <c r="B98" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+        <v>251</v>
+      </c>
+      <c r="C98" s="14" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="9" t="s">
-        <v>195</v>
+        <v>95</v>
       </c>
       <c r="B99" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+        <v>252</v>
+      </c>
+      <c r="C99" s="14" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="9" t="s">
-        <v>197</v>
+        <v>96</v>
       </c>
       <c r="B100" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+        <v>253</v>
+      </c>
+      <c r="C100" s="14" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="11" t="s">
-        <v>199</v>
+        <v>97</v>
       </c>
       <c r="B101" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+      <c r="C101" s="14" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="9" t="s">
-        <v>202</v>
+        <v>98</v>
       </c>
       <c r="B102" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+        <v>255</v>
+      </c>
+      <c r="C102" s="14" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="11" t="s">
-        <v>203</v>
+        <v>99</v>
       </c>
       <c r="B103" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+        <v>256</v>
+      </c>
+      <c r="C103" s="14" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="9" t="s">
-        <v>206</v>
+        <v>100</v>
       </c>
       <c r="B104" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+        <v>257</v>
+      </c>
+      <c r="C104" s="14" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="9" t="s">
-        <v>207</v>
+        <v>101</v>
       </c>
       <c r="B105" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+        <v>258</v>
+      </c>
+      <c r="C105" s="14" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="9" t="s">
-        <v>209</v>
+        <v>102</v>
       </c>
       <c r="B106" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+        <v>259</v>
+      </c>
+      <c r="C106" s="14" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>211</v>
+        <v>103</v>
       </c>
       <c r="B107" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+        <v>260</v>
+      </c>
+      <c r="C107" s="14" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" s="9" t="s">
-        <v>214</v>
+        <v>104</v>
       </c>
       <c r="B108" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+        <v>261</v>
+      </c>
+      <c r="C108" s="14" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>215</v>
+        <v>105</v>
       </c>
       <c r="B109" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+        <v>262</v>
+      </c>
+      <c r="C109" s="14" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" s="11" t="s">
-        <v>217</v>
+        <v>106</v>
       </c>
       <c r="B110" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+        <v>263</v>
+      </c>
+      <c r="C110" s="14" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" s="11" t="s">
-        <v>219</v>
+        <v>107</v>
       </c>
       <c r="B111" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+        <v>264</v>
+      </c>
+      <c r="C111" s="14" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" s="11" t="s">
-        <v>222</v>
+        <v>108</v>
       </c>
       <c r="B112" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+        <v>265</v>
+      </c>
+      <c r="C112" s="14" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" s="11" t="s">
-        <v>226</v>
+        <v>109</v>
       </c>
       <c r="B113" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+        <v>266</v>
+      </c>
+      <c r="C113" s="14" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" s="11" t="s">
-        <v>227</v>
+        <v>110</v>
       </c>
       <c r="B114" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+      <c r="C114" s="14" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" s="11" t="s">
-        <v>228</v>
+        <v>111</v>
       </c>
       <c r="B115" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+        <v>268</v>
+      </c>
+      <c r="C115" s="14" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" s="9" t="s">
-        <v>230</v>
+        <v>112</v>
       </c>
       <c r="B116" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+        <v>269</v>
+      </c>
+      <c r="C116" s="14" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" s="11" t="s">
-        <v>231</v>
+        <v>113</v>
       </c>
       <c r="B117" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+        <v>270</v>
+      </c>
+      <c r="C117" s="14" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" s="11" t="s">
-        <v>234</v>
+        <v>114</v>
       </c>
       <c r="B118" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+        <v>271</v>
+      </c>
+      <c r="C118" s="14" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" s="11" t="s">
-        <v>235</v>
+        <v>115</v>
       </c>
       <c r="B119" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+        <v>272</v>
+      </c>
+      <c r="C119" s="14" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" s="11" t="s">
-        <v>238</v>
+        <v>116</v>
       </c>
       <c r="B120" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+        <v>273</v>
+      </c>
+      <c r="C120" s="14" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" s="11" t="s">
-        <v>248</v>
+        <v>117</v>
       </c>
       <c r="B121" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+        <v>274</v>
+      </c>
+      <c r="C121" s="14" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" s="11" t="s">
-        <v>250</v>
+        <v>118</v>
       </c>
       <c r="B122" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+        <v>275</v>
+      </c>
+      <c r="C122" s="14" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" s="11" t="s">
-        <v>251</v>
+        <v>119</v>
       </c>
       <c r="B123" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+        <v>276</v>
+      </c>
+      <c r="C123" s="14" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" s="11" t="s">
-        <v>252</v>
+        <v>120</v>
       </c>
       <c r="B124" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" s="11" t="s">
-        <v>253</v>
+        <v>121</v>
       </c>
       <c r="B125" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+        <v>278</v>
+      </c>
+      <c r="C125" s="14" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" s="11" t="s">
-        <v>254</v>
+        <v>122</v>
       </c>
       <c r="B126" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+        <v>279</v>
+      </c>
+      <c r="C126" s="14" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" s="11" t="s">
-        <v>256</v>
+        <v>123</v>
       </c>
       <c r="B127" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+        <v>280</v>
+      </c>
+      <c r="C127" s="14" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" s="11" t="s">
-        <v>257</v>
+        <v>124</v>
       </c>
       <c r="B128" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+        <v>281</v>
+      </c>
+      <c r="C128" s="14" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" s="11" t="s">
-        <v>258</v>
+        <v>125</v>
       </c>
       <c r="B129" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+        <v>282</v>
+      </c>
+      <c r="C129" s="14" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" s="11" t="s">
-        <v>260</v>
+        <v>126</v>
       </c>
       <c r="B130" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+        <v>283</v>
+      </c>
+      <c r="C130" s="14" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" s="11" t="s">
-        <v>261</v>
+        <v>127</v>
       </c>
       <c r="B131" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+        <v>284</v>
+      </c>
+      <c r="C131" s="14" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" s="11" t="s">
-        <v>267</v>
+        <v>128</v>
       </c>
       <c r="B132" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+        <v>285</v>
+      </c>
+      <c r="C132" s="14" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" s="11" t="s">
-        <v>268</v>
+        <v>129</v>
       </c>
       <c r="B133" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+        <v>286</v>
+      </c>
+      <c r="C133" s="14" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" s="11" t="s">
-        <v>269</v>
+        <v>130</v>
       </c>
       <c r="B134" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+        <v>287</v>
+      </c>
+      <c r="C134" s="14" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" s="11" t="s">
-        <v>270</v>
+        <v>131</v>
       </c>
       <c r="B135" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+        <v>288</v>
+      </c>
+      <c r="C135" s="14" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" s="11" t="s">
-        <v>272</v>
+        <v>132</v>
       </c>
       <c r="B136" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+        <v>289</v>
+      </c>
+      <c r="C136" s="14" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" s="11" t="s">
-        <v>274</v>
+        <v>354</v>
       </c>
       <c r="B137" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+        <v>353</v>
+      </c>
+      <c r="C137" s="14" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" s="11" t="s">
-        <v>276</v>
+        <v>133</v>
       </c>
       <c r="B138" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+        <v>290</v>
+      </c>
+      <c r="C138" s="14" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" s="11" t="s">
-        <v>284</v>
+        <v>134</v>
       </c>
       <c r="B139" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+        <v>291</v>
+      </c>
+      <c r="C139" s="14" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" s="11" t="s">
-        <v>285</v>
+        <v>135</v>
       </c>
       <c r="B140" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+        <v>292</v>
+      </c>
+      <c r="C140" s="14" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" s="11" t="s">
-        <v>287</v>
+        <v>136</v>
       </c>
       <c r="B141" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+        <v>293</v>
+      </c>
+      <c r="C141" s="14" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" s="11" t="s">
-        <v>288</v>
+        <v>137</v>
       </c>
       <c r="B142" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+        <v>294</v>
+      </c>
+      <c r="C142" s="14" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" s="11" t="s">
-        <v>289</v>
+        <v>138</v>
       </c>
       <c r="B143" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+        <v>295</v>
+      </c>
+      <c r="C143" s="14" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" s="11" t="s">
-        <v>290</v>
+        <v>139</v>
       </c>
       <c r="B144" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+        <v>296</v>
+      </c>
+      <c r="C144" s="14" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" s="11" t="s">
-        <v>292</v>
+        <v>140</v>
       </c>
       <c r="B145" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+        <v>297</v>
+      </c>
+      <c r="C145" s="14" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" s="11" t="s">
-        <v>294</v>
+        <v>364</v>
       </c>
       <c r="B146" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+        <v>363</v>
+      </c>
+      <c r="C146" s="14" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" s="11" t="s">
-        <v>295</v>
+        <v>141</v>
       </c>
       <c r="B147" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+        <v>298</v>
+      </c>
+      <c r="C147" s="14" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" s="11" t="s">
-        <v>296</v>
+        <v>142</v>
       </c>
       <c r="B148" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+        <v>299</v>
+      </c>
+      <c r="C148" s="14" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" s="11" t="s">
-        <v>298</v>
+        <v>143</v>
       </c>
       <c r="B149" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
+        <v>300</v>
+      </c>
+      <c r="C149" s="14" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" s="11" t="s">
-        <v>299</v>
+        <v>144</v>
       </c>
       <c r="B150" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+        <v>301</v>
+      </c>
+      <c r="C150" s="14" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" s="11" t="s">
-        <v>300</v>
+        <v>145</v>
       </c>
       <c r="B151" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
+        <v>302</v>
+      </c>
+      <c r="C151" s="14" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" s="11" t="s">
-        <v>302</v>
+        <v>146</v>
       </c>
       <c r="B152" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
+        <v>303</v>
+      </c>
+      <c r="C152" s="14" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" s="11" t="s">
-        <v>303</v>
+        <v>147</v>
       </c>
       <c r="B153" t="s">
         <v>304</v>
       </c>
-    </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C153" s="14" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="B154" t="s">
         <v>305</v>
       </c>
-      <c r="B154" t="s">
+      <c r="C154" s="14" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="B155" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A155" s="11" t="s">
+      <c r="C155" s="14" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="B156" t="s">
         <v>307</v>
       </c>
-      <c r="B155" t="s">
+      <c r="C156" s="14" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" ht="240" x14ac:dyDescent="0.25">
+      <c r="A157" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="B157" s="13" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A156" s="11" t="s">
-        <v>309</v>
-      </c>
-      <c r="B156" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="157" spans="1:2" ht="225" x14ac:dyDescent="0.25">
-      <c r="A157" s="11" t="s">
-        <v>182</v>
-      </c>
-      <c r="B157" s="13" t="s">
-        <v>311</v>
+    <row r="158" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A158" s="11" t="s">
+        <v>377</v>
+      </c>
+      <c r="B158" s="15" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159" s="11" t="s">
+        <v>379</v>
+      </c>
+      <c r="B159" t="s">
+        <v>380</v>
+      </c>
+      <c r="C159" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160" s="11" t="s">
+        <v>381</v>
+      </c>
+      <c r="B160" t="s">
+        <v>382</v>
+      </c>
+      <c r="C160" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161" s="11" t="s">
+        <v>385</v>
+      </c>
+      <c r="B161" t="s">
+        <v>386</v>
+      </c>
+      <c r="C161" t="s">
+        <v>387</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C93" r:id="rId1"/>
+    <hyperlink ref="C94" r:id="rId2"/>
+    <hyperlink ref="C95" r:id="rId3"/>
+    <hyperlink ref="C96" r:id="rId4"/>
+    <hyperlink ref="C97" r:id="rId5"/>
+    <hyperlink ref="C98" r:id="rId6"/>
+    <hyperlink ref="C99" r:id="rId7"/>
+    <hyperlink ref="C100" r:id="rId8"/>
+    <hyperlink ref="C101" r:id="rId9"/>
+    <hyperlink ref="C102" r:id="rId10"/>
+    <hyperlink ref="C103" r:id="rId11"/>
+    <hyperlink ref="C104" r:id="rId12"/>
+    <hyperlink ref="C105" r:id="rId13"/>
+    <hyperlink ref="C106" r:id="rId14"/>
+    <hyperlink ref="C107" r:id="rId15"/>
+    <hyperlink ref="C108" r:id="rId16"/>
+    <hyperlink ref="C109" r:id="rId17"/>
+    <hyperlink ref="C110" r:id="rId18"/>
+    <hyperlink ref="C111" r:id="rId19"/>
+    <hyperlink ref="C112" r:id="rId20"/>
+    <hyperlink ref="C113" r:id="rId21"/>
+    <hyperlink ref="C114" r:id="rId22"/>
+    <hyperlink ref="C115" r:id="rId23"/>
+    <hyperlink ref="C116" r:id="rId24"/>
+    <hyperlink ref="C117" r:id="rId25"/>
+    <hyperlink ref="C118" r:id="rId26"/>
+    <hyperlink ref="C119" r:id="rId27"/>
+    <hyperlink ref="C120" r:id="rId28"/>
+    <hyperlink ref="C121" r:id="rId29"/>
+    <hyperlink ref="C122" r:id="rId30"/>
+    <hyperlink ref="C123" r:id="rId31"/>
+    <hyperlink ref="C125" r:id="rId32"/>
+    <hyperlink ref="C126" r:id="rId33"/>
+    <hyperlink ref="C127" r:id="rId34"/>
+    <hyperlink ref="C128" r:id="rId35"/>
+    <hyperlink ref="C129" r:id="rId36"/>
+    <hyperlink ref="C130" r:id="rId37"/>
+    <hyperlink ref="C131" r:id="rId38"/>
+    <hyperlink ref="C132" r:id="rId39"/>
+    <hyperlink ref="C133" r:id="rId40"/>
+    <hyperlink ref="C134" r:id="rId41"/>
+    <hyperlink ref="C135" r:id="rId42"/>
+    <hyperlink ref="C136" r:id="rId43"/>
+    <hyperlink ref="C137" r:id="rId44"/>
+    <hyperlink ref="C138" r:id="rId45"/>
+    <hyperlink ref="C139" r:id="rId46"/>
+    <hyperlink ref="C140" r:id="rId47"/>
+    <hyperlink ref="C141" r:id="rId48"/>
+    <hyperlink ref="C142" r:id="rId49"/>
+    <hyperlink ref="C143" r:id="rId50"/>
+    <hyperlink ref="C144" r:id="rId51"/>
+    <hyperlink ref="C145" r:id="rId52"/>
+    <hyperlink ref="C146" r:id="rId53"/>
+    <hyperlink ref="C147" r:id="rId54"/>
+    <hyperlink ref="C148" r:id="rId55"/>
+    <hyperlink ref="C149" r:id="rId56"/>
+    <hyperlink ref="C150" r:id="rId57"/>
+    <hyperlink ref="C151" r:id="rId58"/>
+    <hyperlink ref="C152" r:id="rId59"/>
+    <hyperlink ref="C153" r:id="rId60"/>
+    <hyperlink ref="C154" r:id="rId61"/>
+    <hyperlink ref="C155" r:id="rId62"/>
+    <hyperlink ref="C156" r:id="rId63"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId64"/>
 </worksheet>
 </file>
--- a/database.xlsx
+++ b/database.xlsx
@@ -1188,19 +1188,12 @@
     <t>Создатели</t>
   </si>
   <si>
-    <t>Создателями телеграм бота "Бот статег" являются: Пинжин Кирилл и Злобин Владислав
-Напишите в чат "Кирилл" или "Влад" чтобы узнать о каждом подробнее!</t>
-  </si>
-  <si>
     <t>Кирилл</t>
   </si>
   <si>
     <t>Пинжин Кирилл - главный разработчик проекта. Отвечал за написание кода в Python, интеграцию базы данных Excel, работу с GitHub и развёртывание бота на сервере Bothost.</t>
   </si>
   <si>
-    <t>Влад</t>
-  </si>
-  <si>
     <t>Злобин Влад - контент-менеджер и аналитик прооекта. Отвечал за сбор материалов, изучение трудов академика В.Квинта, структурирование терминов и ведение базы данных в Excel.</t>
   </si>
   <si>
@@ -1217,6 +1210,13 @@
   </si>
   <si>
     <t>https://ibb.co/mV05T4ZZ</t>
+  </si>
+  <si>
+    <t>Владос</t>
+  </si>
+  <si>
+    <t>Создателями телеграм бота "Бот стратег" являются: Пинжин Кирилл и Злобин Владислав
+Напишите в чат "Кирилл" или "Владос" чтобы узнать о каждом подробнее!</t>
   </si>
 </sst>
 </file>
@@ -3074,40 +3074,40 @@
         <v>377</v>
       </c>
       <c r="B158" s="15" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" s="11" t="s">
+        <v>378</v>
+      </c>
+      <c r="B159" t="s">
         <v>379</v>
       </c>
-      <c r="B159" t="s">
-        <v>380</v>
-      </c>
       <c r="C159" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" s="11" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="B160" t="s">
+        <v>380</v>
+      </c>
+      <c r="C160" t="s">
         <v>382</v>
-      </c>
-      <c r="C160" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" s="11" t="s">
+        <v>383</v>
+      </c>
+      <c r="B161" t="s">
+        <v>384</v>
+      </c>
+      <c r="C161" t="s">
         <v>385</v>
-      </c>
-      <c r="B161" t="s">
-        <v>386</v>
-      </c>
-      <c r="C161" t="s">
-        <v>387</v>
       </c>
     </row>
   </sheetData>

--- a/database.xlsx
+++ b/database.xlsx
@@ -12,7 +12,7 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755" tabRatio="603"/>
   </bookViews>
   <sheets>
-    <sheet name="Лист1" sheetId="1" r:id="rId1"/>
+    <sheet name="База" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="386">
   <si>
     <t xml:space="preserve">Алгоритм Беннетта </t>
   </si>
@@ -327,9 +327,6 @@
   </si>
   <si>
     <t>Даниил</t>
-  </si>
-  <si>
-    <t>Дарел Тай Енген</t>
   </si>
   <si>
     <t>Джек Ма</t>
@@ -498,472 +495,506 @@
     <t>Определение</t>
   </si>
   <si>
-    <t>Алгоритм Беннетта  — метод сложения коэффициентов (P=ΣP×Wk), полезный только для оценки крайних значений (самых развитых или самых бедных стран).</t>
-  </si>
-  <si>
-    <t>Алгоритм Квинта — метод умножения коэффициентов (P=1000×ΠPkWk), более точный для малых экономик, где единичные инновации существенно влияют на эффективность.</t>
-  </si>
-  <si>
-    <t>Асимметрия  — нестандартные решения для преимущества</t>
-  </si>
-  <si>
-    <t>Баланс  — состояние системы</t>
-  </si>
-  <si>
-    <t>Беднейшие страны с большой задолженностью (БСБЗ, HIPC)  — страны, квалифицированные по инициативе МВФ и Всемирного банка как неспособные выплатить свой долг.</t>
-  </si>
-  <si>
-    <t>Большая четвёрка — крупнейшие аудиторские фирмы мира: PricewaterhouseCoopers (PwC), Deloitte Touche, Ernst &amp; Young (EY) и KPMG.</t>
-  </si>
-  <si>
-    <t>Видение — представление о будущем состоянии объекта</t>
-  </si>
-  <si>
-    <t>ВНД на душу населения — валовой национальный доход на человека, основа классификации Группы Всемирного банка для кредитных решений</t>
-  </si>
-  <si>
     <t xml:space="preserve">Глобализация </t>
   </si>
   <si>
-    <t>Глобализация  — усиление взаимосвязи экономик и рынков</t>
-  </si>
-  <si>
-    <t>Глобальное рыночное пространство — совокупность мировых рынков</t>
-  </si>
-  <si>
-    <t>Глобальный экономический миропорядок (ГЭМ)— подсистема глобального миропорядка, каркас относительно стабильного сотрудничества бизнеса с глобальными, региональными и национальными институтами. Cтимулирует преимущественно эволюционное развитие глобального рыночного пространства.</t>
-  </si>
-  <si>
-    <t>Закономерности  — повторяющиеся связи развития.</t>
-  </si>
-  <si>
-    <t>Закон экономии времени — время даёт преимущество</t>
-  </si>
-  <si>
-    <t>Закон приоритетов — реализуются только обеспеченные направления</t>
-  </si>
-  <si>
-    <t>Закон своевременности — первый и главный закон стратегии по Квинту; фактор времени является детерминирующим в стратегии</t>
-  </si>
-  <si>
-    <t>Иерархия стратегий — глобальные, национальные, региональные, корпоративные, индивидуальные</t>
-  </si>
-  <si>
-    <t>Индикаторы — основа рейтинговых систем и индексов, на которых строятся классификационные системы стран и регионов</t>
-  </si>
-  <si>
-    <t>Индекс экономики знаний — один из пяти показателей синтезированного странового рейтинга Квинта (относительная значимость 1,0)</t>
-  </si>
-  <si>
-    <t>Индекс индустрии услуг — один из пяти показателей синтезированного рейтинга (относительная значимость 0,7)</t>
-  </si>
-  <si>
-    <t>Индекс современности промышленности — показатель, разработанный Квинтом на основе базы данных ЮНИДО для синтезированного рейтинга стран</t>
-  </si>
-  <si>
-    <t>Индекс современности промышленности — источник преимуществ</t>
-  </si>
-  <si>
-    <t>Интеграция стратегий — объединение всех уровней</t>
-  </si>
-  <si>
-    <t>Инфраструктура международного бизнеса — присутствие в стране международных банков, страховых компаний, аудиторов и юридических фирм, необходимое для входа на иностранный рынок</t>
-  </si>
-  <si>
-    <t>Инерционное мышление — ориентация на прошлое</t>
-  </si>
-  <si>
-    <t>Категории стран — группы, составляющие классификационную систему; внутри категорий также применяется рейтинговая система</t>
-  </si>
-  <si>
-    <t>Конкурентные преимущества — факторы превосходства</t>
-  </si>
-  <si>
-    <t>Контролируемая государством экономика — доминирующая в России конца 2010-х модель, существенно отличающаяся как от государственного капитализма, так и от коммунизма</t>
-  </si>
-  <si>
-    <t>Малые островные развивающиеся государства — одна из трёх дополнительных категорий ООН, отражающая географическую специфику развития.</t>
-  </si>
-  <si>
-    <t>Мантическое предвидение  — псевдопредвидение в виде пророчеств, прорицаний, «откровений» и гаданий</t>
-  </si>
-  <si>
-    <t>Миссия  — фундаментальная цель и смысл существования объекта</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Морфология страны— система характеристик и внутренняя структура государства: политические, экономические, финансовые, технологические индикаторы, культурная и религиозная среда</t>
-  </si>
-  <si>
-    <t>Нави — слово из Торы, ассоциирующееся с мощным и точным видением таких великих лидеров, как Моисей и Самуил</t>
-  </si>
-  <si>
-    <t>Навиим — слово из Торы, отображающее пророка-провидца без лидерских качеств.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Наименее развитые страны (НРС, LDC)— категория ООН с 1971 года. Критерии: низкий доход (ВНД на душу населения), слабый человеческий капитал и экономическая уязвимость.</t>
-  </si>
-  <si>
-    <t>Нанотехнологии — быстро формирующаяся технология, которая может стать основой беспрецедентно больших систем стратегических компетенций.</t>
-  </si>
-  <si>
-    <t>Научное предвидение — информационно-познавательный аспект опережающего отражения как свойства высших форм материи.</t>
-  </si>
-  <si>
-    <t>Недавно индустриализованные азиатские экономики — категория МВФ: Гонконг, Корея, Сингапур и Тайвань.</t>
-  </si>
-  <si>
-    <t>Ненаучное предвидение — интуитивное (связанное с подсознанием), обыденное (по народным приметам) и мантическое (пророчества, гадания) предвидение.</t>
-  </si>
-  <si>
-    <t>Новый Свет— категория, появившаяся благодаря европейским открытиям; несистематизированные территории, ставшие затем странами и регионами.</t>
-  </si>
-  <si>
-    <t>Объективная вероятность — сценарии будущего, в которых сталкиваются или кооперируют ценностные ориентиры, интересы и приоритеты субъектов стратегирования.</t>
-  </si>
-  <si>
-    <t>Ожидаемые воспоминания — концепция Даниэля Канемана: «Мы думаем о нашем будущем как об ожидаемых воспоминаниях».</t>
-  </si>
-  <si>
-    <t>Ойкумена — термин древних греков для описания известного им мира с центром в Элладе; одна из первых попыток системного понимания мира</t>
-  </si>
-  <si>
-    <t>OTSW-анализ — метод, используемый в рамках методологии стратегирования научной школы Квинта. Расшифровывается как Opportunities (Возможности), Threats (Угрозы), Strengths (Сильные стороны) и Weaknesses (Слабые стороны).</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Планирование— разработка действий.</t>
-  </si>
-  <si>
-    <t>Политика — интеграция стратегии и тактики</t>
-  </si>
-  <si>
-    <t>Политический риск инвестиций — риск экспроприации, национализации и повреждения частной собственности иностранных лиц в странах с гражданскими волнениями.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Предвидение — способность понимать будущее.</t>
-  </si>
-  <si>
-    <t>Предсказание — результат понимания будущего.</t>
-  </si>
-  <si>
-    <t>Предугадывание — сложное предвосхищение, вид интеллектуальной деятельности человека на основе личного опыта</t>
-  </si>
-  <si>
-    <t>Предчувствие — простое предвосхищение, свойственное любому организму; одна из форм конкретизации предвидения.</t>
-  </si>
-  <si>
-    <t>Приоритеты — ключевые направления развития</t>
-  </si>
-  <si>
-    <t>Продвинутые экономики — категория МВФ с 1997 года, объединяющая развитые страны и самые зрелые СФР (Южная Корея, Сингапур, Израиль)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Прогнозирование— научное определение будущего.</t>
-  </si>
-  <si>
-    <t>Промышленные страны — устаревшая категория МВФ, заменённая на «продвинутые экономики» из-за сокращения занятости в индустриальном производстве.</t>
-  </si>
-  <si>
-    <t>Пророчество  — интуитивное предвидение.</t>
-  </si>
-  <si>
     <t>Провидцы</t>
   </si>
   <si>
-    <t xml:space="preserve"> Провидцы— люди, «видевшие» картины будущего. Их главная ценность для стратегов — традиция связывать пророчества со шкалой времени</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Пророк-лидер— редчайшее сочетание способностей провидца с лидерскими качествами практика (Моисей, Мухаммед)</t>
-  </si>
-  <si>
-    <t>Прямые иностранные инвестиции (ПИИ) — инвестиции компаний в зарубежные экономики. Новый тренд: ПИИ из СФР направляются в наукоёмкие отрасли развитых стран.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Проспективные векторные решения— решения, ведущие к далёкому будущему, всегда принимаемые на грани сознания и подсознания, рационального и иррационального.</t>
-  </si>
-  <si>
-    <t>Ранги — позиции, присваиваемые странам и регионам в рейтингах, индексах и внутри классификационных категорий.</t>
-  </si>
-  <si>
-    <t>Расцветающие экономики (экономики в фазе расцвета) — высшая стадия СФР (Южная Корея, Сингапур, Израиль, Гонконг, Испания, Португалия, Греция). Стратегически конкурируют с развитыми странами.</t>
-  </si>
-  <si>
-    <t>Ресурсы  — средства для реализации стратегии.</t>
-  </si>
-  <si>
-    <t>Риск  — вероятность потерь</t>
-  </si>
-  <si>
-    <t>Синтезированный страновый рейтинг — рейтинг технологического, экономического и социального развития стран на основе пяти индикаторов.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Старый Свет— классификационная категория, ядром которой стала цивилизация ойкумены к концу XV века.</t>
-  </si>
-  <si>
-    <t>Стратег — мудрый дисциплинированный и оптимистичный профессионал, имеющий стратегическое мышление, видение будущего и интуицию, подкрепленную методологией стратегирования.</t>
-  </si>
-  <si>
-    <t>Стратеги — мудрые дисциплинированные и оптимистичные профессионалы, имеющие стратегическое мышление, видение будущего и интуицию, подкрепленную методологией стратегирования.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Стратегическая доктрина— система официальных взглядов и положений, устанавливающая направления долгосрочного развития объекта стратегирования.</t>
-  </si>
-  <si>
-    <t>Стратегическое мышление — способность принимать долгосрочные решения.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Стратегическое управление— процесс формирования и функционирования системы стратегического управления, обеспечивающей разработку и долгосрочную реализацию стратегии, её доктрины, в соответствии с содержащимися в них конкурентными преимуществами, приоритетами, целями и задачами.</t>
-  </si>
-  <si>
-    <t>Стратегический мониторинг — контроль и корректировка стратегии.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Стратегический сценарий— один из альтернативных вариантов реализации стратегии. Как правило, разрабатывается не менее трёх сценариев, которые отличаются соотношением риска, асимметричности и общественно-экономической эффективности.</t>
-  </si>
-  <si>
-    <t>Стратегия — система поиска, формулирования и развития доктрины, обеспечивающей долгосрочный успех</t>
-  </si>
-  <si>
-    <t>Стратегия дна пирамиды (BOP) — концепция профессора Прахалада о заработке на беднейших слоях за счёт продажи малых упаковок товаров при высоком обороте.</t>
-  </si>
-  <si>
-    <t>Стратегирование — процесс разработки, реализации и обновления стратегии.</t>
-  </si>
-  <si>
-    <t>Страны без выхода к морю— одна из трёх дополнительных категорий ООН, отражающая географические ограничения развития.</t>
-  </si>
-  <si>
-    <t>Страны с переходной экономикой — категория восточноевропейских стран и СНГ. Квинт критикует её: логически все СФР и развивающиеся страны находятся в переходной стадии</t>
-  </si>
-  <si>
-    <t>Страны, приступившие к формированию рынка (СПФР, frontier economies) — переходная стадия от развивающихся к СФР (Тунис, Монголия, Мадагаскар, Буркина Фасо).</t>
-  </si>
-  <si>
-    <t>Субъективная вероятность  — сценарии, в которых сталкиваются или кооперируют ценностные ориентиры, интересы и приоритеты субъектов стратегирования.</t>
-  </si>
-  <si>
-    <t>Тактика — система текущих действий для реализации стратегии.</t>
-  </si>
-  <si>
-    <t>Таксономия — теория систематизации и иерархических сфер действительности и знаний, созданная Карлом Линнеем в 1813 году.</t>
-  </si>
-  <si>
-    <t>Теория проспектного мышления— теория Канемана и Тверски о принятии решений в условиях высоких рисков, исключительно важная для стратегирования.</t>
-  </si>
-  <si>
-    <t>Третий мир — термин, ассоциировавшийся с бедными неразвитыми странами. Большинство из них отклонили принципы свободного конкурентного рынка и стали беднее.</t>
-  </si>
-  <si>
-    <t>Тренды — устойчивые направления развития.</t>
-  </si>
-  <si>
-    <t>Угрозы — негативные факторы.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Фактор времени— ключ к стратегическому преимуществу.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Фиктивная естественная убыль населения— главная стратегическая угроза для России и ещё более 20 стран в XXI веке; депопуляция, игнорируемая в большинстве стратегических документов.</t>
-  </si>
-  <si>
-    <t>Хаос будущего — неопределённость среды.</t>
-  </si>
-  <si>
-    <t>Цели — конкретные ориентиры, размещённые во времени.</t>
-  </si>
-  <si>
-    <t>Экологическая устойчивость — показатель стратегического уровня развития. Северные страны обеспечивают наиболее устойчивую окружающую среду; страны с диктатурами замыкают рейтинг.</t>
-  </si>
-  <si>
-    <t>Экологическая цивилизация — стратегия Китая «Пять в одном»: посадка деревьев на четверти территории, восстановление 30% береговой линии, сокращение потребления угля на 40%.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Авраам — Первый библейский патриарх и пророк. Отнесён к проактивным лидерам, чьё стратегическое предвидение направляло не только семью, но и целые поколения. Пример провидца, который действует, а не только созерцает.</t>
-  </si>
-  <si>
-    <t>Аарон — Период: XIII век до н. э. Старший брат Моисея и Первый первосвященник. Квинт проводит границу: Аарон —  Моисей — пророк и стратег. Духовный сан и стратегическое лидерство — разные.</t>
-  </si>
-  <si>
-    <t>Александр Невский — Внёс вклад в развитие государственной и военной стратегии Руси. Прославился грамотным использованием местности, дипломатией и способностью принимать стратегические решения в сложных условиях. Его победы и политика помогли сохранить независимость русских земель.</t>
-  </si>
-  <si>
-    <t>Александр Суворов — Один из величайших русских полководцев. Внёс вклад в развитие военной стратегии благодаря мобильности армии, быстроте принятия решений и нестандартным действиям. Его принципы подготовки войск и дисциплины стали важной частью военного стратегирования.</t>
-  </si>
-  <si>
-    <t>Амос Тверски — 1937–1996.Психолог, соавтор Канемана. Их исследования ошибочных суждений и восприятия риска в условиях неопределённости Квинт считает критически важными для теории стратегирования.</t>
-  </si>
-  <si>
-    <t>Амир Темур (Тамерлан) — стратег и основатель Империи Тимуридов. Владимир Квинт посвятил его лидерству отдельную книгу. Главный принцип: успех государства зависит от привлечения талантливых людей («предприимчивых, мужественных и благоразумных»), ценность которых превышает ценность тысяч безвольных работников</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Артур Уэлсли (Веллингтон)  — Герцог Веллингтон. Внёс вклад в развитие военной стратегии благодаря успешному противостоянию армии Наполеона. Уделял внимание дисциплине, подготовке армии и грамотному использованию местности.</t>
-  </si>
-  <si>
-    <t>Барри Гиллс — современный исследователь (XX–XXI вв.).Специалист по политэкономии Восточной Азии. Квинт цитирует его работы о связи авторитарной олигархии и экономической структуры стран ЮВА.</t>
-  </si>
-  <si>
-    <t>Билл Гейтс — ключевой стратег цифровой эпохи. Развивал программное обеспечение и сделал ставку на массовое распространение персональных компьютеров. Его решения сыграли большую роль в развитии мировой IT-индустрии</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Владимир Квинт — Создатель Общей теории стратегии и теории глобального формирующегося рынка. Под его руководством разработаны стратегии развития Санкт-Петербурга и Кузбасса до 2035 года. Иностранный член РАН, лауреат Госпремии Узбекистана. В апреле 2026 года получил звание почетного профессора Шанхайского университета.</t>
-  </si>
-  <si>
-    <t>Георгий Жуков — Один из крупнейших полководцев XX века. Внёс вклад в развитие стратегического управления армией во время Второй мировой войны. Его решения в крупнейших операциях повлияли на советскую и мировую военную стратегию</t>
-  </si>
-  <si>
-    <t>Даниил — Один из великих библейских пророков. Его видения охватывали века. Квинт подчёркивает уникальную глубину его предсказаний, недоступную даже современному планированию. Эталон предвидения.</t>
-  </si>
-  <si>
-    <t>Дарел Тай Енген — Современный американский историк экономики (XX–XXI вв.).Исследовал античные модели: свободное предпринимательство в Древней Греции и дворцовая монополия в Египте как два изначальных стратегических пути экономики.</t>
-  </si>
-  <si>
-    <t>Джек Ма — Внёс вклад в развитие цифровой стратегии и интернет-торговли. Создал платформу Alibaba, сделав ставку на развитие онлайн-бизнеса и глобальной электронной коммерции.</t>
-  </si>
-  <si>
-    <t>Джек Уэлч  — Внёс вклад в развитие корпоративной стратегии. Руководя General Electric, внедрял инновации, оптимизацию процессов и долгосрочное планирование. Пример эффективного стратегического менеджмента.</t>
-  </si>
-  <si>
-    <t>Джон Бойд — Внёс вклад в развитие современной стратегической теории. Разработал концепцию OODA Loop (быстрый анализ ситуации и принятие решений). Идеи используются в военной стратегии, бизнесе и управлении.</t>
-  </si>
-  <si>
-    <t>Джон Майкл Монтиас — 1928–2005. Историк экономики, коллега Купманса. Предложил подход к сравнению экономических систем по организационным функциям, который Квинт рассматривает как важный шаг, но с ограничениями.</t>
-  </si>
-  <si>
-    <t>Джонатан Свифт — 1667–1745.Англо-ирландский писатель. Квинт отмечает его предвидение: за полтора века до открытия Свифт описал два спутника Марса и их орбитальные параметры, почти совпавшие с реальностью.</t>
-  </si>
-  <si>
-    <t>Дэн Сяопин — Внёс огромный вклад в развитие экономической стратегии Китая. Провёл реформы, открывшие страну для мирового рынка. Благодаря этому Китай начал быстрое экономическое развитие</t>
-  </si>
-  <si>
-    <t>Игорь Бестужев-Лада — 1927–2015. Советский и российский учёный, социолог и футуролог. Представитель отечественной школы, начавшей осмысливать процессы научного и ненаучного познания будущего</t>
-  </si>
-  <si>
-    <t>Иисус Навин — ок. XIII–XII века до н. э. Преемник Моисея, завоеватель Ханаана. Квинт описывает его как образец военного стратега и полководца, а не пророка.</t>
-  </si>
-  <si>
-    <t>Илон Маск — Известен долгосрочным стратегическим видением и инновационным подходом. Развивает проекты в области космоса, электромобилей и ИИ. Стратегии основаны на высоких рисках и стремлении изменить будущее</t>
-  </si>
-  <si>
-    <t>Император Маврикий — Внёс значительный вклад в развитие византийской военной стратегии. Систематизировал знания о ведении войны и организации армии. Его труды стали основой для многих военных трактатов Средневековья.</t>
-  </si>
-  <si>
-    <t>Кассандра — ок. XIII–XII века до н. э. (мифология).Троянская царевна с даром точного предвидения, но обречённая на то, что ей никто не верил. Символ трагедии провидца, лишённого стратегического влияния.</t>
-  </si>
-  <si>
-    <t>Карл фон Клаузевиц  — Один из главных теоретиков стратегии. В работе «О войне» рассматривал войну как продолжение политики. Его идеи оказали огромное влияние на современную военную и государственную стратегию</t>
-  </si>
-  <si>
-    <t>Кеничи Омае — Ведущий специалист в области бизнес-стратегии. Изучал глобализацию и конкурентные преимущества. Его идеи повлияли на современное корпоративное стратегирование</t>
-  </si>
-  <si>
-    <t>Конрад Аденауэр — Сыграл важную роль в восстановлении Германии после Второй мировой войны. Использовал долгосрочное стратегическое планирование для укрепления экономики и международных отношений</t>
-  </si>
-  <si>
-    <t>Корнелиус Вандербилт  — Внёс вклад в развитие экономической и транспортной стратегии. Создал крупную транспортную империю, используя долгосрочное планирование и контроль инфраструктуры</t>
-  </si>
-  <si>
-    <t>Лев VI Мудрый — Развивал стратегические и тактические принципы Византии. Уделял внимание анализу военных действий и изучению опыта прошлых войн. Сохранил византийскую школу стратегирования</t>
-  </si>
-  <si>
-    <t>Марк Аврелий  — правил 161–180. Римский император, философ-стоик. Уникальный пример сочетания императора, мудреца и стратега-провидца, не допускавшего ошибок от конфликта этих ролей.</t>
-  </si>
-  <si>
-    <t>Мартин Кайдин  — 1927–1997.Американский писатель, автор романа «Киборг». Предвосхитил появление бионических протезов, управляемых силой мысли</t>
-  </si>
-  <si>
-    <t>Мэрилл Келли Беннетт  — Американский экономист, профессор Стэнфорда. Автор методики рейтингования стран середины XX века. Квинт критикует его алгоритм сложения показателей за неточность.</t>
-  </si>
-  <si>
-    <t>Миямото Мусаси  — Японский стратег и мастер боевых искусств. Разработал подход, основанный на дисциплине, психологическом превосходстве и анализе противника. Автор «Книги пяти колец».</t>
-  </si>
-  <si>
-    <t>Моисей  —  приблизительно XIII век до н. э.Библейский пророк и вождь. Квинт считает его величайшим провидцем-стратегом, сочетавшим дар предвидения и практическое лидерство, ведя народ сквозь хаос пустыни</t>
-  </si>
-  <si>
-    <t>Мухаммед (Магомет) — ок. 570–632. Основатель ислама и глава первого мусульманского государства. Редчайшая фигура, сочетавшая посланническую миссию и практическое стратегическое руководство</t>
-  </si>
-  <si>
-    <t>Натан (Нафан)  — X век до н. э.Пророк при дворе царя Давида. Предвидел воцарение Соломона и строительство Храма. Пример стратегического совета провидца, определявшего государственные решения</t>
-  </si>
-  <si>
-    <t>Наполеон Бонапарт  — 1769–1821.Император Франции и великий полководец. Активно использовал скорость, концентрацию сил и мобильность. Квинт анализирует поход 1812 года как трагедию выбора пути гибели без чёткого плана</t>
-  </si>
-  <si>
-    <t>Нострадамус (Мишель де Нострдам)  — 1503–1566.Французский врач и астролог. Квинт восхищается точностью ряда предсказаний, но делает вывод: Нострадамус — предсказатель, а не пророк.</t>
-  </si>
-  <si>
-    <t>Олдос Хаксли  — 1894–1963. Английский писатель, автор «О дивный новый мир». Предсказал генную инженерию и вмешательство в репродукцию задолго до появления технологий</t>
-  </si>
-  <si>
-    <t>Отто фон Бисмарк — Мастер дипломатической стратегии. Объединил Германию благодаря продуманной политике, союзам и использованию международной обстановки. Пример долгосрочного государственного планирования.</t>
-  </si>
-  <si>
-    <t>Павел I — Уделял внимание реформированию армии и укреплению дисциплины. Стремился повысить эффективность вооружённых сил, что повлияло на дальнейшее развитие военной стратегии России.</t>
-  </si>
-  <si>
-    <t>Пётр I  — Внёс большой вклад в развитие государственной и военной стратегии России. Провёл масштабные реформы армии, флота и управления. Укрепил международное положение России</t>
-  </si>
-  <si>
-    <t>Роберт Ауман  — родился в 1930 году. Израильский математик, нобелевский лауреат. Вывод: в долгосрочных конфликтах выигрывает тот, кто ставит стратегию выше быстрой выгоды</t>
-  </si>
-  <si>
-    <t>Роберт Брюс — Внёс вклад в развитие национальной и военной стратегии Шотландии. Добился независимости страны благодаря грамотному использованию ресурсов и поддержке населения</t>
-  </si>
-  <si>
-    <t>Самсон — ок. XI века до н. э.Последний из великих судей Израилевых. Обладал силой, но был лишён дара видения и стратегического мышления</t>
-  </si>
-  <si>
-    <t>Самуил (Шмуэль) — XI век до н. э.Последний судья и первый крупный пророк Израиля. Путь от провидца до государственного стратега, руководившего военными действиями и помазанием царей.</t>
-  </si>
-  <si>
-    <t>Сергей Королёв — Внёс вклад в развитие научно-технологической стратегии СССР. Реализовал космические программы, позволившие СССР стать лидером космической гонки.</t>
-  </si>
-  <si>
-    <t>Соломон — царствовал ок. 970–931 до н. э. Сын Давида, построил Иерусалимский Храм. Символ того, как сбывшееся стратегическое предвидение воплощается в деяниях следующего поколения.</t>
-  </si>
-  <si>
-    <t>Стив Джобс  — Внёс вклад в развитие инновационной и технологической стратегии. Ставка на качество, дизайн и создание новых рынков. Превратил Apple в крупнейшую технологическую компанию.</t>
-  </si>
-  <si>
-    <t>Султан Мехмет II — Завоеватель Константинополя. Использовал новые технологии, артиллерию и стратегическое планирование. Повлиял на развитие османской стратегии.</t>
-  </si>
-  <si>
-    <t>Сулейман Великолепный  — Внёс вклад в развитие государственной и военной стратегии Османской империи. Достиг максимального могущества благодаря грамотному управлению и дипломатии</t>
-  </si>
-  <si>
-    <t>Тертуллиан — ок. 155–220.Раннехристианский теолог. Квинт цитирует его парадокс «Верую, ибо абсурдно», подчеркивая роль иррационального в принятии стратегических решений.</t>
-  </si>
-  <si>
-    <t>Тьяллинг Купманс  — 1910–1985. Американский экономист, нобелевский лауреат. Предложил сравнивать экономики по оргфункциям. Квинт считает подход широким, но недостаточным для стратегической классификации.</t>
-  </si>
-  <si>
-    <t>Уильям Коэн — Внёс вклад в развитие государственной и оборонной стратегии США. Занимался вопросами национальной безопасности и модернизации вооружённых сил.</t>
-  </si>
-  <si>
-    <t>Фридрих Великий  — Внёс вклад в развитие военной стратегии и управления государством. Реформировал армию Пруссии, уделяя внимание дисциплине, скорости и маневрированию.</t>
-  </si>
-  <si>
-    <t>Хельмут фон Мольтке  — Внёс большой вклад в развитие современной военной стратегии. Развивал идеи оперативного планирования, координации войск и использования железных дорог</t>
-  </si>
-  <si>
-    <t>Царь Давид  — ок. 1035–970 до н. э. Второй царь Израиля. Успешный правитель и воин, но сам пророком не был. Приглашал провидцев в ближний круг, компенсируя отсутствие собственного дара предвидения</t>
-  </si>
-  <si>
-    <t>Царь Саул — правил ок. 1029–1009 до н. э. Первый царь Израиля. Его правление знаменует рубеж разделения функций правителя и пророка, важный этап в генезисе профессии стратега.</t>
-  </si>
-  <si>
-    <t>Чингисхан  — Один из самых успешных стратегов благодаря мобильности армии, дисциплине и управлению территориями. Использовал разведку, психологическое воздействие и неожиданные атаки.</t>
-  </si>
-  <si>
-    <t>Эрик Шмидт  —  Внёс вклад в развитие цифровой стратегии Google. Под его руководством компания расширила направления деятельности и укрепила позиции на мировом рынке.</t>
-  </si>
-  <si>
-    <t>Жюль Верн — 1828–1905.Французский писатель. Пример технического визионера: детально описал подводную лодку «Наутилус» задолго до её появления.</t>
-  </si>
-  <si>
-    <t>Генрих Жомини  — 1779–1869.Генерал и теоретик. Квинт называет его основоположником, создавшим в 1817 году первую в мире теорию стратегии и сделавшим Россию родиной этой дисциплины.</t>
-  </si>
-  <si>
-    <t>15 правил стратегирования В.Л. Квинта
+    <t>К. К. Прахалад</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Теодор Эйро Додж </t>
+  </si>
+  <si>
+    <t>Картинка</t>
+  </si>
+  <si>
+    <t>Создатели</t>
+  </si>
+  <si>
+    <t>Кирилл</t>
+  </si>
+  <si>
+    <t>https://ibb.co/Lz3mT6Jh</t>
+  </si>
+  <si>
+    <t>https://giga.chat/files/public/generated/e36c7924-4bf2-41ca-bf1a-0a49b945dcca</t>
+  </si>
+  <si>
+    <t>Денчик Иванов</t>
+  </si>
+  <si>
+    <t>Владос</t>
+  </si>
+  <si>
+    <t>Создателями телеграм бота "Бот стратег" являются: Пинжин Кирилл и Злобин Владислав
+Напишите в чат "Кирилл" или "Владос" чтобы узнать о каждом подробнее!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  — метод сложения коэффициентов (P=ΣP×Wk), полезный только для оценки крайних значений (самых развитых или самых бедных стран).</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> — метод умножения коэффициентов (P=1000×ΠPkWk), более точный для малых экономик, где единичные инновации существенно влияют на эффективность.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> — нестандартные решения для преимущества</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> — состояние системы</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> — страны, квалифицированные по инициативе МВФ и Всемирного банка как неспособные выплатить свой долг.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> — крупнейшие аудиторские фирмы мира: PricewaterhouseCoopers (PwC), Deloitte Touche, Ernst &amp; Young (EY) и KPMG.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> — представление о будущем состоянии объекта</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> — валовой национальный доход на человека, основа классификации Группы Всемирного банка для кредитных решений</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> — усиление взаимосвязи экономик и рынков</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> — совокупность мировых рынков</t>
+  </si>
+  <si>
+    <t>— подсистема глобального миропорядка, каркас относительно стабильного сотрудничества бизнеса с глобальными, региональными и национальными институтами. Cтимулирует преимущественно эволюционное развитие глобального рыночного пространства.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> — повторяющиеся связи развития.</t>
+  </si>
+  <si>
+    <t>— время даёт преимущество</t>
+  </si>
+  <si>
+    <t>— реализуются только обеспеченные направления</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> — первый и главный закон стратегии по Квинту; фактор времени является детерминирующим в стратегии</t>
+  </si>
+  <si>
+    <t>— глобальные, национальные, региональные, корпоративные, индивидуальные</t>
+  </si>
+  <si>
+    <t>— основа рейтинговых систем и индексов, на которых строятся классификационные системы стран и регионов</t>
+  </si>
+  <si>
+    <t>— один из пяти показателей синтезированного странового рейтинга Квинта (относительная значимость 1,0)</t>
+  </si>
+  <si>
+    <t>— один из пяти показателей синтезированного рейтинга (относительная значимость 0,7)</t>
+  </si>
+  <si>
+    <t>— показатель, разработанный Квинтом на основе базы данных ЮНИДО для синтезированного рейтинга стран</t>
+  </si>
+  <si>
+    <t>— источник преимуществ</t>
+  </si>
+  <si>
+    <t>— объединение всех уровней</t>
+  </si>
+  <si>
+    <t>— присутствие в стране международных банков, страховых компаний, аудиторов и юридических фирм, необходимое для входа на иностранный рынок</t>
+  </si>
+  <si>
+    <t>— ориентация на прошлое</t>
+  </si>
+  <si>
+    <t>— группы, составляющие классификационную систему; внутри категорий также применяется рейтинговая система</t>
+  </si>
+  <si>
+    <t>— факторы превосходства</t>
+  </si>
+  <si>
+    <t>— доминирующая в России конца 2010-х модель, существенно отличающаяся как от государственного капитализма, так и от коммунизма</t>
+  </si>
+  <si>
+    <t>— одна из трёх дополнительных категорий ООН, отражающая географическую специфику развития.</t>
+  </si>
+  <si>
+    <t>— псевдопредвидение в виде пророчеств, прорицаний, «откровений» и гаданий</t>
+  </si>
+  <si>
+    <t>— фундаментальная цель и смысл существования объекта</t>
+  </si>
+  <si>
+    <t>— система характеристик и внутренняя структура государства: политические, экономические, финансовые, технологические индикаторы, культурная и религиозная среда</t>
+  </si>
+  <si>
+    <t>— слово из Торы, ассоциирующееся с мощным и точным видением таких великих лидеров, как Моисей и Самуил</t>
+  </si>
+  <si>
+    <t>— слово из Торы, отображающее пророка-провидца без лидерских качеств.</t>
+  </si>
+  <si>
+    <t>— категория ООН с 1971 года. Критерии: низкий доход (ВНД на душу населения), слабый человеческий капитал и экономическая уязвимость.</t>
+  </si>
+  <si>
+    <t>— быстро формирующаяся технология, которая может стать основой беспрецедентно больших систем стратегических компетенций.</t>
+  </si>
+  <si>
+    <t>— информационно-познавательный аспект опережающего отражения как свойства высших форм материи.</t>
+  </si>
+  <si>
+    <t>— категория МВФ: Гонконг, Корея, Сингапур и Тайвань.</t>
+  </si>
+  <si>
+    <t>— интуитивное (связанное с подсознанием), обыденное (по народным приметам) и мантическое (пророчества, гадания) предвидение.</t>
+  </si>
+  <si>
+    <t>— категория, появившаяся благодаря европейским открытиям; несистематизированные территории, ставшие затем странами и регионами.</t>
+  </si>
+  <si>
+    <t>— сценарии будущего, в которых сталкиваются или кооперируют ценностные ориентиры, интересы и приоритеты субъектов стратегирования.</t>
+  </si>
+  <si>
+    <t>— концепция Даниэля Канемана: «Мы думаем о нашем будущем как об ожидаемых воспоминаниях».</t>
+  </si>
+  <si>
+    <t>— термин древних греков для описания известного им мира с центром в Элладе; одна из первых попыток системного понимания мира</t>
+  </si>
+  <si>
+    <t>— метод, используемый в рамках методологии стратегирования научной школы Квинта. Расшифровывается как Opportunities (Возможности), Threats (Угрозы), Strengths (Сильные стороны) и Weaknesses (Слабые стороны).</t>
+  </si>
+  <si>
+    <t>— разработка действий.</t>
+  </si>
+  <si>
+    <t>— интеграция стратегии и тактики</t>
+  </si>
+  <si>
+    <t>— риск экспроприации, национализации и повреждения частной собственности иностранных лиц в странах с гражданскими волнениями.</t>
+  </si>
+  <si>
+    <t>— способность понимать будущее.</t>
+  </si>
+  <si>
+    <t>— результат понимания будущего.</t>
+  </si>
+  <si>
+    <t>— сложное предвосхищение, вид интеллектуальной деятельности человека на основе личного опыта</t>
+  </si>
+  <si>
+    <t>— простое предвосхищение, свойственное любому организму; одна из форм конкретизации предвидения.</t>
+  </si>
+  <si>
+    <t>— ключевые направления развития</t>
+  </si>
+  <si>
+    <t>— категория МВФ с 1997 года, объединяющая развитые страны и самые зрелые СФР (Южная Корея, Сингапур, Израиль)</t>
+  </si>
+  <si>
+    <t>— научное определение будущего.</t>
+  </si>
+  <si>
+    <t>— устаревшая категория МВФ, заменённая на «продвинутые экономики» из-за сокращения занятости в индустриальном производстве.</t>
+  </si>
+  <si>
+    <t>— интуитивное предвидение.</t>
+  </si>
+  <si>
+    <t>— люди, «видевшие» картины будущего. Их главная ценность для стратегов — традиция связывать пророчества со шкалой времени</t>
+  </si>
+  <si>
+    <t>— редчайшее сочетание способностей провидца с лидерскими качествами практика (Моисей, Мухаммед)</t>
+  </si>
+  <si>
+    <t>— инвестиции компаний в зарубежные экономики. Новый тренд: ПИИ из СФР направляются в наукоёмкие отрасли развитых стран.</t>
+  </si>
+  <si>
+    <t>— решения, ведущие к далёкому будущему, всегда принимаемые на грани сознания и подсознания, рационального и иррационального.</t>
+  </si>
+  <si>
+    <t>— позиции, присваиваемые странам и регионам в рейтингах, индексах и внутри классификационных категорий.</t>
+  </si>
+  <si>
+    <t>— высшая стадия СФР (Южная Корея, Сингапур, Израиль, Гонконг, Испания, Португалия, Греция). Стратегически конкурируют с развитыми странами.</t>
+  </si>
+  <si>
+    <t>— средства для реализации стратегии.</t>
+  </si>
+  <si>
+    <t>— вероятность потерь</t>
+  </si>
+  <si>
+    <t>— рейтинг технологического, экономического и социального развития стран на основе пяти индикаторов.</t>
+  </si>
+  <si>
+    <t>— классификационная категория, ядром которой стала цивилизация ойкумены к концу XV века.</t>
+  </si>
+  <si>
+    <t>— мудрый дисциплинированный и оптимистичный профессионал, имеющий стратегическое мышление, видение будущего и интуицию, подкрепленную методологией стратегирования.</t>
+  </si>
+  <si>
+    <t>— мудрые дисциплинированные и оптимистичные профессионалы, имеющие стратегическое мышление, видение будущего и интуицию, подкрепленную методологией стратегирования.</t>
+  </si>
+  <si>
+    <t>— система официальных взглядов и положений, устанавливающая направления долгосрочного развития объекта стратегирования.</t>
+  </si>
+  <si>
+    <t>— способность принимать долгосрочные решения.</t>
+  </si>
+  <si>
+    <t>— процесс формирования и функционирования системы стратегического управления, обеспечивающей разработку и долгосрочную реализацию стратегии, её доктрины, в соответствии с содержащимися в них конкурентными преимуществами, приоритетами, целями и задачами.</t>
+  </si>
+  <si>
+    <t>— контроль и корректировка стратегии.</t>
+  </si>
+  <si>
+    <t>— один из альтернативных вариантов реализации стратегии. Как правило, разрабатывается не менее трёх сценариев, которые отличаются соотношением риска, асимметричности и общественно-экономической эффективности.</t>
+  </si>
+  <si>
+    <t>— система поиска, формулирования и развития доктрины, обеспечивающей долгосрочный успех</t>
+  </si>
+  <si>
+    <t>— концепция профессора Прахалада о заработке на беднейших слоях за счёт продажи малых упаковок товаров при высоком обороте.</t>
+  </si>
+  <si>
+    <t>— процесс разработки, реализации и обновления стратегии.</t>
+  </si>
+  <si>
+    <t>— одна из трёх дополнительных категорий ООН, отражающая географические ограничения развития.</t>
+  </si>
+  <si>
+    <t>— категория восточноевропейских стран и СНГ. Квинт критикует её: логически все СФР и развивающиеся страны находятся в переходной стадии</t>
+  </si>
+  <si>
+    <t>— переходная стадия от развивающихся к СФР (Тунис, Монголия, Мадагаскар, Буркина Фасо).</t>
+  </si>
+  <si>
+    <t>— сценарии, в которых сталкиваются или кооперируют ценностные ориентиры, интересы и приоритеты субъектов стратегирования.</t>
+  </si>
+  <si>
+    <t>— система текущих действий для реализации стратегии.</t>
+  </si>
+  <si>
+    <t>— теория систематизации и иерархических сфер действительности и знаний, созданная Карлом Линнеем в 1813 году.</t>
+  </si>
+  <si>
+    <t>— теория Канемана и Тверски о принятии решений в условиях высоких рисков, исключительно важная для стратегирования.</t>
+  </si>
+  <si>
+    <t>— термин, ассоциировавшийся с бедными неразвитыми странами. Большинство из них отклонили принципы свободного конкурентного рынка и стали беднее.</t>
+  </si>
+  <si>
+    <t>— устойчивые направления развития.</t>
+  </si>
+  <si>
+    <t>— негативные факторы.</t>
+  </si>
+  <si>
+    <t>— ключ к стратегическому преимуществу.</t>
+  </si>
+  <si>
+    <t>— главная стратегическая угроза для России и ещё более 20 стран в XXI веке; депопуляция, игнорируемая в большинстве стратегических документов.</t>
+  </si>
+  <si>
+    <t>— неопределённость среды.</t>
+  </si>
+  <si>
+    <t>— конкретные ориентиры, размещённые во времени.</t>
+  </si>
+  <si>
+    <t>— показатель стратегического уровня развития. Северные страны обеспечивают наиболее устойчивую окружающую среду; страны с диктатурами замыкают рейтинг.</t>
+  </si>
+  <si>
+    <t>— стратегия Китая «Пять в одном»: посадка деревьев на четверти территории, восстановление 30% береговой линии, сокращение потребления угля на 40%.</t>
+  </si>
+  <si>
+    <t>— Первый библейский патриарх и пророк. Отнесён к проактивным лидерам, чьё стратегическое предвидение направляло не только семью, но и целые поколения. Пример провидца, который действует, а не только созерцает.</t>
+  </si>
+  <si>
+    <t>— Период: XIII век до н. э. Старший брат Моисея и Первый первосвященник. Квинт проводит границу: Аарон —  Моисей — пророк и стратег. Духовный сан и стратегическое лидерство — разные.</t>
+  </si>
+  <si>
+    <t>— Внёс вклад в развитие государственной и военной стратегии Руси. Прославился грамотным использованием местности, дипломатией и способностью принимать стратегические решения в сложных условиях. Его победы и политика помогли сохранить независимость русских земель.</t>
+  </si>
+  <si>
+    <t>— Один из величайших русских полководцев. Внёс вклад в развитие военной стратегии благодаря мобильности армии, быстроте принятия решений и нестандартным действиям. Его принципы подготовки войск и дисциплины стали важной частью военного стратегирования.</t>
+  </si>
+  <si>
+    <t>— 1937–1996.Психолог, соавтор Канемана. Их исследования ошибочных суждений и восприятия риска в условиях неопределённости Квинт считает критически важными для теории стратегирования.</t>
+  </si>
+  <si>
+    <t>— стратег и основатель Империи Тимуридов. Владимир Квинт посвятил его лидерству отдельную книгу. Главный принцип: успех государства зависит от привлечения талантливых людей («предприимчивых, мужественных и благоразумных»), ценность которых превышает ценность тысяч безвольных работников</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> — Герцог Веллингтон. Внёс вклад в развитие военной стратегии благодаря успешному противостоянию армии Наполеона. Уделял внимание дисциплине, подготовке армии и грамотному использованию местности.</t>
+  </si>
+  <si>
+    <t>— современный исследователь (XX–XXI вв.).Специалист по политэкономии Восточной Азии. Квинт цитирует его работы о связи авторитарной олигархии и экономической структуры стран ЮВА.</t>
+  </si>
+  <si>
+    <t>— ключевой стратег цифровой эпохи. Развивал программное обеспечение и сделал ставку на массовое распространение персональных компьютеров. Его решения сыграли большую роль в развитии мировой IT-индустрии</t>
+  </si>
+  <si>
+    <t>— Один из крупнейших полководцев XX века. Внёс вклад в развитие стратегического управления армией во время Второй мировой войны. Его решения в крупнейших операциях повлияли на советскую и мировую военную стратегию</t>
+  </si>
+  <si>
+    <t>— Один из великих библейских пророков. Его видения охватывали века. Квинт подчёркивает уникальную глубину его предсказаний, недоступную даже современному планированию. Эталон предвидения.</t>
+  </si>
+  <si>
+    <t>— Современный американский историк экономики (XX–XXI вв.).Исследовал античные модели: свободное предпринимательство в Древней Греции и дворцовая монополия в Египте как два изначальных стратегических пути экономики.</t>
+  </si>
+  <si>
+    <t>— Внёс вклад в развитие цифровой стратегии и интернет-торговли. Создал платформу Alibaba, сделав ставку на развитие онлайн-бизнеса и глобальной электронной коммерции.</t>
+  </si>
+  <si>
+    <t>— Внёс вклад в развитие корпоративной стратегии. Руководя General Electric, внедрял инновации, оптимизацию процессов и долгосрочное планирование. Пример эффективного стратегического менеджмента.</t>
+  </si>
+  <si>
+    <t>— Внёс вклад в развитие современной стратегической теории. Разработал концепцию OODA Loop (быстрый анализ ситуации и принятие решений). Идеи используются в военной стратегии, бизнесе и управлении.</t>
+  </si>
+  <si>
+    <t>— 1928–2005. Историк экономики, коллега Купманса. Предложил подход к сравнению экономических систем по организационным функциям, который Квинт рассматривает как важный шаг, но с ограничениями.</t>
+  </si>
+  <si>
+    <t>— 1667–1745.Англо-ирландский писатель. Квинт отмечает его предвидение: за полтора века до открытия Свифт описал два спутника Марса и их орбитальные параметры, почти совпавшие с реальностью.</t>
+  </si>
+  <si>
+    <t>— Внёс огромный вклад в развитие экономической стратегии Китая. Провёл реформы, открывшие страну для мирового рынка. Благодаря этому Китай начал быстрое экономическое развитие</t>
+  </si>
+  <si>
+    <t>— 1927–2015. Советский и российский учёный, социолог и футуролог. Представитель отечественной школы, начавшей осмысливать процессы научного и ненаучного познания будущего</t>
+  </si>
+  <si>
+    <t>— ок. XIII–XII века до н. э. Преемник Моисея, завоеватель Ханаана. Квинт описывает его как образец военного стратега и полководца, а не пророка.</t>
+  </si>
+  <si>
+    <t>— Известен долгосрочным стратегическим видением и инновационным подходом. Развивает проекты в области космоса, электромобилей и ИИ. Стратегии основаны на высоких рисках и стремлении изменить будущее</t>
+  </si>
+  <si>
+    <t>— Внёс значительный вклад в развитие византийской военной стратегии. Систематизировал знания о ведении войны и организации армии. Его труды стали основой для многих военных трактатов Средневековья.</t>
+  </si>
+  <si>
+    <t>— ок. XIII–XII века до н. э. (мифология).Троянская царевна с даром точного предвидения, но обречённая на то, что ей никто не верил. Символ трагедии провидца, лишённого стратегического влияния.</t>
+  </si>
+  <si>
+    <t>— Один из главных теоретиков стратегии. В работе «О войне» рассматривал войну как продолжение политики. Его идеи оказали огромное влияние на современную военную и государственную стратегию</t>
+  </si>
+  <si>
+    <t>— Ведущий специалист в области бизнес-стратегии. Изучал глобализацию и конкурентные преимущества. Его идеи повлияли на современное корпоративное стратегирование</t>
+  </si>
+  <si>
+    <t>— Сыграл важную роль в восстановлении Германии после Второй мировой войны. Использовал долгосрочное стратегическое планирование для укрепления экономики и международных отношений</t>
+  </si>
+  <si>
+    <t>— Внёс вклад в развитие экономической и транспортной стратегии. Создал крупную транспортную империю, используя долгосрочное планирование и контроль инфраструктуры</t>
+  </si>
+  <si>
+    <t>— Развивал стратегические и тактические принципы Византии. Уделял внимание анализу военных действий и изучению опыта прошлых войн. Сохранил византийскую школу стратегирования</t>
+  </si>
+  <si>
+    <t>— правил 161–180. Римский император, философ-стоик. Уникальный пример сочетания императора, мудреца и стратега-провидца, не допускавшего ошибок от конфликта этих ролей.</t>
+  </si>
+  <si>
+    <t>— 1927–1997.Американский писатель, автор романа «Киборг». Предвосхитил появление бионических протезов, управляемых силой мысли</t>
+  </si>
+  <si>
+    <t>— Американский экономист, профессор Стэнфорда. Автор методики рейтингования стран середины XX века. Квинт критикует его алгоритм сложения показателей за неточность.</t>
+  </si>
+  <si>
+    <t>— Японский стратег и мастер боевых искусств. Разработал подход, основанный на дисциплине, психологическом превосходстве и анализе противника. Автор «Книги пяти колец».</t>
+  </si>
+  <si>
+    <t>—  приблизительно XIII век до н. э.Библейский пророк и вождь. Квинт считает его величайшим провидцем-стратегом, сочетавшим дар предвидения и практическое лидерство, ведя народ сквозь хаос пустыни</t>
+  </si>
+  <si>
+    <t>— ок. 570–632. Основатель ислама и глава первого мусульманского государства. Редчайшая фигура, сочетавшая посланническую миссию и практическое стратегическое руководство</t>
+  </si>
+  <si>
+    <t>— X век до н. э.Пророк при дворе царя Давида. Предвидел воцарение Соломона и строительство Храма. Пример стратегического совета провидца, определявшего государственные решения</t>
+  </si>
+  <si>
+    <t>— 1769–1821.Император Франции и великий полководец. Активно использовал скорость, концентрацию сил и мобильность. Квинт анализирует поход 1812 года как трагедию выбора пути гибели без чёткого плана</t>
+  </si>
+  <si>
+    <t>— 1503–1566.Французский врач и астролог. Квинт восхищается точностью ряда предсказаний, но делает вывод: Нострадамус — предсказатель, а не пророк.</t>
+  </si>
+  <si>
+    <t>— 1894–1963. Английский писатель, автор «О дивный новый мир». Предсказал генную инженерию и вмешательство в репродукцию задолго до появления технологий</t>
+  </si>
+  <si>
+    <t>— Мастер дипломатической стратегии. Объединил Германию благодаря продуманной политике, союзам и использованию международной обстановки. Пример долгосрочного государственного планирования.</t>
+  </si>
+  <si>
+    <t>— Уделял внимание реформированию армии и укреплению дисциплины. Стремился повысить эффективность вооружённых сил, что повлияло на дальнейшее развитие военной стратегии России.</t>
+  </si>
+  <si>
+    <t>— Внёс большой вклад в развитие государственной и военной стратегии России. Провёл масштабные реформы армии, флота и управления. Укрепил международное положение России</t>
+  </si>
+  <si>
+    <t>— родился в 1930 году. Израильский математик, нобелевский лауреат. Вывод: в долгосрочных конфликтах выигрывает тот, кто ставит стратегию выше быстрой выгоды</t>
+  </si>
+  <si>
+    <t>— Внёс вклад в развитие национальной и военной стратегии Шотландии. Добился независимости страны благодаря грамотному использованию ресурсов и поддержке населения</t>
+  </si>
+  <si>
+    <t>— 1941–2010.Профессор Мичиганского университета. Автор концепции «Дно пирамиды» (заработок на беднейших слоях за счёт малого товара и высокого оборота).</t>
+  </si>
+  <si>
+    <t>— ок. XI века до н. э.Последний из великих судей Израилевых. Обладал силой, но был лишён дара видения и стратегического мышления</t>
+  </si>
+  <si>
+    <t>— XI век до н. э.Последний судья и первый крупный пророк Израиля. Путь от провидца до государственного стратега, руководившего военными действиями и помазанием царей.</t>
+  </si>
+  <si>
+    <t>— Внёс вклад в развитие научно-технологической стратегии СССР. Реализовал космические программы, позволившие СССР стать лидером космической гонки.</t>
+  </si>
+  <si>
+    <t>— царствовал ок. 970–931 до н. э. Сын Давида, построил Иерусалимский Храм. Символ того, как сбывшееся стратегическое предвидение воплощается в деяниях следующего поколения.</t>
+  </si>
+  <si>
+    <t>— Внёс вклад в развитие инновационной и технологической стратегии. Ставка на качество, дизайн и создание новых рынков. Превратил Apple в крупнейшую технологическую компанию.</t>
+  </si>
+  <si>
+    <t>— Завоеватель Константинополя. Использовал новые технологии, артиллерию и стратегическое планирование. Повлиял на развитие османской стратегии.</t>
+  </si>
+  <si>
+    <t>— Внёс вклад в развитие государственной и военной стратегии Османской империи. Достиг максимального могущества благодаря грамотному управлению и дипломатии</t>
+  </si>
+  <si>
+    <t>— ок. 155–220.Раннехристианский теолог. Квинт цитирует его парадокс «Верую, ибо абсурдно», подчеркивая роль иррационального в принятии стратегических решений.</t>
+  </si>
+  <si>
+    <t>— Внёс вклад в развитие военной истории и стратегической аналитики. Изучал деятельность великих полководцев, помогая развитию стратегического образования.</t>
+  </si>
+  <si>
+    <t>— 1910–1985. Американский экономист, нобелевский лауреат. Предложил сравнивать экономики по оргфункциям. Квинт считает подход широким, но недостаточным для стратегической классификации.</t>
+  </si>
+  <si>
+    <t>— Внёс вклад в развитие государственной и оборонной стратегии США. Занимался вопросами национальной безопасности и модернизации вооружённых сил.</t>
+  </si>
+  <si>
+    <t>— Внёс вклад в развитие военной стратегии и управления государством. Реформировал армию Пруссии, уделяя внимание дисциплине, скорости и маневрированию.</t>
+  </si>
+  <si>
+    <t>— Внёс большой вклад в развитие современной военной стратегии. Развивал идеи оперативного планирования, координации войск и использования железных дорог</t>
+  </si>
+  <si>
+    <t>— ок. 1035–970 до н. э. Второй царь Израиля. Успешный правитель и воин, но сам пророком не был. Приглашал провидцев в ближний круг, компенсируя отсутствие собственного дара предвидения</t>
+  </si>
+  <si>
+    <t>— правил ок. 1029–1009 до н. э. Первый царь Израиля. Его правление знаменует рубеж разделения функций правителя и пророка, важный этап в генезисе профессии стратега.</t>
+  </si>
+  <si>
+    <t>— Один из самых успешных стратегов благодаря мобильности армии, дисциплине и управлению территориями. Использовал разведку, психологическое воздействие и неожиданные атаки.</t>
+  </si>
+  <si>
+    <t>—  Внёс вклад в развитие цифровой стратегии Google. Под его руководством компания расширила направления деятельности и укрепила позиции на мировом рынке.</t>
+  </si>
+  <si>
+    <t>— 1828–1905.Французский писатель. Пример технического визионера: детально описал подводную лодку «Наутилус» задолго до её появления.</t>
+  </si>
+  <si>
+    <t>— 1779–1869.Генерал и теоретик. Квинт называет его основоположником, создавшим в 1817 году первую в мире теорию стратегии и сделавшим Россию родиной этой дисциплины.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
 1. В стратегии нельзя полагаться только на здравый смысл
 2. В стратегии мнение большинства обычно ошибочно
 3. Стратегически настоящее — это уже прошлое
@@ -981,242 +1012,205 @@
 15. Стратеги должны выявлять и ориентироваться на истинные потребности организации, а не на желания руководителей</t>
   </si>
   <si>
-    <t>https://pravoslavie.wiki/prorok-avraam-praroditel-narodov.html</t>
-  </si>
-  <si>
-    <t>https://my.tretyakov.ru/app/masterpiece/47834</t>
-  </si>
-  <si>
-    <t>https://rg.ru/2020/10/06/pochemu-dlia-nas-segodnia-vazhen-aleksandr-nevskij.html</t>
-  </si>
-  <si>
-    <t>https://klincollege.ru/novosti/velikie-lyudi-rossijskoj-istorii.-aleksandr-suvorov/</t>
-  </si>
-  <si>
-    <t>https://www.psygazeta.ru/rubriki/psikhologicheskij-kalendar/4969-5-faktov-ob-amose-tverski.html</t>
-  </si>
-  <si>
-    <t>https://novotours.uz/ru/about-uzbekistan/izvestnye-lyudi-uzbekistana/amir_temur.html/</t>
-  </si>
-  <si>
-    <t>https://ru.wikipedia.org/wiki/%D0%92%D0%B5%D0%BB%D0%BB%D0%B8%D0%BD%D0%B3%D1%82%D0%BE%D0%BD,_%D0%90%D1%80%D1%82%D1%83%D1%80_%D0%A3%D1%8D%D0%BB%D1%81%D0%BB%D0%B8</t>
-  </si>
-  <si>
-    <t>https://www.tni.org/en/profile/barry-k-gills</t>
-  </si>
-  <si>
-    <t>https://ru.wikipedia.org/wiki/%D0%93%D0%B5%D0%B9%D1%82%D1%81,_%D0%91%D0%B8%D0%BB%D0%BB</t>
-  </si>
-  <si>
-    <t>https://snob.ru/news/121217/</t>
-  </si>
-  <si>
-    <t>https://virtual.uspu.ru/znamenatelnye-daty-v-istorii-rossii/zhukov-georgij-konstantinovich-1-dekabrya-1896-18-iyunya-1974</t>
-  </si>
-  <si>
-    <t>https://history.ru/read/biographies/daniil-alieksandrovich-moskovskii</t>
-  </si>
-  <si>
-    <t>https://www.wipo.int/ru/web/director-general/daren-tang/cv</t>
-  </si>
-  <si>
-    <t>https://ru.wikipedia.org/wiki/%D0%94%D0%B6%D0%B5%D0%BA_%D0%9C%D0%B0</t>
-  </si>
-  <si>
-    <t>https://ru.wikipedia.org/wiki/%D0%A3%D1%8D%D0%BB%D1%87,_%D0%94%D0%B6%D0%B5%D0%BA</t>
-  </si>
-  <si>
-    <t>https://marketer.ua/ru/history-of-the-f-16-how-the-mad-major-and-like-minded-people-created-a-revolutionary-fighter/</t>
-  </si>
-  <si>
-    <t>https://www.irwincollier.com/yale-meet-an-assistant-professor-of-economics-montias-1960/</t>
-  </si>
-  <si>
-    <t>https://historia.nationalgeographic.com.es/a/jonathan-swift-autor-los-viajes-gulliver-y-mayor-critico-ser-humano_15743</t>
-  </si>
-  <si>
-    <t>https://ria.ru/20140822/1020737967.html</t>
-  </si>
-  <si>
-    <t>https://habr.com/ru/articles/388977/</t>
-  </si>
-  <si>
-    <t>https://www.icon-art.info/detail.php?det_id=5573</t>
-  </si>
-  <si>
-    <t>https://ru.wikipedia.org/wiki/%D0%9C%D0%B0%D1%81%D0%BA,_%D0%98%D0%BB%D0%BE%D0%BD</t>
-  </si>
-  <si>
-    <t>https://azbyka.ru/days/sv-mavrikij-apamejskij</t>
-  </si>
-  <si>
-    <t>https://ru.ruwiki.ru/wiki/%D0%9A%D0%B0%D1%81%D1%81%D0%B0%D0%BD%D0%B4%D1%80%D0%B0</t>
-  </si>
-  <si>
-    <t>https://ru.wikipedia.org/wiki/%D0%A4%D0%B0%D0%B9%D0%BB:Carl_von_Clausewitz.PNG</t>
-  </si>
-  <si>
-    <t>https://alpinabook.ru/authors/omae-kenichi/?srsltid=AYCX9vJPkSutnBw2zwv7RvpqSyR55A5kufDT1nv20y5i-hF-bSUCJJFN</t>
-  </si>
-  <si>
-    <t>https://ru.wikipedia.org/wiki/%D0%90%D0%B4%D0%B5%D0%BD%D0%B0%D1%83%D1%8D%D1%80,_%D0%9A%D0%BE%D0%BD%D1%80%D0%B0%D0%B4</t>
-  </si>
-  <si>
-    <t>https://ru.wikipedia.org/wiki/%D0%92%D0%B0%D0%BD%D0%B4%D0%B5%D1%80%D0%B1%D0%B8%D0%BB%D1%8C%D1%82,_%D0%9A%D0%BE%D1%80%D0%BD%D0%B5%D0%BB%D0%B8%D1%83%D1%81</t>
-  </si>
-  <si>
-    <t>https://rus.team/people/lev-vi-filosof</t>
-  </si>
-  <si>
-    <t>https://biographe.ru/politiki/mark-avreliy/</t>
-  </si>
-  <si>
-    <t>https://en.wikipedia.org/wiki/Martin_Caidin</t>
-  </si>
-  <si>
-    <t>https://www.shogunclub.ru/faktyi-o-miyamoto-musasi</t>
-  </si>
-  <si>
-    <t>https://my.tretyakov.ru/app/masterpiece/47839</t>
-  </si>
-  <si>
-    <t>https://www.asekose.am/ru/post/ukaz-proroka-muxammeda-pro-armanskiy-narod</t>
-  </si>
-  <si>
-    <t>https://azbyka.ru/days/sv-nafan</t>
-  </si>
-  <si>
-    <t>https://udm.wikipedia.org/wiki/%D0%9D%D0%B0%D0%BF%D0%BE%D0%BB%D0%B5%D0%BE%D0%BD</t>
-  </si>
-  <si>
-    <t>https://www.kommersant.ru/doc/3826527</t>
-  </si>
-  <si>
-    <t>https://ru.wikipedia.org/wiki/%D0%A5%D0%B0%D0%BA%D1%81%D0%BB%D0%B8,_%D0%9E%D0%BB%D0%B4%D0%BE%D1%81</t>
-  </si>
-  <si>
-    <t>https://ru.wikipedia.org/wiki/%D0%91%D0%B8%D1%81%D0%BC%D0%B0%D1%80%D0%BA,_%D0%9E%D1%82%D1%82%D0%BE_%D1%84%D0%BE%D0%BD</t>
-  </si>
-  <si>
-    <t>https://ru.wikipedia.org/wiki/%D0%9F%D0%B0%D0%B2%D0%B5%D0%BB_I</t>
-  </si>
-  <si>
-    <t>https://ru.wikipedia.org/wiki/%D0%9F%D1%91%D1%82%D1%80_I</t>
-  </si>
-  <si>
-    <t>https://www.peoples.ru/science/mathematics/robert_aumann/</t>
-  </si>
-  <si>
-    <t>https://ru.wikipedia.org/wiki/%D0%A0%D0%BE%D0%B1%D0%B5%D1%80%D1%82_I_%28%D0%BA%D0%BE%D1%80%D0%BE%D0%BB%D1%8C_%D0%A8%D0%BE%D1%82%D0%BB%D0%B0%D0%BD%D0%B4%D0%B8%D0%B8%29</t>
-  </si>
-  <si>
-    <t>https://www.olbuss.ru/avtory/prakhalad-k-k</t>
-  </si>
-  <si>
-    <t>К. К. Прахалад — 1941–2010.Профессор Мичиганского университета. Автор концепции «Дно пирамиды» (заработок на беднейших слоях за счёт малого товара и высокого оборота).</t>
-  </si>
-  <si>
-    <t>К. К. Прахалад</t>
-  </si>
-  <si>
-    <t>https://ru.wikipedia.org/wiki/%D0%A1%D0%B0%D0%BC%D1%81%D0%BE%D0%BD</t>
-  </si>
-  <si>
-    <t>https://ru.wikipedia.org/wiki/%D0%A1%D0%B0%D0%BC%D1%83%D0%B8%D0%BB</t>
-  </si>
-  <si>
-    <t>https://ru.wikipedia.org/wiki/%D0%9A%D0%BE%D1%80%D0%BE%D0%BB%D1%91%D0%B2,_%D0%A1%D0%B5%D1%80%D0%B3%D0%B5%D0%B9_%D0%9F%D0%B0%D0%B2%D0%BB%D0%BE%D0%B2%D0%B8%D1%87</t>
-  </si>
-  <si>
-    <t>https://ru.wikipedia.org/wiki/%D0%A1%D0%BE%D0%BB%D0%BE%D0%BC%D0%BE%D0%BD</t>
-  </si>
-  <si>
-    <t>https://adebiportal.kz/ru/authors/view/114</t>
-  </si>
-  <si>
-    <t>https://ru.wikipedia.org/wiki/%D0%9C%D0%B5%D1%85%D0%BC%D0%B5%D0%B4_II</t>
-  </si>
-  <si>
-    <t>https://interesnyefakty.org/sulejman-velikolepnyj/</t>
-  </si>
-  <si>
-    <t>https://ru.wikipedia.org/wiki/%D0%A2%D0%B5%D1%80%D1%82%D1%83%D0%BB%D0%BB%D0%B8%D0%B0%D0%BD</t>
-  </si>
-  <si>
-    <t>Теодор Эйро Додж  — Внёс вклад в развитие военной истории и стратегической аналитики. Изучал деятельность великих полководцев, помогая развитию стратегического образования.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Теодор Эйро Додж </t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/commons/thumb/2/29/Theodore_Ayrault_Dodge_1842%E2%80%931909.jpg/960px-Theodore_Ayrault_Dodge_1842%E2%80%931909.jpg</t>
-  </si>
-  <si>
-    <t>https://avatars.mds.yandex.net/i?id=0006b29a7d8254ae5ba2d6efebab01ae_l-5220706-images-thumbs&amp;n=13</t>
-  </si>
-  <si>
-    <t>https://www.mediaite.com/wp-content/uploads/2019/10/Former-defense-secretary-William-Cohen.jpg</t>
-  </si>
-  <si>
-    <t>https://avatars.mds.yandex.net/i?id=dba8ee2fecc024d669755d4d2ad969f0_l-5167251-images-thumbs&amp;n=13</t>
-  </si>
-  <si>
-    <t>https://veche-info.ru/wp-content/uploads/2023/12/helmuth_karl_bernhard_graf_von_moltke.jpg</t>
-  </si>
-  <si>
-    <t>https://www.krestilnoe.ru/userfiles/ufiles/Zhitie_svyatogo_carya_i_proroka_davida_-_pravoslavnye_molitvy_1.jpg</t>
-  </si>
-  <si>
-    <t>https://avatars.mds.yandex.net/i?id=318f33ae800e6cc51249a26949013cd1_l-5331946-images-thumbs&amp;n=13</t>
-  </si>
-  <si>
-    <t>https://istorik.ru/_next/image?url=%2Fimages%2Fpersons%2Fchingiskhan.jpg&amp;w=3840&amp;q=75</t>
-  </si>
-  <si>
-    <t>https://avatars.mds.yandex.net/i?id=6e0697160b95366e8be584048e53b3bafd2f9542-12421307-images-thumbs&amp;n=13</t>
-  </si>
-  <si>
-    <t>https://mezgore-lib.ru/wp-content/uploads/2024/02/42432-2-768x937-1.jpg</t>
-  </si>
-  <si>
-    <t>https://urss.ru/images/add_ru/$24176$_150831.jpg</t>
-  </si>
-  <si>
-    <t>Картинка</t>
-  </si>
-  <si>
-    <t>Создатели</t>
-  </si>
-  <si>
-    <t>Кирилл</t>
-  </si>
-  <si>
-    <t>Пинжин Кирилл - главный разработчик проекта. Отвечал за написание кода в Python, интеграцию базы данных Excel, работу с GitHub и развёртывание бота на сервере Bothost.</t>
-  </si>
-  <si>
-    <t>Злобин Влад - контент-менеджер и аналитик прооекта. Отвечал за сбор материалов, изучение трудов академика В.Квинта, структурирование терминов и ведение базы данных в Excel.</t>
-  </si>
-  <si>
-    <t>https://ibb.co/Lz3mT6Jh</t>
-  </si>
-  <si>
-    <t>https://giga.chat/files/public/generated/e36c7924-4bf2-41ca-bf1a-0a49b945dcca</t>
-  </si>
-  <si>
-    <t>Денчик Иванов</t>
-  </si>
-  <si>
-    <t>Денчик - кент Кирюхи Пинжина</t>
-  </si>
-  <si>
-    <t>https://ibb.co/mV05T4ZZ</t>
-  </si>
-  <si>
-    <t>Владос</t>
-  </si>
-  <si>
-    <t>Создателями телеграм бота "Бот стратег" являются: Пинжин Кирилл и Злобин Владислав
-Напишите в чат "Кирилл" или "Владос" чтобы узнать о каждом подробнее!</t>
+    <t>— Создатель Общей теории стратегии и теории глобального формирующегося рынка. Под его руководством разработаны стратегии развития Санкт-Петербурга и Кузбасса до 2035 года. Иностранный член РАН, лауреат Госпремии Узбекистана. В апреле 2026 года получил звание почетного профессора Шанхайского университета, известен своим крылатым выражением: «Стратегия есть философия успеха».Он активно продвигает идею о том, что стратегическое мышление необходимо не только государствам и корпорациям, но и каждому человеку для построения успешной и осмысленной жизни.</t>
+  </si>
+  <si>
+    <t>Дарел Тай Энген</t>
+  </si>
+  <si>
+    <t>https://ibb.co/VW5z13bw</t>
+  </si>
+  <si>
+    <t>https://ibb.co/q3tjs4KP</t>
+  </si>
+  <si>
+    <t>https://ibb.co/rGf2kK5C</t>
+  </si>
+  <si>
+    <t>https://ibb.co/cXb9G7Np</t>
+  </si>
+  <si>
+    <t>https://ibb.co/WpY2zD1H</t>
+  </si>
+  <si>
+    <t>https://ibb.co/v6j3hZY3</t>
+  </si>
+  <si>
+    <t>https://ibb.co/Kp6m8sz2</t>
+  </si>
+  <si>
+    <t>https://ibb.co/1YcN5tKr</t>
+  </si>
+  <si>
+    <t>https://ibb.co/Q3ZnGsZs</t>
+  </si>
+  <si>
+    <t>https://ibb.co/sdwNNFvc</t>
+  </si>
+  <si>
+    <t>https://ibb.co/6k4vtK6</t>
+  </si>
+  <si>
+    <t>https://ibb.co/0RRRT3V5</t>
+  </si>
+  <si>
+    <t>https://ibb.co/gFrCzYgx</t>
+  </si>
+  <si>
+    <t>https://ibb.co/x8cbqBMH</t>
+  </si>
+  <si>
+    <t>https://ibb.co/gZN7cnKZ</t>
+  </si>
+  <si>
+    <t>https://ibb.co/43WNSS9</t>
+  </si>
+  <si>
+    <t>https://ibb.co/pr4n5KHq</t>
+  </si>
+  <si>
+    <t>https://ibb.co/WWVDg9jc</t>
+  </si>
+  <si>
+    <t>https://ibb.co/bM2RkpX5</t>
+  </si>
+  <si>
+    <t>https://ibb.co/svd1TmBt</t>
+  </si>
+  <si>
+    <t>https://ibb.co/B5gL2s8s</t>
+  </si>
+  <si>
+    <t>https://ibb.co/mF5NkkdJ</t>
+  </si>
+  <si>
+    <t>https://ibb.co/gLWgqyHS</t>
+  </si>
+  <si>
+    <t>https://ibb.co/zVtRbtkP</t>
+  </si>
+  <si>
+    <t>https://ibb.co/WWr5M8Pr</t>
+  </si>
+  <si>
+    <t>https://ibb.co/9HHFbp1Z</t>
+  </si>
+  <si>
+    <t>https://ibb.co/prk4K4L0</t>
+  </si>
+  <si>
+    <t>https://ibb.co/0y4HFkSL</t>
+  </si>
+  <si>
+    <t>https://ibb.co/XxwFHcPb</t>
+  </si>
+  <si>
+    <t>https://ibb.co/bj5dT3vP</t>
+  </si>
+  <si>
+    <t>https://ibb.co/v6LpvYHd</t>
+  </si>
+  <si>
+    <t>https://ibb.co/8nDrfqK9</t>
+  </si>
+  <si>
+    <t>https://ibb.co/Pvmhsvvn</t>
+  </si>
+  <si>
+    <t>https://ibb.co/1fyRWpTQ</t>
+  </si>
+  <si>
+    <t>https://ibb.co/mrVkRvM7</t>
+  </si>
+  <si>
+    <t>https://ibb.co/N2jzTXjJ</t>
+  </si>
+  <si>
+    <t>https://ibb.co/0pZLVqwj</t>
+  </si>
+  <si>
+    <t>https://ibb.co/Vc10cHb7</t>
+  </si>
+  <si>
+    <t>https://ibb.co/cXQSvcNw</t>
+  </si>
+  <si>
+    <t>https://ibb.co/4n8H6D1n</t>
+  </si>
+  <si>
+    <t>https://ibb.co/DTR6k2j</t>
+  </si>
+  <si>
+    <t>https://ibb.co/sJkyc5KX</t>
+  </si>
+  <si>
+    <t>https://ibb.co/spsp1sm7</t>
+  </si>
+  <si>
+    <t>https://ibb.co/RTptszDc</t>
+  </si>
+  <si>
+    <t>https://ibb.co/dwKrwPy6</t>
+  </si>
+  <si>
+    <t>https://ibb.co/4wvYgNKN</t>
+  </si>
+  <si>
+    <t>https://ibb.co/2Y7wWMyK</t>
+  </si>
+  <si>
+    <t>https://ibb.co/Z4ZDGpD</t>
+  </si>
+  <si>
+    <t>https://ibb.co/9D9S855</t>
+  </si>
+  <si>
+    <t>https://ibb.co/1fGm9kfF</t>
+  </si>
+  <si>
+    <t>https://ibb.co/k68128zB</t>
+  </si>
+  <si>
+    <t>https://ibb.co/0R11W8zG</t>
+  </si>
+  <si>
+    <t>https://ibb.co/MxkHpRZg</t>
+  </si>
+  <si>
+    <t>https://ibb.co/cS2TCxmb</t>
+  </si>
+  <si>
+    <t>https://ibb.co/3gbkCmT</t>
+  </si>
+  <si>
+    <t>https://ibb.co/yBBYvxjJ</t>
+  </si>
+  <si>
+    <t>https://ibb.co/QFZCW17G</t>
+  </si>
+  <si>
+    <t>https://ibb.co/6R8BXRMV</t>
+  </si>
+  <si>
+    <t>https://ibb.co/9393Cr4H</t>
+  </si>
+  <si>
+    <t>https://ibb.co/zTH2Q2PT</t>
+  </si>
+  <si>
+    <t>https://ibb.co/xtCTQFzt</t>
+  </si>
+  <si>
+    <t>https://ibb.co/LDCtjBCW</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - кент и духовный вдохновитель Кирилла Пинжина</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - контент-менеджер и аналитик прооекта. Отвечал за сбор материалов, изучение трудов академика В.Квинта, структурирование терминов и ведение базы данных в Excel.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> - главный разработчик проекта. Отвечал за написание кода в Python, интеграцию базы данных Excel, работу с GitHub и развёртывание бота на сервере Bothost.</t>
   </si>
 </sst>
 </file>
@@ -1623,13 +1617,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B1" t="s">
         <v>151</v>
       </c>
-      <c r="B1" t="s">
-        <v>152</v>
-      </c>
       <c r="C1" t="s">
-        <v>376</v>
+        <v>156</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1637,7 +1631,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1645,7 +1639,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1653,7 +1647,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1661,7 +1655,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1669,7 +1663,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1677,7 +1671,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -1685,7 +1679,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -1693,15 +1687,15 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="B10" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -1709,7 +1703,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1717,7 +1711,7 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -1725,7 +1719,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -1733,7 +1727,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -1741,7 +1735,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -1749,7 +1743,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -1757,7 +1751,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -1765,7 +1759,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -1773,7 +1767,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -1781,7 +1775,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -1789,7 +1783,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -1797,7 +1791,7 @@
         <v>18</v>
       </c>
       <c r="B22" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -1805,7 +1799,7 @@
         <v>19</v>
       </c>
       <c r="B23" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -1813,7 +1807,7 @@
         <v>20</v>
       </c>
       <c r="B24" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -1821,7 +1815,7 @@
         <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -1829,7 +1823,7 @@
         <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -1837,7 +1831,7 @@
         <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -1845,7 +1839,7 @@
         <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -1853,7 +1847,7 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -1861,7 +1855,7 @@
         <v>26</v>
       </c>
       <c r="B30" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -1869,7 +1863,7 @@
         <v>27</v>
       </c>
       <c r="B31" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -1877,7 +1871,7 @@
         <v>28</v>
       </c>
       <c r="B32" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -1885,7 +1879,7 @@
         <v>29</v>
       </c>
       <c r="B33" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -1893,7 +1887,7 @@
         <v>30</v>
       </c>
       <c r="B34" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -1901,7 +1895,7 @@
         <v>31</v>
       </c>
       <c r="B35" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -1909,7 +1903,7 @@
         <v>32</v>
       </c>
       <c r="B36" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -1917,7 +1911,7 @@
         <v>33</v>
       </c>
       <c r="B37" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -1925,7 +1919,7 @@
         <v>34</v>
       </c>
       <c r="B38" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -1933,7 +1927,7 @@
         <v>35</v>
       </c>
       <c r="B39" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -1941,7 +1935,7 @@
         <v>36</v>
       </c>
       <c r="B40" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -1949,7 +1943,7 @@
         <v>37</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -1957,7 +1951,7 @@
         <v>38</v>
       </c>
       <c r="B42" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -1965,7 +1959,7 @@
         <v>39</v>
       </c>
       <c r="B43" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -1973,7 +1967,7 @@
         <v>40</v>
       </c>
       <c r="B44" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -1981,7 +1975,7 @@
         <v>41</v>
       </c>
       <c r="B45" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -1989,7 +1983,7 @@
         <v>42</v>
       </c>
       <c r="B46" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -1997,7 +1991,7 @@
         <v>43</v>
       </c>
       <c r="B47" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -2005,7 +1999,7 @@
         <v>44</v>
       </c>
       <c r="B48" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -2013,7 +2007,7 @@
         <v>45</v>
       </c>
       <c r="B49" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -2021,7 +2015,7 @@
         <v>46</v>
       </c>
       <c r="B50" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -2029,7 +2023,7 @@
         <v>47</v>
       </c>
       <c r="B51" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -2037,7 +2031,7 @@
         <v>48</v>
       </c>
       <c r="B52" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -2045,7 +2039,7 @@
         <v>49</v>
       </c>
       <c r="B53" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -2053,7 +2047,7 @@
         <v>50</v>
       </c>
       <c r="B54" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -2061,7 +2055,7 @@
         <v>51</v>
       </c>
       <c r="B55" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -2069,15 +2063,15 @@
         <v>52</v>
       </c>
       <c r="B56" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="9" t="s">
-        <v>209</v>
+        <v>153</v>
       </c>
       <c r="B57" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -2085,7 +2079,7 @@
         <v>53</v>
       </c>
       <c r="B58" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -2093,7 +2087,7 @@
         <v>54</v>
       </c>
       <c r="B59" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -2101,7 +2095,7 @@
         <v>55</v>
       </c>
       <c r="B60" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -2109,7 +2103,7 @@
         <v>56</v>
       </c>
       <c r="B61" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -2117,7 +2111,7 @@
         <v>57</v>
       </c>
       <c r="B62" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -2125,7 +2119,7 @@
         <v>58</v>
       </c>
       <c r="B63" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -2133,7 +2127,7 @@
         <v>59</v>
       </c>
       <c r="B64" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
@@ -2141,7 +2135,7 @@
         <v>60</v>
       </c>
       <c r="B65" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -2149,7 +2143,7 @@
         <v>61</v>
       </c>
       <c r="B66" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
@@ -2157,7 +2151,7 @@
         <v>62</v>
       </c>
       <c r="B67" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -2165,7 +2159,7 @@
         <v>63</v>
       </c>
       <c r="B68" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -2173,7 +2167,7 @@
         <v>64</v>
       </c>
       <c r="B69" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -2181,7 +2175,7 @@
         <v>65</v>
       </c>
       <c r="B70" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
@@ -2189,7 +2183,7 @@
         <v>66</v>
       </c>
       <c r="B71" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
@@ -2197,7 +2191,7 @@
         <v>67</v>
       </c>
       <c r="B72" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
@@ -2205,7 +2199,7 @@
         <v>68</v>
       </c>
       <c r="B73" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
@@ -2213,7 +2207,7 @@
         <v>69</v>
       </c>
       <c r="B74" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
@@ -2221,7 +2215,7 @@
         <v>70</v>
       </c>
       <c r="B75" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
@@ -2229,7 +2223,7 @@
         <v>71</v>
       </c>
       <c r="B76" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
@@ -2237,7 +2231,7 @@
         <v>72</v>
       </c>
       <c r="B77" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
@@ -2245,7 +2239,7 @@
         <v>73</v>
       </c>
       <c r="B78" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
@@ -2253,7 +2247,7 @@
         <v>74</v>
       </c>
       <c r="B79" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
@@ -2261,7 +2255,7 @@
         <v>75</v>
       </c>
       <c r="B80" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
@@ -2269,7 +2263,7 @@
         <v>76</v>
       </c>
       <c r="B81" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
@@ -2277,7 +2271,7 @@
         <v>77</v>
       </c>
       <c r="B82" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
@@ -2285,7 +2279,7 @@
         <v>78</v>
       </c>
       <c r="B83" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
@@ -2293,7 +2287,7 @@
         <v>79</v>
       </c>
       <c r="B84" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
@@ -2301,7 +2295,7 @@
         <v>80</v>
       </c>
       <c r="B85" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
@@ -2309,7 +2303,7 @@
         <v>81</v>
       </c>
       <c r="B86" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
@@ -2317,7 +2311,7 @@
         <v>82</v>
       </c>
       <c r="B87" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
@@ -2325,7 +2319,7 @@
         <v>83</v>
       </c>
       <c r="B88" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
@@ -2333,7 +2327,7 @@
         <v>84</v>
       </c>
       <c r="B89" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
@@ -2341,7 +2335,7 @@
         <v>85</v>
       </c>
       <c r="B90" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
@@ -2349,7 +2343,7 @@
         <v>86</v>
       </c>
       <c r="B91" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
@@ -2357,7 +2351,7 @@
         <v>87</v>
       </c>
       <c r="B92" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
@@ -2365,10 +2359,10 @@
         <v>89</v>
       </c>
       <c r="B93" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="C93" s="14" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
@@ -2376,10 +2370,10 @@
         <v>90</v>
       </c>
       <c r="B94" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="C94" s="14" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
@@ -2387,10 +2381,10 @@
         <v>91</v>
       </c>
       <c r="B95" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="C95" s="14" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
@@ -2398,10 +2392,10 @@
         <v>92</v>
       </c>
       <c r="B96" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="C96" s="14" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
@@ -2409,10 +2403,10 @@
         <v>93</v>
       </c>
       <c r="B97" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="C97" s="14" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
@@ -2420,10 +2414,10 @@
         <v>94</v>
       </c>
       <c r="B98" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="C98" s="14" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
@@ -2431,10 +2425,10 @@
         <v>95</v>
       </c>
       <c r="B99" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="C99" s="14" t="s">
-        <v>315</v>
+        <v>327</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
@@ -2442,10 +2436,10 @@
         <v>96</v>
       </c>
       <c r="B100" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="C100" s="14" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
@@ -2453,10 +2447,10 @@
         <v>97</v>
       </c>
       <c r="B101" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="C101" s="14" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
@@ -2464,10 +2458,10 @@
         <v>98</v>
       </c>
       <c r="B102" t="s">
-        <v>255</v>
+        <v>319</v>
       </c>
       <c r="C102" s="14" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
@@ -2475,10 +2469,10 @@
         <v>99</v>
       </c>
       <c r="B103" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="C103" s="14" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
@@ -2486,579 +2480,577 @@
         <v>100</v>
       </c>
       <c r="B104" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="C104" s="14" t="s">
-        <v>320</v>
+        <v>381</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="9" t="s">
-        <v>101</v>
+        <v>320</v>
       </c>
       <c r="B105" t="s">
-        <v>258</v>
-      </c>
-      <c r="C105" s="14" t="s">
-        <v>321</v>
-      </c>
+        <v>266</v>
+      </c>
+      <c r="C105" s="14"/>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B106" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="C106" s="14" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B107" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="C107" s="14" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B108" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="C108" s="14" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B109" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="C109" s="14" t="s">
-        <v>325</v>
+        <v>335</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B110" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="C110" s="14" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B111" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="C111" s="14" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B112" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="C112" s="14" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B113" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="C113" s="14" t="s">
-        <v>329</v>
+        <v>339</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" s="11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B114" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="C114" s="14" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B115" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="C115" s="14" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B116" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="C116" s="14" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" s="11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B117" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="C117" s="14" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" s="11" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B118" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="C118" s="14" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B119" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="C119" s="14" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" s="11" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B120" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="C120" s="14" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" s="11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B121" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="C121" s="14" t="s">
-        <v>337</v>
+        <v>347</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" s="11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B122" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="C122" s="14" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B123" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="C123" s="14" t="s">
-        <v>339</v>
+        <v>381</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B124" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B125" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="C125" s="14" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" s="11" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B126" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="C126" s="14" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" s="11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B127" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="C127" s="14" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" s="11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B128" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="C128" s="14" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" s="11" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B129" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="C129" s="14" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B130" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="C130" s="14" t="s">
-        <v>345</v>
+        <v>354</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A131" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B131" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="C131" s="14" t="s">
-        <v>346</v>
+        <v>355</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B132" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="C132" s="14" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" s="11" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B133" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="C133" s="14" t="s">
-        <v>348</v>
+        <v>357</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" s="11" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B134" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="C134" s="14" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" s="11" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B135" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="C135" s="14" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" s="11" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B136" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="C136" s="14" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" s="11" t="s">
-        <v>354</v>
+        <v>154</v>
       </c>
       <c r="B137" t="s">
-        <v>353</v>
+        <v>298</v>
       </c>
       <c r="C137" s="14" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" s="11" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B138" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="C138" s="14" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" s="11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B139" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="C139" s="14" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" s="11" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B140" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="C140" s="14" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" s="11" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B141" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="C141" s="14" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" s="11" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B142" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="C142" s="14" t="s">
-        <v>359</v>
+        <v>380</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" s="11" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B143" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="C143" s="14" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" s="11" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B144" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="C144" s="14" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" s="11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B145" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="C145" s="14" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" s="11" t="s">
-        <v>364</v>
+        <v>155</v>
       </c>
       <c r="B146" t="s">
-        <v>363</v>
+        <v>307</v>
       </c>
       <c r="C146" s="14" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" s="11" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B147" t="s">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="C147" s="14" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A148" s="11" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B148" t="s">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="C148" s="14" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B149" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="C149" s="14" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" s="11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B150" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="C150" s="14" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" s="11" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B151" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="C151" s="14" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" s="11" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B152" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="C152" s="14" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B153" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="C153" s="14" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" s="11" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B154" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="C154" s="14" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" s="11" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B155" t="s">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="C155" s="14" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" s="11" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B156" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="C156" s="14" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
     </row>
     <row r="157" spans="1:3" ht="240" x14ac:dyDescent="0.25">
@@ -3066,117 +3058,113 @@
         <v>88</v>
       </c>
       <c r="B157" s="13" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
     </row>
     <row r="158" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A158" s="11" t="s">
-        <v>377</v>
+        <v>157</v>
       </c>
       <c r="B158" s="15" t="s">
-        <v>387</v>
+        <v>163</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" s="11" t="s">
-        <v>378</v>
+        <v>158</v>
       </c>
       <c r="B159" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="C159" t="s">
-        <v>381</v>
+        <v>159</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" s="11" t="s">
-        <v>386</v>
+        <v>162</v>
       </c>
       <c r="B160" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="C160" t="s">
-        <v>382</v>
+        <v>160</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="B161" t="s">
         <v>383</v>
       </c>
-      <c r="B161" t="s">
-        <v>384</v>
-      </c>
-      <c r="C161" t="s">
-        <v>385</v>
+      <c r="C161" s="14" t="s">
+        <v>382</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C93" r:id="rId1"/>
-    <hyperlink ref="C94" r:id="rId2"/>
-    <hyperlink ref="C95" r:id="rId3"/>
-    <hyperlink ref="C96" r:id="rId4"/>
-    <hyperlink ref="C97" r:id="rId5"/>
-    <hyperlink ref="C98" r:id="rId6"/>
-    <hyperlink ref="C99" r:id="rId7"/>
-    <hyperlink ref="C100" r:id="rId8"/>
-    <hyperlink ref="C101" r:id="rId9"/>
-    <hyperlink ref="C102" r:id="rId10"/>
-    <hyperlink ref="C103" r:id="rId11"/>
-    <hyperlink ref="C104" r:id="rId12"/>
-    <hyperlink ref="C105" r:id="rId13"/>
-    <hyperlink ref="C106" r:id="rId14"/>
-    <hyperlink ref="C107" r:id="rId15"/>
-    <hyperlink ref="C108" r:id="rId16"/>
-    <hyperlink ref="C109" r:id="rId17"/>
-    <hyperlink ref="C110" r:id="rId18"/>
-    <hyperlink ref="C111" r:id="rId19"/>
-    <hyperlink ref="C112" r:id="rId20"/>
-    <hyperlink ref="C113" r:id="rId21"/>
-    <hyperlink ref="C114" r:id="rId22"/>
-    <hyperlink ref="C115" r:id="rId23"/>
-    <hyperlink ref="C116" r:id="rId24"/>
-    <hyperlink ref="C117" r:id="rId25"/>
-    <hyperlink ref="C118" r:id="rId26"/>
-    <hyperlink ref="C119" r:id="rId27"/>
-    <hyperlink ref="C120" r:id="rId28"/>
-    <hyperlink ref="C121" r:id="rId29"/>
-    <hyperlink ref="C122" r:id="rId30"/>
-    <hyperlink ref="C123" r:id="rId31"/>
-    <hyperlink ref="C125" r:id="rId32"/>
-    <hyperlink ref="C126" r:id="rId33"/>
-    <hyperlink ref="C127" r:id="rId34"/>
-    <hyperlink ref="C128" r:id="rId35"/>
-    <hyperlink ref="C129" r:id="rId36"/>
-    <hyperlink ref="C130" r:id="rId37"/>
-    <hyperlink ref="C131" r:id="rId38"/>
-    <hyperlink ref="C132" r:id="rId39"/>
-    <hyperlink ref="C133" r:id="rId40"/>
-    <hyperlink ref="C134" r:id="rId41"/>
-    <hyperlink ref="C135" r:id="rId42"/>
-    <hyperlink ref="C136" r:id="rId43"/>
-    <hyperlink ref="C137" r:id="rId44"/>
-    <hyperlink ref="C138" r:id="rId45"/>
-    <hyperlink ref="C139" r:id="rId46"/>
-    <hyperlink ref="C140" r:id="rId47"/>
-    <hyperlink ref="C141" r:id="rId48"/>
-    <hyperlink ref="C142" r:id="rId49"/>
-    <hyperlink ref="C143" r:id="rId50"/>
-    <hyperlink ref="C144" r:id="rId51"/>
-    <hyperlink ref="C145" r:id="rId52"/>
-    <hyperlink ref="C146" r:id="rId53"/>
-    <hyperlink ref="C147" r:id="rId54"/>
-    <hyperlink ref="C148" r:id="rId55"/>
-    <hyperlink ref="C149" r:id="rId56"/>
-    <hyperlink ref="C150" r:id="rId57"/>
-    <hyperlink ref="C151" r:id="rId58"/>
-    <hyperlink ref="C152" r:id="rId59"/>
-    <hyperlink ref="C153" r:id="rId60"/>
-    <hyperlink ref="C154" r:id="rId61"/>
-    <hyperlink ref="C155" r:id="rId62"/>
-    <hyperlink ref="C156" r:id="rId63"/>
+    <hyperlink ref="C95" r:id="rId2"/>
+    <hyperlink ref="C96" r:id="rId3"/>
+    <hyperlink ref="C97" r:id="rId4"/>
+    <hyperlink ref="C98" r:id="rId5"/>
+    <hyperlink ref="C99" r:id="rId6"/>
+    <hyperlink ref="C100" r:id="rId7"/>
+    <hyperlink ref="C101" r:id="rId8"/>
+    <hyperlink ref="C102" r:id="rId9"/>
+    <hyperlink ref="C103" r:id="rId10"/>
+    <hyperlink ref="C107" r:id="rId11"/>
+    <hyperlink ref="C106" r:id="rId12"/>
+    <hyperlink ref="C108" r:id="rId13"/>
+    <hyperlink ref="C109" r:id="rId14"/>
+    <hyperlink ref="C110" r:id="rId15"/>
+    <hyperlink ref="C111" r:id="rId16"/>
+    <hyperlink ref="C112" r:id="rId17"/>
+    <hyperlink ref="C113" r:id="rId18"/>
+    <hyperlink ref="C114" r:id="rId19"/>
+    <hyperlink ref="C115" r:id="rId20"/>
+    <hyperlink ref="C116" r:id="rId21"/>
+    <hyperlink ref="C117" r:id="rId22"/>
+    <hyperlink ref="C118" r:id="rId23"/>
+    <hyperlink ref="C119" r:id="rId24"/>
+    <hyperlink ref="C120" r:id="rId25"/>
+    <hyperlink ref="C121" r:id="rId26"/>
+    <hyperlink ref="C122" r:id="rId27"/>
+    <hyperlink ref="C125" r:id="rId28"/>
+    <hyperlink ref="C126" r:id="rId29"/>
+    <hyperlink ref="C127" r:id="rId30"/>
+    <hyperlink ref="C128" r:id="rId31"/>
+    <hyperlink ref="C129" r:id="rId32"/>
+    <hyperlink ref="C130" r:id="rId33"/>
+    <hyperlink ref="C131" r:id="rId34"/>
+    <hyperlink ref="C132" r:id="rId35"/>
+    <hyperlink ref="C133" r:id="rId36"/>
+    <hyperlink ref="C134" r:id="rId37"/>
+    <hyperlink ref="C135" r:id="rId38"/>
+    <hyperlink ref="C136" r:id="rId39"/>
+    <hyperlink ref="C137" r:id="rId40"/>
+    <hyperlink ref="C138" r:id="rId41"/>
+    <hyperlink ref="C139" r:id="rId42"/>
+    <hyperlink ref="C140" r:id="rId43"/>
+    <hyperlink ref="C143" r:id="rId44"/>
+    <hyperlink ref="C141" r:id="rId45"/>
+    <hyperlink ref="C144" r:id="rId46"/>
+    <hyperlink ref="C145" r:id="rId47"/>
+    <hyperlink ref="C146" r:id="rId48"/>
+    <hyperlink ref="C147" r:id="rId49"/>
+    <hyperlink ref="C148" r:id="rId50"/>
+    <hyperlink ref="C149" r:id="rId51"/>
+    <hyperlink ref="C150" r:id="rId52"/>
+    <hyperlink ref="C151" r:id="rId53"/>
+    <hyperlink ref="C152" r:id="rId54"/>
+    <hyperlink ref="C153" r:id="rId55"/>
+    <hyperlink ref="C154" r:id="rId56"/>
+    <hyperlink ref="C155" r:id="rId57"/>
+    <hyperlink ref="C156" r:id="rId58"/>
+    <hyperlink ref="C161" r:id="rId59"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId64"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId60"/>
 </worksheet>
 </file>
--- a/database.xlsx
+++ b/database.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="389">
   <si>
     <t xml:space="preserve">Алгоритм Беннетта </t>
   </si>
@@ -1212,12 +1212,33 @@
   <si>
     <t xml:space="preserve"> - главный разработчик проекта. Отвечал за написание кода в Python, интеграцию базы данных Excel, работу с GitHub и развёртывание бота на сервере Bothost.</t>
   </si>
+  <si>
+    <r>
+      <t> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>путин, владимир путин, вв путин, президент, глава государства</t>
+    </r>
+  </si>
+  <si>
+    <t>Владимир Владимирович Путин — Президент Российской Федерации. В методологии стратегирования академика В. Квинта государственные стратегии, указы о национальных целях и стратегических приоритетах развития России, утверждаемые Президентом, являются высшей формой практического применения теории стратегии на макроуровне.</t>
+  </si>
+  <si>
+    <t>http://static.kremlin.ru/media/events/press-photos/orig/FA1sRKf4WaYDSJjB4LjCZ0OjGc7qAFXh.jpg?kremlin-ru_photo-50.jpg</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1265,6 +1286,20 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="13"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1287,7 +1322,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1326,6 +1361,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
@@ -1607,7 +1644,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C161"/>
+  <dimension ref="A1:C162"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="255.5703125" customWidth="1"/>
@@ -3100,6 +3137,17 @@
       </c>
       <c r="C161" s="14" t="s">
         <v>382</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A162" s="16" t="s">
+        <v>386</v>
+      </c>
+      <c r="B162" s="17" t="s">
+        <v>387</v>
+      </c>
+      <c r="C162" t="s">
+        <v>388</v>
       </c>
     </row>
   </sheetData>

--- a/database.xlsx
+++ b/database.xlsx
@@ -532,468 +532,6 @@
 Напишите в чат "Кирилл" или "Владос" чтобы узнать о каждом подробнее!</t>
   </si>
   <si>
-    <t xml:space="preserve">  — метод сложения коэффициентов (P=ΣP×Wk), полезный только для оценки крайних значений (самых развитых или самых бедных стран).</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> — метод умножения коэффициентов (P=1000×ΠPkWk), более точный для малых экономик, где единичные инновации существенно влияют на эффективность.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> — нестандартные решения для преимущества</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> — состояние системы</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> — страны, квалифицированные по инициативе МВФ и Всемирного банка как неспособные выплатить свой долг.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> — крупнейшие аудиторские фирмы мира: PricewaterhouseCoopers (PwC), Deloitte Touche, Ernst &amp; Young (EY) и KPMG.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> — представление о будущем состоянии объекта</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> — валовой национальный доход на человека, основа классификации Группы Всемирного банка для кредитных решений</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> — усиление взаимосвязи экономик и рынков</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> — совокупность мировых рынков</t>
-  </si>
-  <si>
-    <t>— подсистема глобального миропорядка, каркас относительно стабильного сотрудничества бизнеса с глобальными, региональными и национальными институтами. Cтимулирует преимущественно эволюционное развитие глобального рыночного пространства.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> — повторяющиеся связи развития.</t>
-  </si>
-  <si>
-    <t>— время даёт преимущество</t>
-  </si>
-  <si>
-    <t>— реализуются только обеспеченные направления</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> — первый и главный закон стратегии по Квинту; фактор времени является детерминирующим в стратегии</t>
-  </si>
-  <si>
-    <t>— глобальные, национальные, региональные, корпоративные, индивидуальные</t>
-  </si>
-  <si>
-    <t>— основа рейтинговых систем и индексов, на которых строятся классификационные системы стран и регионов</t>
-  </si>
-  <si>
-    <t>— один из пяти показателей синтезированного странового рейтинга Квинта (относительная значимость 1,0)</t>
-  </si>
-  <si>
-    <t>— один из пяти показателей синтезированного рейтинга (относительная значимость 0,7)</t>
-  </si>
-  <si>
-    <t>— показатель, разработанный Квинтом на основе базы данных ЮНИДО для синтезированного рейтинга стран</t>
-  </si>
-  <si>
-    <t>— источник преимуществ</t>
-  </si>
-  <si>
-    <t>— объединение всех уровней</t>
-  </si>
-  <si>
-    <t>— присутствие в стране международных банков, страховых компаний, аудиторов и юридических фирм, необходимое для входа на иностранный рынок</t>
-  </si>
-  <si>
-    <t>— ориентация на прошлое</t>
-  </si>
-  <si>
-    <t>— группы, составляющие классификационную систему; внутри категорий также применяется рейтинговая система</t>
-  </si>
-  <si>
-    <t>— факторы превосходства</t>
-  </si>
-  <si>
-    <t>— доминирующая в России конца 2010-х модель, существенно отличающаяся как от государственного капитализма, так и от коммунизма</t>
-  </si>
-  <si>
-    <t>— одна из трёх дополнительных категорий ООН, отражающая географическую специфику развития.</t>
-  </si>
-  <si>
-    <t>— псевдопредвидение в виде пророчеств, прорицаний, «откровений» и гаданий</t>
-  </si>
-  <si>
-    <t>— фундаментальная цель и смысл существования объекта</t>
-  </si>
-  <si>
-    <t>— система характеристик и внутренняя структура государства: политические, экономические, финансовые, технологические индикаторы, культурная и религиозная среда</t>
-  </si>
-  <si>
-    <t>— слово из Торы, ассоциирующееся с мощным и точным видением таких великих лидеров, как Моисей и Самуил</t>
-  </si>
-  <si>
-    <t>— слово из Торы, отображающее пророка-провидца без лидерских качеств.</t>
-  </si>
-  <si>
-    <t>— категория ООН с 1971 года. Критерии: низкий доход (ВНД на душу населения), слабый человеческий капитал и экономическая уязвимость.</t>
-  </si>
-  <si>
-    <t>— быстро формирующаяся технология, которая может стать основой беспрецедентно больших систем стратегических компетенций.</t>
-  </si>
-  <si>
-    <t>— информационно-познавательный аспект опережающего отражения как свойства высших форм материи.</t>
-  </si>
-  <si>
-    <t>— категория МВФ: Гонконг, Корея, Сингапур и Тайвань.</t>
-  </si>
-  <si>
-    <t>— интуитивное (связанное с подсознанием), обыденное (по народным приметам) и мантическое (пророчества, гадания) предвидение.</t>
-  </si>
-  <si>
-    <t>— категория, появившаяся благодаря европейским открытиям; несистематизированные территории, ставшие затем странами и регионами.</t>
-  </si>
-  <si>
-    <t>— сценарии будущего, в которых сталкиваются или кооперируют ценностные ориентиры, интересы и приоритеты субъектов стратегирования.</t>
-  </si>
-  <si>
-    <t>— концепция Даниэля Канемана: «Мы думаем о нашем будущем как об ожидаемых воспоминаниях».</t>
-  </si>
-  <si>
-    <t>— термин древних греков для описания известного им мира с центром в Элладе; одна из первых попыток системного понимания мира</t>
-  </si>
-  <si>
-    <t>— метод, используемый в рамках методологии стратегирования научной школы Квинта. Расшифровывается как Opportunities (Возможности), Threats (Угрозы), Strengths (Сильные стороны) и Weaknesses (Слабые стороны).</t>
-  </si>
-  <si>
-    <t>— разработка действий.</t>
-  </si>
-  <si>
-    <t>— интеграция стратегии и тактики</t>
-  </si>
-  <si>
-    <t>— риск экспроприации, национализации и повреждения частной собственности иностранных лиц в странах с гражданскими волнениями.</t>
-  </si>
-  <si>
-    <t>— способность понимать будущее.</t>
-  </si>
-  <si>
-    <t>— результат понимания будущего.</t>
-  </si>
-  <si>
-    <t>— сложное предвосхищение, вид интеллектуальной деятельности человека на основе личного опыта</t>
-  </si>
-  <si>
-    <t>— простое предвосхищение, свойственное любому организму; одна из форм конкретизации предвидения.</t>
-  </si>
-  <si>
-    <t>— ключевые направления развития</t>
-  </si>
-  <si>
-    <t>— категория МВФ с 1997 года, объединяющая развитые страны и самые зрелые СФР (Южная Корея, Сингапур, Израиль)</t>
-  </si>
-  <si>
-    <t>— научное определение будущего.</t>
-  </si>
-  <si>
-    <t>— устаревшая категория МВФ, заменённая на «продвинутые экономики» из-за сокращения занятости в индустриальном производстве.</t>
-  </si>
-  <si>
-    <t>— интуитивное предвидение.</t>
-  </si>
-  <si>
-    <t>— люди, «видевшие» картины будущего. Их главная ценность для стратегов — традиция связывать пророчества со шкалой времени</t>
-  </si>
-  <si>
-    <t>— редчайшее сочетание способностей провидца с лидерскими качествами практика (Моисей, Мухаммед)</t>
-  </si>
-  <si>
-    <t>— инвестиции компаний в зарубежные экономики. Новый тренд: ПИИ из СФР направляются в наукоёмкие отрасли развитых стран.</t>
-  </si>
-  <si>
-    <t>— решения, ведущие к далёкому будущему, всегда принимаемые на грани сознания и подсознания, рационального и иррационального.</t>
-  </si>
-  <si>
-    <t>— позиции, присваиваемые странам и регионам в рейтингах, индексах и внутри классификационных категорий.</t>
-  </si>
-  <si>
-    <t>— высшая стадия СФР (Южная Корея, Сингапур, Израиль, Гонконг, Испания, Португалия, Греция). Стратегически конкурируют с развитыми странами.</t>
-  </si>
-  <si>
-    <t>— средства для реализации стратегии.</t>
-  </si>
-  <si>
-    <t>— вероятность потерь</t>
-  </si>
-  <si>
-    <t>— рейтинг технологического, экономического и социального развития стран на основе пяти индикаторов.</t>
-  </si>
-  <si>
-    <t>— классификационная категория, ядром которой стала цивилизация ойкумены к концу XV века.</t>
-  </si>
-  <si>
-    <t>— мудрый дисциплинированный и оптимистичный профессионал, имеющий стратегическое мышление, видение будущего и интуицию, подкрепленную методологией стратегирования.</t>
-  </si>
-  <si>
-    <t>— мудрые дисциплинированные и оптимистичные профессионалы, имеющие стратегическое мышление, видение будущего и интуицию, подкрепленную методологией стратегирования.</t>
-  </si>
-  <si>
-    <t>— система официальных взглядов и положений, устанавливающая направления долгосрочного развития объекта стратегирования.</t>
-  </si>
-  <si>
-    <t>— способность принимать долгосрочные решения.</t>
-  </si>
-  <si>
-    <t>— процесс формирования и функционирования системы стратегического управления, обеспечивающей разработку и долгосрочную реализацию стратегии, её доктрины, в соответствии с содержащимися в них конкурентными преимуществами, приоритетами, целями и задачами.</t>
-  </si>
-  <si>
-    <t>— контроль и корректировка стратегии.</t>
-  </si>
-  <si>
-    <t>— один из альтернативных вариантов реализации стратегии. Как правило, разрабатывается не менее трёх сценариев, которые отличаются соотношением риска, асимметричности и общественно-экономической эффективности.</t>
-  </si>
-  <si>
-    <t>— система поиска, формулирования и развития доктрины, обеспечивающей долгосрочный успех</t>
-  </si>
-  <si>
-    <t>— концепция профессора Прахалада о заработке на беднейших слоях за счёт продажи малых упаковок товаров при высоком обороте.</t>
-  </si>
-  <si>
-    <t>— процесс разработки, реализации и обновления стратегии.</t>
-  </si>
-  <si>
-    <t>— одна из трёх дополнительных категорий ООН, отражающая географические ограничения развития.</t>
-  </si>
-  <si>
-    <t>— категория восточноевропейских стран и СНГ. Квинт критикует её: логически все СФР и развивающиеся страны находятся в переходной стадии</t>
-  </si>
-  <si>
-    <t>— переходная стадия от развивающихся к СФР (Тунис, Монголия, Мадагаскар, Буркина Фасо).</t>
-  </si>
-  <si>
-    <t>— сценарии, в которых сталкиваются или кооперируют ценностные ориентиры, интересы и приоритеты субъектов стратегирования.</t>
-  </si>
-  <si>
-    <t>— система текущих действий для реализации стратегии.</t>
-  </si>
-  <si>
-    <t>— теория систематизации и иерархических сфер действительности и знаний, созданная Карлом Линнеем в 1813 году.</t>
-  </si>
-  <si>
-    <t>— теория Канемана и Тверски о принятии решений в условиях высоких рисков, исключительно важная для стратегирования.</t>
-  </si>
-  <si>
-    <t>— термин, ассоциировавшийся с бедными неразвитыми странами. Большинство из них отклонили принципы свободного конкурентного рынка и стали беднее.</t>
-  </si>
-  <si>
-    <t>— устойчивые направления развития.</t>
-  </si>
-  <si>
-    <t>— негативные факторы.</t>
-  </si>
-  <si>
-    <t>— ключ к стратегическому преимуществу.</t>
-  </si>
-  <si>
-    <t>— главная стратегическая угроза для России и ещё более 20 стран в XXI веке; депопуляция, игнорируемая в большинстве стратегических документов.</t>
-  </si>
-  <si>
-    <t>— неопределённость среды.</t>
-  </si>
-  <si>
-    <t>— конкретные ориентиры, размещённые во времени.</t>
-  </si>
-  <si>
-    <t>— показатель стратегического уровня развития. Северные страны обеспечивают наиболее устойчивую окружающую среду; страны с диктатурами замыкают рейтинг.</t>
-  </si>
-  <si>
-    <t>— стратегия Китая «Пять в одном»: посадка деревьев на четверти территории, восстановление 30% береговой линии, сокращение потребления угля на 40%.</t>
-  </si>
-  <si>
-    <t>— Первый библейский патриарх и пророк. Отнесён к проактивным лидерам, чьё стратегическое предвидение направляло не только семью, но и целые поколения. Пример провидца, который действует, а не только созерцает.</t>
-  </si>
-  <si>
-    <t>— Период: XIII век до н. э. Старший брат Моисея и Первый первосвященник. Квинт проводит границу: Аарон —  Моисей — пророк и стратег. Духовный сан и стратегическое лидерство — разные.</t>
-  </si>
-  <si>
-    <t>— Внёс вклад в развитие государственной и военной стратегии Руси. Прославился грамотным использованием местности, дипломатией и способностью принимать стратегические решения в сложных условиях. Его победы и политика помогли сохранить независимость русских земель.</t>
-  </si>
-  <si>
-    <t>— Один из величайших русских полководцев. Внёс вклад в развитие военной стратегии благодаря мобильности армии, быстроте принятия решений и нестандартным действиям. Его принципы подготовки войск и дисциплины стали важной частью военного стратегирования.</t>
-  </si>
-  <si>
-    <t>— 1937–1996.Психолог, соавтор Канемана. Их исследования ошибочных суждений и восприятия риска в условиях неопределённости Квинт считает критически важными для теории стратегирования.</t>
-  </si>
-  <si>
-    <t>— стратег и основатель Империи Тимуридов. Владимир Квинт посвятил его лидерству отдельную книгу. Главный принцип: успех государства зависит от привлечения талантливых людей («предприимчивых, мужественных и благоразумных»), ценность которых превышает ценность тысяч безвольных работников</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> — Герцог Веллингтон. Внёс вклад в развитие военной стратегии благодаря успешному противостоянию армии Наполеона. Уделял внимание дисциплине, подготовке армии и грамотному использованию местности.</t>
-  </si>
-  <si>
-    <t>— современный исследователь (XX–XXI вв.).Специалист по политэкономии Восточной Азии. Квинт цитирует его работы о связи авторитарной олигархии и экономической структуры стран ЮВА.</t>
-  </si>
-  <si>
-    <t>— ключевой стратег цифровой эпохи. Развивал программное обеспечение и сделал ставку на массовое распространение персональных компьютеров. Его решения сыграли большую роль в развитии мировой IT-индустрии</t>
-  </si>
-  <si>
-    <t>— Один из крупнейших полководцев XX века. Внёс вклад в развитие стратегического управления армией во время Второй мировой войны. Его решения в крупнейших операциях повлияли на советскую и мировую военную стратегию</t>
-  </si>
-  <si>
-    <t>— Один из великих библейских пророков. Его видения охватывали века. Квинт подчёркивает уникальную глубину его предсказаний, недоступную даже современному планированию. Эталон предвидения.</t>
-  </si>
-  <si>
-    <t>— Современный американский историк экономики (XX–XXI вв.).Исследовал античные модели: свободное предпринимательство в Древней Греции и дворцовая монополия в Египте как два изначальных стратегических пути экономики.</t>
-  </si>
-  <si>
-    <t>— Внёс вклад в развитие цифровой стратегии и интернет-торговли. Создал платформу Alibaba, сделав ставку на развитие онлайн-бизнеса и глобальной электронной коммерции.</t>
-  </si>
-  <si>
-    <t>— Внёс вклад в развитие корпоративной стратегии. Руководя General Electric, внедрял инновации, оптимизацию процессов и долгосрочное планирование. Пример эффективного стратегического менеджмента.</t>
-  </si>
-  <si>
-    <t>— Внёс вклад в развитие современной стратегической теории. Разработал концепцию OODA Loop (быстрый анализ ситуации и принятие решений). Идеи используются в военной стратегии, бизнесе и управлении.</t>
-  </si>
-  <si>
-    <t>— 1928–2005. Историк экономики, коллега Купманса. Предложил подход к сравнению экономических систем по организационным функциям, который Квинт рассматривает как важный шаг, но с ограничениями.</t>
-  </si>
-  <si>
-    <t>— 1667–1745.Англо-ирландский писатель. Квинт отмечает его предвидение: за полтора века до открытия Свифт описал два спутника Марса и их орбитальные параметры, почти совпавшие с реальностью.</t>
-  </si>
-  <si>
-    <t>— Внёс огромный вклад в развитие экономической стратегии Китая. Провёл реформы, открывшие страну для мирового рынка. Благодаря этому Китай начал быстрое экономическое развитие</t>
-  </si>
-  <si>
-    <t>— 1927–2015. Советский и российский учёный, социолог и футуролог. Представитель отечественной школы, начавшей осмысливать процессы научного и ненаучного познания будущего</t>
-  </si>
-  <si>
-    <t>— ок. XIII–XII века до н. э. Преемник Моисея, завоеватель Ханаана. Квинт описывает его как образец военного стратега и полководца, а не пророка.</t>
-  </si>
-  <si>
-    <t>— Известен долгосрочным стратегическим видением и инновационным подходом. Развивает проекты в области космоса, электромобилей и ИИ. Стратегии основаны на высоких рисках и стремлении изменить будущее</t>
-  </si>
-  <si>
-    <t>— Внёс значительный вклад в развитие византийской военной стратегии. Систематизировал знания о ведении войны и организации армии. Его труды стали основой для многих военных трактатов Средневековья.</t>
-  </si>
-  <si>
-    <t>— ок. XIII–XII века до н. э. (мифология).Троянская царевна с даром точного предвидения, но обречённая на то, что ей никто не верил. Символ трагедии провидца, лишённого стратегического влияния.</t>
-  </si>
-  <si>
-    <t>— Один из главных теоретиков стратегии. В работе «О войне» рассматривал войну как продолжение политики. Его идеи оказали огромное влияние на современную военную и государственную стратегию</t>
-  </si>
-  <si>
-    <t>— Ведущий специалист в области бизнес-стратегии. Изучал глобализацию и конкурентные преимущества. Его идеи повлияли на современное корпоративное стратегирование</t>
-  </si>
-  <si>
-    <t>— Сыграл важную роль в восстановлении Германии после Второй мировой войны. Использовал долгосрочное стратегическое планирование для укрепления экономики и международных отношений</t>
-  </si>
-  <si>
-    <t>— Внёс вклад в развитие экономической и транспортной стратегии. Создал крупную транспортную империю, используя долгосрочное планирование и контроль инфраструктуры</t>
-  </si>
-  <si>
-    <t>— Развивал стратегические и тактические принципы Византии. Уделял внимание анализу военных действий и изучению опыта прошлых войн. Сохранил византийскую школу стратегирования</t>
-  </si>
-  <si>
-    <t>— правил 161–180. Римский император, философ-стоик. Уникальный пример сочетания императора, мудреца и стратега-провидца, не допускавшего ошибок от конфликта этих ролей.</t>
-  </si>
-  <si>
-    <t>— 1927–1997.Американский писатель, автор романа «Киборг». Предвосхитил появление бионических протезов, управляемых силой мысли</t>
-  </si>
-  <si>
-    <t>— Американский экономист, профессор Стэнфорда. Автор методики рейтингования стран середины XX века. Квинт критикует его алгоритм сложения показателей за неточность.</t>
-  </si>
-  <si>
-    <t>— Японский стратег и мастер боевых искусств. Разработал подход, основанный на дисциплине, психологическом превосходстве и анализе противника. Автор «Книги пяти колец».</t>
-  </si>
-  <si>
-    <t>—  приблизительно XIII век до н. э.Библейский пророк и вождь. Квинт считает его величайшим провидцем-стратегом, сочетавшим дар предвидения и практическое лидерство, ведя народ сквозь хаос пустыни</t>
-  </si>
-  <si>
-    <t>— ок. 570–632. Основатель ислама и глава первого мусульманского государства. Редчайшая фигура, сочетавшая посланническую миссию и практическое стратегическое руководство</t>
-  </si>
-  <si>
-    <t>— X век до н. э.Пророк при дворе царя Давида. Предвидел воцарение Соломона и строительство Храма. Пример стратегического совета провидца, определявшего государственные решения</t>
-  </si>
-  <si>
-    <t>— 1769–1821.Император Франции и великий полководец. Активно использовал скорость, концентрацию сил и мобильность. Квинт анализирует поход 1812 года как трагедию выбора пути гибели без чёткого плана</t>
-  </si>
-  <si>
-    <t>— 1503–1566.Французский врач и астролог. Квинт восхищается точностью ряда предсказаний, но делает вывод: Нострадамус — предсказатель, а не пророк.</t>
-  </si>
-  <si>
-    <t>— 1894–1963. Английский писатель, автор «О дивный новый мир». Предсказал генную инженерию и вмешательство в репродукцию задолго до появления технологий</t>
-  </si>
-  <si>
-    <t>— Мастер дипломатической стратегии. Объединил Германию благодаря продуманной политике, союзам и использованию международной обстановки. Пример долгосрочного государственного планирования.</t>
-  </si>
-  <si>
-    <t>— Уделял внимание реформированию армии и укреплению дисциплины. Стремился повысить эффективность вооружённых сил, что повлияло на дальнейшее развитие военной стратегии России.</t>
-  </si>
-  <si>
-    <t>— Внёс большой вклад в развитие государственной и военной стратегии России. Провёл масштабные реформы армии, флота и управления. Укрепил международное положение России</t>
-  </si>
-  <si>
-    <t>— родился в 1930 году. Израильский математик, нобелевский лауреат. Вывод: в долгосрочных конфликтах выигрывает тот, кто ставит стратегию выше быстрой выгоды</t>
-  </si>
-  <si>
-    <t>— Внёс вклад в развитие национальной и военной стратегии Шотландии. Добился независимости страны благодаря грамотному использованию ресурсов и поддержке населения</t>
-  </si>
-  <si>
-    <t>— 1941–2010.Профессор Мичиганского университета. Автор концепции «Дно пирамиды» (заработок на беднейших слоях за счёт малого товара и высокого оборота).</t>
-  </si>
-  <si>
-    <t>— ок. XI века до н. э.Последний из великих судей Израилевых. Обладал силой, но был лишён дара видения и стратегического мышления</t>
-  </si>
-  <si>
-    <t>— XI век до н. э.Последний судья и первый крупный пророк Израиля. Путь от провидца до государственного стратега, руководившего военными действиями и помазанием царей.</t>
-  </si>
-  <si>
-    <t>— Внёс вклад в развитие научно-технологической стратегии СССР. Реализовал космические программы, позволившие СССР стать лидером космической гонки.</t>
-  </si>
-  <si>
-    <t>— царствовал ок. 970–931 до н. э. Сын Давида, построил Иерусалимский Храм. Символ того, как сбывшееся стратегическое предвидение воплощается в деяниях следующего поколения.</t>
-  </si>
-  <si>
-    <t>— Внёс вклад в развитие инновационной и технологической стратегии. Ставка на качество, дизайн и создание новых рынков. Превратил Apple в крупнейшую технологическую компанию.</t>
-  </si>
-  <si>
-    <t>— Завоеватель Константинополя. Использовал новые технологии, артиллерию и стратегическое планирование. Повлиял на развитие османской стратегии.</t>
-  </si>
-  <si>
-    <t>— Внёс вклад в развитие государственной и военной стратегии Османской империи. Достиг максимального могущества благодаря грамотному управлению и дипломатии</t>
-  </si>
-  <si>
-    <t>— ок. 155–220.Раннехристианский теолог. Квинт цитирует его парадокс «Верую, ибо абсурдно», подчеркивая роль иррационального в принятии стратегических решений.</t>
-  </si>
-  <si>
-    <t>— Внёс вклад в развитие военной истории и стратегической аналитики. Изучал деятельность великих полководцев, помогая развитию стратегического образования.</t>
-  </si>
-  <si>
-    <t>— 1910–1985. Американский экономист, нобелевский лауреат. Предложил сравнивать экономики по оргфункциям. Квинт считает подход широким, но недостаточным для стратегической классификации.</t>
-  </si>
-  <si>
-    <t>— Внёс вклад в развитие государственной и оборонной стратегии США. Занимался вопросами национальной безопасности и модернизации вооружённых сил.</t>
-  </si>
-  <si>
-    <t>— Внёс вклад в развитие военной стратегии и управления государством. Реформировал армию Пруссии, уделяя внимание дисциплине, скорости и маневрированию.</t>
-  </si>
-  <si>
-    <t>— Внёс большой вклад в развитие современной военной стратегии. Развивал идеи оперативного планирования, координации войск и использования железных дорог</t>
-  </si>
-  <si>
-    <t>— ок. 1035–970 до н. э. Второй царь Израиля. Успешный правитель и воин, но сам пророком не был. Приглашал провидцев в ближний круг, компенсируя отсутствие собственного дара предвидения</t>
-  </si>
-  <si>
-    <t>— правил ок. 1029–1009 до н. э. Первый царь Израиля. Его правление знаменует рубеж разделения функций правителя и пророка, важный этап в генезисе профессии стратега.</t>
-  </si>
-  <si>
-    <t>— Один из самых успешных стратегов благодаря мобильности армии, дисциплине и управлению территориями. Использовал разведку, психологическое воздействие и неожиданные атаки.</t>
-  </si>
-  <si>
-    <t>—  Внёс вклад в развитие цифровой стратегии Google. Под его руководством компания расширила направления деятельности и укрепила позиции на мировом рынке.</t>
-  </si>
-  <si>
-    <t>— 1828–1905.Французский писатель. Пример технического визионера: детально описал подводную лодку «Наутилус» задолго до её появления.</t>
-  </si>
-  <si>
-    <t>— 1779–1869.Генерал и теоретик. Квинт называет его основоположником, создавшим в 1817 году первую в мире теорию стратегии и сделавшим Россию родиной этой дисциплины.</t>
-  </si>
-  <si>
     <t xml:space="preserve">
 1. В стратегии нельзя полагаться только на здравый смысл
 2. В стратегии мнение большинства обычно ошибочно
@@ -1012,9 +550,6 @@
 15. Стратеги должны выявлять и ориентироваться на истинные потребности организации, а не на желания руководителей</t>
   </si>
   <si>
-    <t>— Создатель Общей теории стратегии и теории глобального формирующегося рынка. Под его руководством разработаны стратегии развития Санкт-Петербурга и Кузбасса до 2035 года. Иностранный член РАН, лауреат Госпремии Узбекистана. В апреле 2026 года получил звание почетного профессора Шанхайского университета, известен своим крылатым выражением: «Стратегия есть философия успеха».Он активно продвигает идею о том, что стратегическое мышление необходимо не только государствам и корпорациям, но и каждому человеку для построения успешной и осмысленной жизни.</t>
-  </si>
-  <si>
     <t>Дарел Тай Энген</t>
   </si>
   <si>
@@ -1204,34 +739,487 @@
     <t>https://ibb.co/LDCtjBCW</t>
   </si>
   <si>
-    <t xml:space="preserve"> - кент и духовный вдохновитель Кирилла Пинжина</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - контент-менеджер и аналитик прооекта. Отвечал за сбор материалов, изучение трудов академика В.Квинта, структурирование терминов и ведение базы данных в Excel.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> - главный разработчик проекта. Отвечал за написание кода в Python, интеграцию базы данных Excel, работу с GitHub и развёртывание бота на сервере Bothost.</t>
-  </si>
-  <si>
-    <r>
-      <t> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FFFFFFFF"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-        <charset val="204"/>
-      </rPr>
-      <t>путин, владимир путин, вв путин, президент, глава государства</t>
-    </r>
-  </si>
-  <si>
-    <t>Владимир Владимирович Путин — Президент Российской Федерации. В методологии стратегирования академика В. Квинта государственные стратегии, указы о национальных целях и стратегических приоритетах развития России, утверждаемые Президентом, являются высшей формой практического применения теории стратегии на макроуровне.</t>
-  </si>
-  <si>
     <t>http://static.kremlin.ru/media/events/press-photos/orig/FA1sRKf4WaYDSJjB4LjCZ0OjGc7qAFXh.jpg?kremlin-ru_photo-50.jpg</t>
+  </si>
+  <si>
+    <t>Владимир Владимирович Путин</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Президент Российской Федерации. В методологии стратегирования академика В. Квинта государственные стратегии, указы о национальных целях и стратегических приоритетах развития России, утверждаемые Президентом, являются высшей формой практического применения теории стратегии на макроуровне.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   метод сложения коэффициентов (P=ΣP×Wk), полезный только для оценки крайних значений (самых развитых или самых бедных стран).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  метод умножения коэффициентов (P=1000×ΠPkWk), более точный для малых экономик, где единичные инновации существенно влияют на эффективность.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  нестандартные решения для преимущества</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  состояние системы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  страны, квалифицированные по инициативе МВФ и Всемирного банка как неспособные выплатить свой долг.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> крупнейшие аудиторские фирмы мира: PricewaterhouseCoopers (PwC), Deloitte Touche, Ernst &amp; Young (EY) и KPMG.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  представление о будущем состоянии объекта</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  валовой национальный доход на человека, основа классификации Группы Всемирного банка для кредитных решений</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  усиление взаимосвязи экономик и рынков</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  совокупность мировых рынков</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> подсистема глобального миропорядка, каркас относительно стабильного сотрудничества бизнеса с глобальными, региональными и национальными институтами. Cтимулирует преимущественно эволюционное развитие глобального рыночного пространства.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> время даёт преимущество</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  повторяющиеся связи развития.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> реализуются только обеспеченные направления</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  первый и главный закон стратегии по Квинту; фактор времени является детерминирующим в стратегии</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> глобальные, национальные, региональные, корпоративные, индивидуальные</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> основа рейтинговых систем и индексов, на которых строятся классификационные системы стран и регионов</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> один из пяти показателей синтезированного странового рейтинга Квинта (относительная значимость 1,0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> один из пяти показателей синтезированного рейтинга (относительная значимость 0,7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> показатель, разработанный Квинтом на основе базы данных ЮНИДО для синтезированного рейтинга стран</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> источник преимуществ</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> объединение всех уровней</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> присутствие в стране международных банков, страховых компаний, аудиторов и юридических фирм, необходимое для входа на иностранный рынок</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ориентация на прошлое</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> группы, составляющие классификационную систему; внутри категорий также применяется рейтинговая система</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> факторы превосходства</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> доминирующая в России конца 2010-х модель, существенно отличающаяся как от государственного капитализма, так и от коммунизма</t>
+  </si>
+  <si>
+    <t>одна из трёх дополнительных категорий ООН, отражающая географическую специфику развития.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> псевдопредвидение в виде пророчеств, прорицаний, «откровений» и гаданий</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> фундаментальная цель и смысл существования объекта</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> слово из Торы, ассоциирующееся с мощным и точным видением таких великих лидеров, как Моисей и Самуил</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> система характеристик и внутренняя структура государства: политические, экономические, финансовые, технологические индикаторы, культурная и религиозная среда</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> слово из Торы, отображающее пророка-провидца без лидерских качеств.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> быстро формирующаяся технология, которая может стать основой беспрецедентно больших систем стратегических компетенций.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> категория ООН с 1971 года. Критерии: низкий доход (ВНД на душу населения), слабый человеческий капитал и экономическая уязвимость.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> информационно-познавательный аспект опережающего отражения как свойства высших форм материи.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> категория МВФ: Гонконг, Корея, Сингапур и Тайвань.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> интуитивное (связанное с подсознанием), обыденное (по народным приметам) и мантическое (пророчества, гадания) предвидение.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> категория, появившаяся благодаря европейским открытиям; несистематизированные территории, ставшие затем странами и регионами.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> сценарии будущего, в которых сталкиваются или кооперируют ценностные ориентиры, интересы и приоритеты субъектов стратегирования.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> термин древних греков для описания известного им мира с центром в Элладе; одна из первых попыток системного понимания мира</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> разработка действий.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> метод, используемый в рамках методологии стратегирования научной школы Квинта. Расшифровывается как Opportunities (Возможности), Threats (Угрозы), Strengths (Сильные стороны) и Weaknesses (Слабые стороны).</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> концепция Даниэля Канемана: «Мы думаем о нашем будущем как об ожидаемых воспоминаниях».</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> риск экспроприации, национализации и повреждения частной собственности иностранных лиц в странах с гражданскими волнениями.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> интеграция стратегии и тактики</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> результат понимания будущего.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> способность понимать будущее.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> сложное предвосхищение, вид интеллектуальной деятельности человека на основе личного опыта</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> простое предвосхищение, свойственное любому организму; одна из форм конкретизации предвидения.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ключевые направления развития</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> категория МВФ с 1997 года, объединяющая развитые страны и самые зрелые СФР (Южная Корея, Сингапур, Израиль)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> устаревшая категория МВФ, заменённая на «продвинутые экономики» из-за сокращения занятости в индустриальном производстве.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> научное определение будущего.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> люди, «видевшие» картины будущего. Их главная ценность для стратегов — традиция связывать пророчества со шкалой времени</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> интуитивное предвидение.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> редчайшее сочетание способностей провидца с лидерскими качествами практика (Моисей, Мухаммед)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> инвестиции компаний в зарубежные экономики. Новый тренд: ПИИ из СФР направляются в наукоёмкие отрасли развитых стран.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> решения, ведущие к далёкому будущему, всегда принимаемые на грани сознания и подсознания, рационального и иррационального.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> позиции, присваиваемые странам и регионам в рейтингах, индексах и внутри классификационных категорий.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> высшая стадия СФР (Южная Корея, Сингапур, Израиль, Гонконг, Испания, Португалия, Греция). Стратегически конкурируют с развитыми странами.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> вероятность потерь</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> средства для реализации стратегии.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> рейтинг технологического, экономического и социального развития стран на основе пяти индикаторов.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> мудрый дисциплинированный и оптимистичный профессионал, имеющий стратегическое мышление, видение будущего и интуицию, подкрепленную методологией стратегирования.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> классификационная категория, ядром которой стала цивилизация ойкумены к концу XV века.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> мудрые дисциплинированные и оптимистичные профессионалы, имеющие стратегическое мышление, видение будущего и интуицию, подкрепленную методологией стратегирования.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> способность принимать долгосрочные решения.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> система официальных взглядов и положений, устанавливающая направления долгосрочного развития объекта стратегирования.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> процесс формирования и функционирования системы стратегического управления, обеспечивающей разработку и долгосрочную реализацию стратегии, её доктрины, в соответствии с содержащимися в них конкурентными преимуществами, приоритетами, целями и задачами.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> контроль и корректировка стратегии.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> система поиска, формулирования и развития доктрины, обеспечивающей долгосрочный успех</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> один из альтернативных вариантов реализации стратегии. Как правило, разрабатывается не менее трёх сценариев, которые отличаются соотношением риска, асимметричности и общественно-экономической эффективности.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> концепция профессора Прахалада о заработке на беднейших слоях за счёт продажи малых упаковок товаров при высоком обороте.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> процесс разработки, реализации и обновления стратегии.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> категория восточноевропейских стран и СНГ. Квинт критикует её: логически все СФР и развивающиеся страны находятся в переходной стадии</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> одна из трёх дополнительных категорий ООН, отражающая географические ограничения развития.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> переходная стадия от развивающихся к СФР (Тунис, Монголия, Мадагаскар, Буркина Фасо).</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> сценарии, в которых сталкиваются или кооперируют ценностные ориентиры, интересы и приоритеты субъектов стратегирования.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> система текущих действий для реализации стратегии.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> теория систематизации и иерархических сфер действительности и знаний, созданная Карлом Линнеем в 1813 году.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> теория Канемана и Тверски о принятии решений в условиях высоких рисков, исключительно важная для стратегирования.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> термин, ассоциировавшийся с бедными неразвитыми странами. Большинство из них отклонили принципы свободного конкурентного рынка и стали беднее.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> устойчивые направления развития.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> негативные факторы.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> главная стратегическая угроза для России и ещё более 20 стран в XXI веке; депопуляция, игнорируемая в большинстве стратегических документов.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ключ к стратегическому преимуществу.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> неопределённость среды.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> показатель стратегического уровня развития. Северные страны обеспечивают наиболее устойчивую окружающую среду; страны с диктатурами замыкают рейтинг.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> конкретные ориентиры, размещённые во времени.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> стратегия Китая «Пять в одном»: посадка деревьев на четверти территории, восстановление 30% береговой линии, сокращение потребления угля на 40%.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Первый библейский патриарх и пророк. Отнесён к проактивным лидерам, чьё стратегическое предвидение направляло не только семью, но и целые поколения. Пример провидца, который действует, а не только созерцает.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Период: XIII век до н. э. Старший брат Моисея и Первый первосвященник. Квинт проводит границу: Аарон —  Моисей — пророк и стратег. Духовный сан и стратегическое лидерство — разные.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Внёс вклад в развитие государственной и военной стратегии Руси. Прославился грамотным использованием местности, дипломатией и способностью принимать стратегические решения в сложных условиях. Его победы и политика помогли сохранить независимость русских земель.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Один из величайших русских полководцев. Внёс вклад в развитие военной стратегии благодаря мобильности армии, быстроте принятия решений и нестандартным действиям. Его принципы подготовки войск и дисциплины стали важной частью военного стратегирования.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1937–1996.Психолог, соавтор Канемана. Их исследования ошибочных суждений и восприятия риска в условиях неопределённости Квинт считает критически важными для теории стратегирования.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> стратег и основатель Империи Тимуридов. Владимир Квинт посвятил его лидерству отдельную книгу. Главный принцип: успех государства зависит от привлечения талантливых людей («предприимчивых, мужественных и благоразумных»), ценность которых превышает ценность тысяч безвольных работников</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Герцог Веллингтон. Внёс вклад в развитие военной стратегии благодаря успешному противостоянию армии Наполеона. Уделял внимание дисциплине, подготовке армии и грамотному использованию местности.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ключевой стратег цифровой эпохи. Развивал программное обеспечение и сделал ставку на массовое распространение персональных компьютеров. Его решения сыграли большую роль в развитии мировой IT-индустрии</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> современный исследователь (XX–XXI вв.).Специалист по политэкономии Восточной Азии. Квинт цитирует его работы о связи авторитарной олигархии и экономической структуры стран ЮВА.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Создатель Общей теории стратегии и теории глобального формирующегося рынка. Под его руководством разработаны стратегии развития Санкт-Петербурга и Кузбасса до 2035 года. Иностранный член РАН, лауреат Госпремии Узбекистана. В апреле 2026 года получил звание почетного профессора Шанхайского университета, известен своим крылатым выражением: «Стратегия есть философия успеха».Он активно продвигает идею о том, что стратегическое мышление необходимо не только государствам и корпорациям, но и каждому человеку для построения успешной и осмысленной жизни.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Один из крупнейших полководцев XX века. Внёс вклад в развитие стратегического управления армией во время Второй мировой войны. Его решения в крупнейших операциях повлияли на советскую и мировую военную стратегию</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Один из великих библейских пророков. Его видения охватывали века. Квинт подчёркивает уникальную глубину его предсказаний, недоступную даже современному планированию. Эталон предвидения.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Современный американский историк экономики (XX–XXI вв.).Исследовал античные модели: свободное предпринимательство в Древней Греции и дворцовая монополия в Египте как два изначальных стратегических пути экономики.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Внёс вклад в развитие цифровой стратегии и интернет-торговли. Создал платформу Alibaba, сделав ставку на развитие онлайн-бизнеса и глобальной электронной коммерции.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Внёс вклад в развитие корпоративной стратегии. Руководя General Electric, внедрял инновации, оптимизацию процессов и долгосрочное планирование. Пример эффективного стратегического менеджмента.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Внёс вклад в развитие современной стратегической теории. Разработал концепцию OODA Loop (быстрый анализ ситуации и принятие решений). Идеи используются в военной стратегии, бизнесе и управлении.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1928–2005. Историк экономики, коллега Купманса. Предложил подход к сравнению экономических систем по организационным функциям, который Квинт рассматривает как важный шаг, но с ограничениями.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1667–1745.Англо-ирландский писатель. Квинт отмечает его предвидение: за полтора века до открытия Свифт описал два спутника Марса и их орбитальные параметры, почти совпавшие с реальностью.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Внёс огромный вклад в развитие экономической стратегии Китая. Провёл реформы, открывшие страну для мирового рынка. Благодаря этому Китай начал быстрое экономическое развитие</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ок. XIII–XII века до н. э. Преемник Моисея, завоеватель Ханаана. Квинт описывает его как образец военного стратега и полководца, а не пророка.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1927–2015. Советский и российский учёный, социолог и футуролог. Представитель отечественной школы, начавшей осмысливать процессы научного и ненаучного познания будущего</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Внёс значительный вклад в развитие византийской военной стратегии. Систематизировал знания о ведении войны и организации армии. Его труды стали основой для многих военных трактатов Средневековья.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Известен долгосрочным стратегическим видением и инновационным подходом. Развивает проекты в области космоса, электромобилей и ИИ. Стратегии основаны на высоких рисках и стремлении изменить будущее</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ок. XIII–XII века до н. э. (мифология).Троянская царевна с даром точного предвидения, но обречённая на то, что ей никто не верил. Символ трагедии провидца, лишённого стратегического влияния.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Один из главных теоретиков стратегии. В работе «О войне» рассматривал войну как продолжение политики. Его идеи оказали огромное влияние на современную военную и государственную стратегию</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ведущий специалист в области бизнес-стратегии. Изучал глобализацию и конкурентные преимущества. Его идеи повлияли на современное корпоративное стратегирование</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Сыграл важную роль в восстановлении Германии после Второй мировой войны. Использовал долгосрочное стратегическое планирование для укрепления экономики и международных отношений</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Развивал стратегические и тактические принципы Византии. Уделял внимание анализу военных действий и изучению опыта прошлых войн. Сохранил византийскую школу стратегирования</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Внёс вклад в развитие экономической и транспортной стратегии. Создал крупную транспортную империю, используя долгосрочное планирование и контроль инфраструктуры</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> правил 161–180. Римский император, философ-стоик. Уникальный пример сочетания императора, мудреца и стратега-провидца, не допускавшего ошибок от конфликта этих ролей.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1927–1997.Американский писатель, автор романа «Киборг». Предвосхитил появление бионических протезов, управляемых силой мысли</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Японский стратег и мастер боевых искусств. Разработал подход, основанный на дисциплине, психологическом превосходстве и анализе противника. Автор «Книги пяти колец».</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Американский экономист, профессор Стэнфорда. Автор методики рейтингования стран середины XX века. Квинт критикует его алгоритм сложения показателей за неточность.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  приблизительно XIII век до н. э.Библейский пророк и вождь. Квинт считает его величайшим провидцем-стратегом, сочетавшим дар предвидения и практическое лидерство, ведя народ сквозь хаос пустыни</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ок. 570–632. Основатель ислама и глава первого мусульманского государства. Редчайшая фигура, сочетавшая посланническую миссию и практическое стратегическое руководство</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> X век до н. э.Пророк при дворе царя Давида. Предвидел воцарение Соломона и строительство Храма. Пример стратегического совета провидца, определявшего государственные решения</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1769–1821.Император Франции и великий полководец. Активно использовал скорость, концентрацию сил и мобильность. Квинт анализирует поход 1812 года как трагедию выбора пути гибели без чёткого плана</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1503–1566.Французский врач и астролог. Квинт восхищается точностью ряда предсказаний, но делает вывод: Нострадамус — предсказатель, а не пророк.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1894–1963. Английский писатель, автор «О дивный новый мир». Предсказал генную инженерию и вмешательство в репродукцию задолго до появления технологий</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Мастер дипломатической стратегии. Объединил Германию благодаря продуманной политике, союзам и использованию международной обстановки. Пример долгосрочного государственного планирования.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Внёс большой вклад в развитие государственной и военной стратегии России. Провёл масштабные реформы армии, флота и управления. Укрепил международное положение России</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Уделял внимание реформированию армии и укреплению дисциплины. Стремился повысить эффективность вооружённых сил, что повлияло на дальнейшее развитие военной стратегии России.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> родился в 1930 году. Израильский математик, нобелевский лауреат. Вывод: в долгосрочных конфликтах выигрывает тот, кто ставит стратегию выше быстрой выгоды</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Внёс вклад в развитие национальной и военной стратегии Шотландии. Добился независимости страны благодаря грамотному использованию ресурсов и поддержке населения</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1941–2010.Профессор Мичиганского университета. Автор концепции «Дно пирамиды» (заработок на беднейших слоях за счёт малого товара и высокого оборота).</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ок. XI века до н. э.Последний из великих судей Израилевых. Обладал силой, но был лишён дара видения и стратегического мышления</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Внёс вклад в развитие научно-технологической стратегии СССР. Реализовал космические программы, позволившие СССР стать лидером космической гонки.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> XI век до н. э.Последний судья и первый крупный пророк Израиля. Путь от провидца до государственного стратега, руководившего военными действиями и помазанием царей.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Внёс вклад в развитие инновационной и технологической стратегии. Ставка на качество, дизайн и создание новых рынков. Превратил Apple в крупнейшую технологическую компанию.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> царствовал ок. 970–931 до н. э. Сын Давида, построил Иерусалимский Храм. Символ того, как сбывшееся стратегическое предвидение воплощается в деяниях следующего поколения.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Завоеватель Константинополя. Использовал новые технологии, артиллерию и стратегическое планирование. Повлиял на развитие османской стратегии.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Внёс вклад в развитие государственной и военной стратегии Османской империи. Достиг максимального могущества благодаря грамотному управлению и дипломатии</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ок. 155–220.Раннехристианский теолог. Квинт цитирует его парадокс «Верую, ибо абсурдно», подчеркивая роль иррационального в принятии стратегических решений.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Внёс вклад в развитие военной истории и стратегической аналитики. Изучал деятельность великих полководцев, помогая развитию стратегического образования.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1910–1985. Американский экономист, нобелевский лауреат. Предложил сравнивать экономики по оргфункциям. Квинт считает подход широким, но недостаточным для стратегической классификации.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Внёс вклад в развитие государственной и оборонной стратегии США. Занимался вопросами национальной безопасности и модернизации вооружённых сил.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Внёс вклад в развитие военной стратегии и управления государством. Реформировал армию Пруссии, уделяя внимание дисциплине, скорости и маневрированию.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Внёс большой вклад в развитие современной военной стратегии. Развивал идеи оперативного планирования, координации войск и использования железных дорог</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ок. 1035–970 до н. э. Второй царь Израиля. Успешный правитель и воин, но сам пророком не был. Приглашал провидцев в ближний круг, компенсируя отсутствие собственного дара предвидения</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> правил ок. 1029–1009 до н. э. Первый царь Израиля. Его правление знаменует рубеж разделения функций правителя и пророка, важный этап в генезисе профессии стратега.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Один из самых успешных стратегов благодаря мобильности армии, дисциплине и управлению территориями. Использовал разведку, психологическое воздействие и неожиданные атаки.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Внёс вклад в развитие цифровой стратегии Google. Под его руководством компания расширила направления деятельности и укрепила позиции на мировом рынке.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1828–1905.Французский писатель. Пример технического визионера: детально описал подводную лодку «Наутилус» задолго до её появления.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1779–1869.Генерал и теоретик. Квинт называет его основоположником, создавшим в 1817 году первую в мире теорию стратегии и сделавшим Россию родиной этой дисциплины.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> главный разработчик проекта. Отвечал за написание кода в Python, интеграцию базы данных Excel, работу с GitHub и развёртывание бота на сервере Bothost.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> контент-менеджер и аналитик прооекта. Отвечал за сбор материалов, изучение трудов академика В.Квинта, структурирование терминов и ведение базы данных в Excel.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> кент и духовный вдохновитель Кирилла Пинжина</t>
   </si>
 </sst>
 </file>
@@ -1668,7 +1656,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>164</v>
+        <v>231</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1676,7 +1664,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>165</v>
+        <v>232</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1684,7 +1672,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>166</v>
+        <v>233</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1692,7 +1680,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>167</v>
+        <v>234</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1700,7 +1688,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>168</v>
+        <v>235</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1708,7 +1696,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>169</v>
+        <v>236</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -1716,7 +1704,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>170</v>
+        <v>237</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -1724,7 +1712,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>171</v>
+        <v>238</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -1732,7 +1720,7 @@
         <v>152</v>
       </c>
       <c r="B10" t="s">
-        <v>172</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -1740,7 +1728,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>173</v>
+        <v>240</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1748,7 +1736,7 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>174</v>
+        <v>241</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
@@ -1756,7 +1744,7 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>175</v>
+        <v>243</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
@@ -1764,7 +1752,7 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>176</v>
+        <v>242</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -1772,7 +1760,7 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>177</v>
+        <v>244</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
@@ -1780,7 +1768,7 @@
         <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>178</v>
+        <v>245</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -1788,7 +1776,7 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>179</v>
+        <v>246</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -1796,7 +1784,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>180</v>
+        <v>247</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -1804,7 +1792,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>181</v>
+        <v>248</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -1812,7 +1800,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>182</v>
+        <v>249</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -1820,7 +1808,7 @@
         <v>18</v>
       </c>
       <c r="B21" t="s">
-        <v>183</v>
+        <v>250</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -1828,7 +1816,7 @@
         <v>18</v>
       </c>
       <c r="B22" t="s">
-        <v>184</v>
+        <v>251</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -1836,7 +1824,7 @@
         <v>19</v>
       </c>
       <c r="B23" t="s">
-        <v>185</v>
+        <v>252</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -1844,7 +1832,7 @@
         <v>20</v>
       </c>
       <c r="B24" t="s">
-        <v>186</v>
+        <v>253</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -1852,7 +1840,7 @@
         <v>21</v>
       </c>
       <c r="B25" t="s">
-        <v>187</v>
+        <v>254</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -1860,7 +1848,7 @@
         <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>188</v>
+        <v>255</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -1868,7 +1856,7 @@
         <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>189</v>
+        <v>256</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
@@ -1876,7 +1864,7 @@
         <v>24</v>
       </c>
       <c r="B28" t="s">
-        <v>190</v>
+        <v>257</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
@@ -1884,7 +1872,7 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>191</v>
+        <v>258</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
@@ -1892,7 +1880,7 @@
         <v>26</v>
       </c>
       <c r="B30" t="s">
-        <v>192</v>
+        <v>259</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
@@ -1900,7 +1888,7 @@
         <v>27</v>
       </c>
       <c r="B31" t="s">
-        <v>193</v>
+        <v>260</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
@@ -1908,7 +1896,7 @@
         <v>28</v>
       </c>
       <c r="B32" t="s">
-        <v>194</v>
+        <v>262</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
@@ -1916,7 +1904,7 @@
         <v>29</v>
       </c>
       <c r="B33" t="s">
-        <v>195</v>
+        <v>261</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
@@ -1924,7 +1912,7 @@
         <v>30</v>
       </c>
       <c r="B34" t="s">
-        <v>196</v>
+        <v>263</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
@@ -1932,7 +1920,7 @@
         <v>31</v>
       </c>
       <c r="B35" t="s">
-        <v>197</v>
+        <v>265</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
@@ -1940,7 +1928,7 @@
         <v>32</v>
       </c>
       <c r="B36" t="s">
-        <v>198</v>
+        <v>264</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
@@ -1948,7 +1936,7 @@
         <v>33</v>
       </c>
       <c r="B37" t="s">
-        <v>199</v>
+        <v>266</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
@@ -1956,7 +1944,7 @@
         <v>34</v>
       </c>
       <c r="B38" t="s">
-        <v>200</v>
+        <v>267</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
@@ -1964,7 +1952,7 @@
         <v>35</v>
       </c>
       <c r="B39" t="s">
-        <v>201</v>
+        <v>268</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
@@ -1972,7 +1960,7 @@
         <v>36</v>
       </c>
       <c r="B40" t="s">
-        <v>202</v>
+        <v>269</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
@@ -1980,7 +1968,7 @@
         <v>37</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
@@ -1988,7 +1976,7 @@
         <v>38</v>
       </c>
       <c r="B42" t="s">
-        <v>204</v>
+        <v>274</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
@@ -1996,7 +1984,7 @@
         <v>39</v>
       </c>
       <c r="B43" t="s">
-        <v>205</v>
+        <v>271</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
@@ -2004,7 +1992,7 @@
         <v>40</v>
       </c>
       <c r="B44" t="s">
-        <v>206</v>
+        <v>273</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
@@ -2012,7 +2000,7 @@
         <v>41</v>
       </c>
       <c r="B45" t="s">
-        <v>207</v>
+        <v>272</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
@@ -2020,7 +2008,7 @@
         <v>42</v>
       </c>
       <c r="B46" t="s">
-        <v>208</v>
+        <v>276</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
@@ -2028,7 +2016,7 @@
         <v>43</v>
       </c>
       <c r="B47" t="s">
-        <v>209</v>
+        <v>275</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
@@ -2036,7 +2024,7 @@
         <v>44</v>
       </c>
       <c r="B48" t="s">
-        <v>210</v>
+        <v>278</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
@@ -2044,7 +2032,7 @@
         <v>45</v>
       </c>
       <c r="B49" t="s">
-        <v>211</v>
+        <v>277</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
@@ -2052,7 +2040,7 @@
         <v>46</v>
       </c>
       <c r="B50" t="s">
-        <v>212</v>
+        <v>279</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
@@ -2060,7 +2048,7 @@
         <v>47</v>
       </c>
       <c r="B51" t="s">
-        <v>213</v>
+        <v>280</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
@@ -2068,7 +2056,7 @@
         <v>48</v>
       </c>
       <c r="B52" t="s">
-        <v>214</v>
+        <v>281</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
@@ -2076,7 +2064,7 @@
         <v>49</v>
       </c>
       <c r="B53" t="s">
-        <v>215</v>
+        <v>282</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
@@ -2084,7 +2072,7 @@
         <v>50</v>
       </c>
       <c r="B54" t="s">
-        <v>216</v>
+        <v>284</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
@@ -2092,7 +2080,7 @@
         <v>51</v>
       </c>
       <c r="B55" t="s">
-        <v>217</v>
+        <v>283</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
@@ -2100,7 +2088,7 @@
         <v>52</v>
       </c>
       <c r="B56" t="s">
-        <v>218</v>
+        <v>286</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
@@ -2108,7 +2096,7 @@
         <v>153</v>
       </c>
       <c r="B57" t="s">
-        <v>219</v>
+        <v>285</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
@@ -2116,7 +2104,7 @@
         <v>53</v>
       </c>
       <c r="B58" t="s">
-        <v>220</v>
+        <v>287</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
@@ -2124,7 +2112,7 @@
         <v>54</v>
       </c>
       <c r="B59" t="s">
-        <v>221</v>
+        <v>288</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
@@ -2132,7 +2120,7 @@
         <v>55</v>
       </c>
       <c r="B60" t="s">
-        <v>222</v>
+        <v>289</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
@@ -2140,7 +2128,7 @@
         <v>56</v>
       </c>
       <c r="B61" t="s">
-        <v>223</v>
+        <v>290</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
@@ -2148,7 +2136,7 @@
         <v>57</v>
       </c>
       <c r="B62" t="s">
-        <v>224</v>
+        <v>291</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
@@ -2156,7 +2144,7 @@
         <v>58</v>
       </c>
       <c r="B63" t="s">
-        <v>225</v>
+        <v>293</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
@@ -2164,7 +2152,7 @@
         <v>59</v>
       </c>
       <c r="B64" t="s">
-        <v>226</v>
+        <v>292</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
@@ -2172,7 +2160,7 @@
         <v>60</v>
       </c>
       <c r="B65" t="s">
-        <v>227</v>
+        <v>294</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
@@ -2180,7 +2168,7 @@
         <v>61</v>
       </c>
       <c r="B66" t="s">
-        <v>228</v>
+        <v>296</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
@@ -2188,7 +2176,7 @@
         <v>62</v>
       </c>
       <c r="B67" t="s">
-        <v>229</v>
+        <v>295</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
@@ -2196,7 +2184,7 @@
         <v>63</v>
       </c>
       <c r="B68" t="s">
-        <v>230</v>
+        <v>297</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
@@ -2204,7 +2192,7 @@
         <v>64</v>
       </c>
       <c r="B69" t="s">
-        <v>231</v>
+        <v>299</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
@@ -2212,7 +2200,7 @@
         <v>65</v>
       </c>
       <c r="B70" t="s">
-        <v>232</v>
+        <v>298</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
@@ -2220,7 +2208,7 @@
         <v>66</v>
       </c>
       <c r="B71" t="s">
-        <v>233</v>
+        <v>300</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
@@ -2228,7 +2216,7 @@
         <v>67</v>
       </c>
       <c r="B72" t="s">
-        <v>234</v>
+        <v>301</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
@@ -2236,7 +2224,7 @@
         <v>68</v>
       </c>
       <c r="B73" t="s">
-        <v>235</v>
+        <v>303</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
@@ -2244,7 +2232,7 @@
         <v>69</v>
       </c>
       <c r="B74" t="s">
-        <v>236</v>
+        <v>302</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
@@ -2252,7 +2240,7 @@
         <v>70</v>
       </c>
       <c r="B75" t="s">
-        <v>237</v>
+        <v>304</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
@@ -2260,7 +2248,7 @@
         <v>71</v>
       </c>
       <c r="B76" t="s">
-        <v>238</v>
+        <v>305</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
@@ -2268,7 +2256,7 @@
         <v>72</v>
       </c>
       <c r="B77" t="s">
-        <v>239</v>
+        <v>307</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
@@ -2276,7 +2264,7 @@
         <v>73</v>
       </c>
       <c r="B78" t="s">
-        <v>240</v>
+        <v>306</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
@@ -2284,7 +2272,7 @@
         <v>74</v>
       </c>
       <c r="B79" t="s">
-        <v>241</v>
+        <v>308</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
@@ -2292,7 +2280,7 @@
         <v>75</v>
       </c>
       <c r="B80" t="s">
-        <v>242</v>
+        <v>309</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
@@ -2300,7 +2288,7 @@
         <v>76</v>
       </c>
       <c r="B81" t="s">
-        <v>243</v>
+        <v>310</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
@@ -2308,7 +2296,7 @@
         <v>77</v>
       </c>
       <c r="B82" t="s">
-        <v>244</v>
+        <v>311</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
@@ -2316,7 +2304,7 @@
         <v>78</v>
       </c>
       <c r="B83" t="s">
-        <v>245</v>
+        <v>312</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
@@ -2324,7 +2312,7 @@
         <v>79</v>
       </c>
       <c r="B84" t="s">
-        <v>246</v>
+        <v>313</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
@@ -2332,7 +2320,7 @@
         <v>80</v>
       </c>
       <c r="B85" t="s">
-        <v>247</v>
+        <v>314</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
@@ -2340,7 +2328,7 @@
         <v>81</v>
       </c>
       <c r="B86" t="s">
-        <v>248</v>
+        <v>315</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
@@ -2348,7 +2336,7 @@
         <v>82</v>
       </c>
       <c r="B87" t="s">
-        <v>249</v>
+        <v>317</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
@@ -2356,7 +2344,7 @@
         <v>83</v>
       </c>
       <c r="B88" t="s">
-        <v>250</v>
+        <v>316</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
@@ -2364,7 +2352,7 @@
         <v>84</v>
       </c>
       <c r="B89" t="s">
-        <v>251</v>
+        <v>318</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
@@ -2372,7 +2360,7 @@
         <v>85</v>
       </c>
       <c r="B90" t="s">
-        <v>252</v>
+        <v>320</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
@@ -2380,7 +2368,7 @@
         <v>86</v>
       </c>
       <c r="B91" t="s">
-        <v>253</v>
+        <v>319</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
@@ -2388,7 +2376,7 @@
         <v>87</v>
       </c>
       <c r="B92" t="s">
-        <v>254</v>
+        <v>321</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
@@ -2396,10 +2384,10 @@
         <v>89</v>
       </c>
       <c r="B93" t="s">
-        <v>255</v>
+        <v>322</v>
       </c>
       <c r="C93" s="14" t="s">
-        <v>321</v>
+        <v>166</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
@@ -2407,10 +2395,10 @@
         <v>90</v>
       </c>
       <c r="B94" t="s">
-        <v>256</v>
+        <v>323</v>
       </c>
       <c r="C94" s="14" t="s">
-        <v>322</v>
+        <v>167</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
@@ -2418,10 +2406,10 @@
         <v>91</v>
       </c>
       <c r="B95" t="s">
-        <v>257</v>
+        <v>324</v>
       </c>
       <c r="C95" s="14" t="s">
-        <v>323</v>
+        <v>168</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
@@ -2429,10 +2417,10 @@
         <v>92</v>
       </c>
       <c r="B96" t="s">
-        <v>258</v>
+        <v>325</v>
       </c>
       <c r="C96" s="14" t="s">
-        <v>324</v>
+        <v>169</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
@@ -2440,10 +2428,10 @@
         <v>93</v>
       </c>
       <c r="B97" t="s">
-        <v>259</v>
+        <v>326</v>
       </c>
       <c r="C97" s="14" t="s">
-        <v>325</v>
+        <v>170</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
@@ -2451,10 +2439,10 @@
         <v>94</v>
       </c>
       <c r="B98" t="s">
-        <v>260</v>
+        <v>327</v>
       </c>
       <c r="C98" s="14" t="s">
-        <v>326</v>
+        <v>171</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
@@ -2462,10 +2450,10 @@
         <v>95</v>
       </c>
       <c r="B99" t="s">
-        <v>261</v>
+        <v>328</v>
       </c>
       <c r="C99" s="14" t="s">
-        <v>327</v>
+        <v>172</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
@@ -2473,10 +2461,10 @@
         <v>96</v>
       </c>
       <c r="B100" t="s">
-        <v>262</v>
+        <v>330</v>
       </c>
       <c r="C100" s="14" t="s">
-        <v>328</v>
+        <v>173</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
@@ -2484,10 +2472,10 @@
         <v>97</v>
       </c>
       <c r="B101" t="s">
-        <v>263</v>
+        <v>329</v>
       </c>
       <c r="C101" s="14" t="s">
-        <v>329</v>
+        <v>174</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
@@ -2495,10 +2483,10 @@
         <v>98</v>
       </c>
       <c r="B102" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="C102" s="14" t="s">
-        <v>330</v>
+        <v>175</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
@@ -2506,10 +2494,10 @@
         <v>99</v>
       </c>
       <c r="B103" t="s">
-        <v>264</v>
+        <v>332</v>
       </c>
       <c r="C103" s="14" t="s">
-        <v>331</v>
+        <v>176</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
@@ -2517,18 +2505,18 @@
         <v>100</v>
       </c>
       <c r="B104" t="s">
-        <v>265</v>
+        <v>333</v>
       </c>
       <c r="C104" s="14" t="s">
-        <v>381</v>
+        <v>226</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="9" t="s">
-        <v>320</v>
+        <v>165</v>
       </c>
       <c r="B105" t="s">
-        <v>266</v>
+        <v>334</v>
       </c>
       <c r="C105" s="14"/>
     </row>
@@ -2537,10 +2525,10 @@
         <v>101</v>
       </c>
       <c r="B106" t="s">
-        <v>267</v>
+        <v>335</v>
       </c>
       <c r="C106" s="14" t="s">
-        <v>332</v>
+        <v>177</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
@@ -2548,10 +2536,10 @@
         <v>102</v>
       </c>
       <c r="B107" t="s">
-        <v>268</v>
+        <v>336</v>
       </c>
       <c r="C107" s="14" t="s">
-        <v>333</v>
+        <v>178</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
@@ -2559,10 +2547,10 @@
         <v>103</v>
       </c>
       <c r="B108" t="s">
-        <v>269</v>
+        <v>337</v>
       </c>
       <c r="C108" s="14" t="s">
-        <v>334</v>
+        <v>179</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
@@ -2570,10 +2558,10 @@
         <v>104</v>
       </c>
       <c r="B109" t="s">
-        <v>270</v>
+        <v>338</v>
       </c>
       <c r="C109" s="14" t="s">
-        <v>335</v>
+        <v>180</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
@@ -2581,10 +2569,10 @@
         <v>105</v>
       </c>
       <c r="B110" t="s">
-        <v>271</v>
+        <v>339</v>
       </c>
       <c r="C110" s="14" t="s">
-        <v>336</v>
+        <v>181</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
@@ -2592,10 +2580,10 @@
         <v>106</v>
       </c>
       <c r="B111" t="s">
-        <v>272</v>
+        <v>340</v>
       </c>
       <c r="C111" s="14" t="s">
-        <v>337</v>
+        <v>182</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
@@ -2603,10 +2591,10 @@
         <v>107</v>
       </c>
       <c r="B112" t="s">
-        <v>273</v>
+        <v>342</v>
       </c>
       <c r="C112" s="14" t="s">
-        <v>338</v>
+        <v>183</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
@@ -2614,10 +2602,10 @@
         <v>108</v>
       </c>
       <c r="B113" t="s">
-        <v>274</v>
+        <v>341</v>
       </c>
       <c r="C113" s="14" t="s">
-        <v>339</v>
+        <v>184</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
@@ -2625,10 +2613,10 @@
         <v>109</v>
       </c>
       <c r="B114" t="s">
-        <v>275</v>
+        <v>344</v>
       </c>
       <c r="C114" s="14" t="s">
-        <v>340</v>
+        <v>185</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
@@ -2636,10 +2624,10 @@
         <v>110</v>
       </c>
       <c r="B115" t="s">
-        <v>276</v>
+        <v>343</v>
       </c>
       <c r="C115" s="14" t="s">
-        <v>341</v>
+        <v>186</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
@@ -2647,10 +2635,10 @@
         <v>111</v>
       </c>
       <c r="B116" t="s">
-        <v>277</v>
+        <v>345</v>
       </c>
       <c r="C116" s="14" t="s">
-        <v>342</v>
+        <v>187</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
@@ -2658,10 +2646,10 @@
         <v>112</v>
       </c>
       <c r="B117" t="s">
-        <v>278</v>
+        <v>346</v>
       </c>
       <c r="C117" s="14" t="s">
-        <v>343</v>
+        <v>188</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
@@ -2669,10 +2657,10 @@
         <v>113</v>
       </c>
       <c r="B118" t="s">
-        <v>279</v>
+        <v>347</v>
       </c>
       <c r="C118" s="14" t="s">
-        <v>344</v>
+        <v>189</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
@@ -2680,10 +2668,10 @@
         <v>114</v>
       </c>
       <c r="B119" t="s">
-        <v>280</v>
+        <v>348</v>
       </c>
       <c r="C119" s="14" t="s">
-        <v>345</v>
+        <v>190</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
@@ -2691,10 +2679,10 @@
         <v>115</v>
       </c>
       <c r="B120" t="s">
-        <v>281</v>
+        <v>350</v>
       </c>
       <c r="C120" s="14" t="s">
-        <v>346</v>
+        <v>191</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
@@ -2702,10 +2690,10 @@
         <v>116</v>
       </c>
       <c r="B121" t="s">
-        <v>282</v>
+        <v>349</v>
       </c>
       <c r="C121" s="14" t="s">
-        <v>347</v>
+        <v>192</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
@@ -2713,10 +2701,10 @@
         <v>117</v>
       </c>
       <c r="B122" t="s">
-        <v>283</v>
+        <v>351</v>
       </c>
       <c r="C122" s="14" t="s">
-        <v>348</v>
+        <v>193</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
@@ -2724,10 +2712,10 @@
         <v>118</v>
       </c>
       <c r="B123" t="s">
-        <v>284</v>
+        <v>352</v>
       </c>
       <c r="C123" s="14" t="s">
-        <v>381</v>
+        <v>226</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
@@ -2735,7 +2723,7 @@
         <v>119</v>
       </c>
       <c r="B124" t="s">
-        <v>285</v>
+        <v>354</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
@@ -2743,10 +2731,10 @@
         <v>120</v>
       </c>
       <c r="B125" t="s">
-        <v>286</v>
+        <v>353</v>
       </c>
       <c r="C125" s="14" t="s">
-        <v>349</v>
+        <v>194</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
@@ -2754,10 +2742,10 @@
         <v>121</v>
       </c>
       <c r="B126" t="s">
-        <v>287</v>
+        <v>355</v>
       </c>
       <c r="C126" s="14" t="s">
-        <v>350</v>
+        <v>195</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
@@ -2765,10 +2753,10 @@
         <v>122</v>
       </c>
       <c r="B127" t="s">
-        <v>288</v>
+        <v>356</v>
       </c>
       <c r="C127" s="14" t="s">
-        <v>351</v>
+        <v>196</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
@@ -2776,10 +2764,10 @@
         <v>123</v>
       </c>
       <c r="B128" t="s">
-        <v>289</v>
+        <v>357</v>
       </c>
       <c r="C128" s="14" t="s">
-        <v>352</v>
+        <v>197</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
@@ -2787,10 +2775,10 @@
         <v>124</v>
       </c>
       <c r="B129" t="s">
-        <v>290</v>
+        <v>358</v>
       </c>
       <c r="C129" s="14" t="s">
-        <v>353</v>
+        <v>198</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
@@ -2798,10 +2786,10 @@
         <v>125</v>
       </c>
       <c r="B130" t="s">
-        <v>291</v>
+        <v>359</v>
       </c>
       <c r="C130" s="14" t="s">
-        <v>354</v>
+        <v>199</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
@@ -2809,10 +2797,10 @@
         <v>126</v>
       </c>
       <c r="B131" t="s">
-        <v>292</v>
+        <v>360</v>
       </c>
       <c r="C131" s="14" t="s">
-        <v>355</v>
+        <v>200</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
@@ -2820,10 +2808,10 @@
         <v>127</v>
       </c>
       <c r="B132" t="s">
-        <v>293</v>
+        <v>361</v>
       </c>
       <c r="C132" s="14" t="s">
-        <v>356</v>
+        <v>201</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
@@ -2831,10 +2819,10 @@
         <v>128</v>
       </c>
       <c r="B133" t="s">
-        <v>294</v>
+        <v>363</v>
       </c>
       <c r="C133" s="14" t="s">
-        <v>357</v>
+        <v>202</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
@@ -2842,10 +2830,10 @@
         <v>129</v>
       </c>
       <c r="B134" t="s">
-        <v>295</v>
+        <v>362</v>
       </c>
       <c r="C134" s="14" t="s">
-        <v>358</v>
+        <v>203</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
@@ -2853,10 +2841,10 @@
         <v>130</v>
       </c>
       <c r="B135" t="s">
-        <v>296</v>
+        <v>364</v>
       </c>
       <c r="C135" s="14" t="s">
-        <v>359</v>
+        <v>204</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
@@ -2864,10 +2852,10 @@
         <v>131</v>
       </c>
       <c r="B136" t="s">
-        <v>297</v>
+        <v>365</v>
       </c>
       <c r="C136" s="14" t="s">
-        <v>360</v>
+        <v>205</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
@@ -2875,10 +2863,10 @@
         <v>154</v>
       </c>
       <c r="B137" t="s">
-        <v>298</v>
+        <v>366</v>
       </c>
       <c r="C137" s="14" t="s">
-        <v>361</v>
+        <v>206</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
@@ -2886,10 +2874,10 @@
         <v>132</v>
       </c>
       <c r="B138" t="s">
-        <v>299</v>
+        <v>367</v>
       </c>
       <c r="C138" s="14" t="s">
-        <v>362</v>
+        <v>207</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
@@ -2897,10 +2885,10 @@
         <v>133</v>
       </c>
       <c r="B139" t="s">
-        <v>300</v>
+        <v>369</v>
       </c>
       <c r="C139" s="14" t="s">
-        <v>363</v>
+        <v>208</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
@@ -2908,10 +2896,10 @@
         <v>134</v>
       </c>
       <c r="B140" t="s">
-        <v>301</v>
+        <v>368</v>
       </c>
       <c r="C140" s="14" t="s">
-        <v>364</v>
+        <v>209</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
@@ -2919,10 +2907,10 @@
         <v>135</v>
       </c>
       <c r="B141" t="s">
-        <v>302</v>
+        <v>371</v>
       </c>
       <c r="C141" s="14" t="s">
-        <v>366</v>
+        <v>211</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
@@ -2930,10 +2918,10 @@
         <v>136</v>
       </c>
       <c r="B142" t="s">
-        <v>303</v>
+        <v>370</v>
       </c>
       <c r="C142" s="14" t="s">
-        <v>380</v>
+        <v>225</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
@@ -2941,10 +2929,10 @@
         <v>137</v>
       </c>
       <c r="B143" t="s">
-        <v>304</v>
+        <v>372</v>
       </c>
       <c r="C143" s="14" t="s">
-        <v>365</v>
+        <v>210</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
@@ -2952,10 +2940,10 @@
         <v>138</v>
       </c>
       <c r="B144" t="s">
-        <v>305</v>
+        <v>373</v>
       </c>
       <c r="C144" s="14" t="s">
-        <v>367</v>
+        <v>212</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
@@ -2963,10 +2951,10 @@
         <v>139</v>
       </c>
       <c r="B145" t="s">
-        <v>306</v>
+        <v>374</v>
       </c>
       <c r="C145" s="14" t="s">
-        <v>368</v>
+        <v>213</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
@@ -2974,10 +2962,10 @@
         <v>155</v>
       </c>
       <c r="B146" t="s">
-        <v>307</v>
+        <v>375</v>
       </c>
       <c r="C146" s="14" t="s">
-        <v>369</v>
+        <v>214</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
@@ -2985,10 +2973,10 @@
         <v>140</v>
       </c>
       <c r="B147" t="s">
-        <v>308</v>
+        <v>376</v>
       </c>
       <c r="C147" s="14" t="s">
-        <v>370</v>
+        <v>215</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
@@ -2996,10 +2984,10 @@
         <v>141</v>
       </c>
       <c r="B148" t="s">
-        <v>309</v>
+        <v>377</v>
       </c>
       <c r="C148" s="14" t="s">
-        <v>371</v>
+        <v>216</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
@@ -3007,10 +2995,10 @@
         <v>142</v>
       </c>
       <c r="B149" t="s">
-        <v>310</v>
+        <v>378</v>
       </c>
       <c r="C149" s="14" t="s">
-        <v>372</v>
+        <v>217</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
@@ -3018,10 +3006,10 @@
         <v>143</v>
       </c>
       <c r="B150" t="s">
-        <v>311</v>
+        <v>379</v>
       </c>
       <c r="C150" s="14" t="s">
-        <v>373</v>
+        <v>218</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
@@ -3029,10 +3017,10 @@
         <v>144</v>
       </c>
       <c r="B151" t="s">
-        <v>312</v>
+        <v>380</v>
       </c>
       <c r="C151" s="14" t="s">
-        <v>374</v>
+        <v>219</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
@@ -3040,10 +3028,10 @@
         <v>145</v>
       </c>
       <c r="B152" t="s">
-        <v>313</v>
+        <v>381</v>
       </c>
       <c r="C152" s="14" t="s">
-        <v>375</v>
+        <v>220</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
@@ -3051,10 +3039,10 @@
         <v>146</v>
       </c>
       <c r="B153" t="s">
-        <v>314</v>
+        <v>382</v>
       </c>
       <c r="C153" s="14" t="s">
-        <v>376</v>
+        <v>221</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
@@ -3062,10 +3050,10 @@
         <v>147</v>
       </c>
       <c r="B154" t="s">
-        <v>315</v>
+        <v>383</v>
       </c>
       <c r="C154" s="14" t="s">
-        <v>377</v>
+        <v>222</v>
       </c>
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
@@ -3073,10 +3061,10 @@
         <v>148</v>
       </c>
       <c r="B155" t="s">
-        <v>316</v>
+        <v>384</v>
       </c>
       <c r="C155" s="14" t="s">
-        <v>378</v>
+        <v>223</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
@@ -3084,10 +3072,10 @@
         <v>149</v>
       </c>
       <c r="B156" t="s">
-        <v>317</v>
+        <v>385</v>
       </c>
       <c r="C156" s="14" t="s">
-        <v>379</v>
+        <v>224</v>
       </c>
     </row>
     <row r="157" spans="1:3" ht="240" x14ac:dyDescent="0.25">
@@ -3095,7 +3083,7 @@
         <v>88</v>
       </c>
       <c r="B157" s="13" t="s">
-        <v>318</v>
+        <v>164</v>
       </c>
     </row>
     <row r="158" spans="1:3" ht="30" x14ac:dyDescent="0.25">
@@ -3111,7 +3099,7 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C159" t="s">
         <v>159</v>
@@ -3122,7 +3110,7 @@
         <v>162</v>
       </c>
       <c r="B160" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="C160" t="s">
         <v>160</v>
@@ -3133,21 +3121,21 @@
         <v>161</v>
       </c>
       <c r="B161" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="C161" s="14" t="s">
-        <v>382</v>
+        <v>227</v>
       </c>
     </row>
     <row r="162" spans="1:3" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A162" s="16" t="s">
-        <v>386</v>
+        <v>229</v>
       </c>
       <c r="B162" s="17" t="s">
-        <v>387</v>
+        <v>230</v>
       </c>
       <c r="C162" t="s">
-        <v>388</v>
+        <v>228</v>
       </c>
     </row>
   </sheetData>

--- a/database.xlsx
+++ b/database.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="391" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="395">
   <si>
     <t xml:space="preserve">Алгоритм Беннетта </t>
   </si>
@@ -1219,14 +1219,59 @@
     <t xml:space="preserve"> контент-менеджер и аналитик прооекта. Отвечал за сбор материалов, изучение трудов академика В.Квинта, структурирование терминов и ведение базы данных в Excel.</t>
   </si>
   <si>
-    <t xml:space="preserve"> кент и духовный вдохновитель Кирилла Пинжина</t>
+    <t xml:space="preserve"> друг и духовный вдохновитель Кирилла Пинжина</t>
+  </si>
+  <si>
+    <t>Даниэль Канеман</t>
+  </si>
+  <si>
+    <t>Платон</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">В теории и методологии стратегирования академика Владимира Квинта идеи нобелевского лауреата </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t>Даниэля Канемана занимают фундаментальное место при исследовании психологическихаспектов принятия стратегических решений, оценки рисков и человеческой иррациональности</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>. В. Л. Квинт активно интегрирует поведенческую экономику в свою общую теорию стратегии. [1, 2, 3, 4]</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Платон заложил онтологический фундамент стратегии, обосновав необходимость долгосрочного планирования через несовершенство мира.
+Владимир Квинт выделяет две ключевые платоновские идеи:
+• Несовершенство мира как стимул: Так как текущая реальность несовершенна, возникает потребность в её улучшении — это и есть главная цель любой стратегии.
+• Вторичность текущих фактов: Настоящее мимолётно, поэтому стратег должен смотреть сквозь сегодняшние проблемы, ориентируясь на глобальные тренды будущего.
+</t>
+  </si>
+  <si>
+    <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wCEAAkGBwgHBgkIBwgKCgkLDRYPDQwMDRsUFRAWIB0iIiAdHx8kKDQsJCYxJx8fLT0tMTU3Ojo6Iys/RD84QzQ5OjcBCgoKDQwNGg8PGjclHyU3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3N//AABEIAJQAwAMBIgACEQEDEQH/xAAbAAACAwEBAQAAAAAAAAAAAAADBAIFBgABB//EADoQAAIBAwMBBgQFAwQABwAAAAECEQADIQQSMUEFEyJRYXGBocHwFDKRsdEGQuEjJFLxFTM0YnKCov/EABoBAAMBAQEBAAAAAAAAAAAAAAECAwQFAAb/xAAnEQACAgICAQQBBQEAAAAAAAAAAQIRAyESMQQTMkFRIhQjQmFxBf/aAAwDAQACEQMRAD8AoS0nIHwqBbaRA946VxQjMMfFUQu5tshd7QGJML6mOlbmyKJ2lVxLKuOaY2DG0wOOaUsGfzcnpTNsienxqTHJrJGfzTMHiukDjpmPOos22Bn3oTGTuErPlI9qRs9QZSm7xGfIj79q9A3kozlTkjbmBUEZdvg2g+rRUJVCpkO5acHnzFTb+xqHbaKqB7eIOTHHl/NGJJLADcOfaPsVCwvg3Mcf3E9J86DpRe19i6l0XBZe4u24AFG2PygDqTFLPMorQ8cbb2MI9nv+7tMrR8R+1OW9El8QpYzInjM4Geab7P0GnUWzbVO8eGxEQI/zVhfCXdK2w7WtECUwJif2rm5fMlf4muGCKWyvsdm94Bd74SCZXZkc9Zor9jd5kXoPAxgY8qvNPYt20W4ACLi7iDyVkn5TQtbbFjUaa7bEoX2OpzE+Xxj9TSR8zJ8s88MTL6rsTUjxW0m34RAMgefwpcaNLIc3FgkkYIO2cj6edbW6iJqHtgc5iKS1/ZqX7e5NiXFxkYYx1rbh8u3+RCWGujILZK7jIMQIBwwGfWlLts2bkhhtM7SvA61c6vTORLrsZI8QP5fgfbn1pS7bVxsAMEY9IgT68itqku10Qa+xENPiwcQBBzUSWMmFMxEEHp6V2xrV8WrgCkYn9j+9RuHOCQCMRj/ui4qxD3eJ8SAKBkERHoKKB4fBj186UWYaT9flR7Rh4ORUpYx0ydxtuY8ceU1JAx5UQfTmvXG9t4M9eetMIgRFkcdPv41GSpFAFy1aIfa7MAJORAzQHAVQRBPkPeiaVt1m/DSRbmPiOaB3viBJJEZ9a6CdmcGqw8zzRUHP93pQVuB2kSPSio23PrStBs9vHA8RM0AGFIKgH9qLcdGzIWCaCG3GMD0NKkGwyMxH5+M1xvpsa7l2TlTIg9F+/pSty73aM0wQZg8enzqenuJ/4XaUZcaglgQCfy4Pvmo5dDw2Xeo04/29rUOTZFoX7+MPJzPmcAR/3VpZsm9bs27Y23Lp3MvGwRgewO35+tLW1R+zz3xl7d1AT5oJIX9SaaDd8Si3O7ubdu9V3CY52yJPxrmzdmuOhsbrWsuXh/5OmtQAOpiNv3501ZtlNKbdzw39V0GdoP8AA+dS09mFRCU7udxWQWY+ZA4AppdPcbUXntLDd5h9s7QAOJ9ZrHOSovEKl9B3YUyLcjzk4x8q9CrcW5cvMEto4JI4EZP8fCoabsxltgXSwY5JQ5mjX9O2zaVJVfyrPh+PnU00ns899CZ1YOpBueG5eO9V52pwJ9/pXu6LkTDE8n3x9+lcLW64XgtcY/3nippZ8ZCcjBxifL1q3NNaE409iHamja7prmosqe9tjxBP7gPTzrKi5uDPaJOZKqMz7Vt2vLo0JY5YEQTI9vrWL7W017RdtX9OkiWlCAJAYSP3rq+HPmuJkzR47AAIWfaTBkmf8dar7rNuYGcfOnkYC4N5AdRO5Wn0ih6i1glSdwggxA4rd8kGKiAZzMRgc0VFAlysRIFc6zLKDHOenlNEttIhuPOOtTmz0UcEZgpX1p20ZtL6xz5Cho4eNuDPnzRYOTPSIqDLFdpgPw2sddsIqA8yAW5pJ3JJBM+tNaVWTS6wuANyofaGH69KVa3JMZWcVuWjOzlPiJ85ijIxIwSF45pdR4oMx6UzbVIAfI5imZ5EGkQVJ3TzQzIgNyfUGmAJHgABHE0JkAMnn9c0FE9YtqQbihZyMgRTWkt2hp9Ogup3t1ySpB9InHPPtNL3LioviTdIwIrtNqPwNzx3LilwHGCJkTPXzP71k8hO9FcTVGxs6Syume4rDxFVYMYM8gQfIQT71LSK9u5tsAsclienvP0qt7JYXrJYuWYnBbyqxtveGRdJU4IDYkVyZquzoxVo12iAPiYjdGYFOWjOBxWc7M1RssqXWgHAM8GtDpyv4g2t2RBHrNY5aZRqhsZGRQ3Q7SRSNvWou5bhIM9OtHt6u23Bx5E0ZceIiTsV1VkOhV0waWtpcC21sMLhPWCSIwZHM1Zs6OMZzERVdrbd+1B0ybyTna+w/sZpcUt8WGXViL6bVm+biohU5krMTOcH2qn7b03cXkv3C9wvyzf3MOkHgY+VaCzpzaF65fuKdQSW3W7rMVPkZAxxwKz/APUGoJ06i6rC1ug5BAJn/HWur41xypGTK7hZUEIXwGhgAcTP89aldTurR71iWjMjHFC0Vg94zb3AyJnlulNaq0LjWt2YIBJAPlOK6c9OjJHYgxBkx+U5xEc/fxqCuN8rO2RkjimdRZJt7skGTLHjHH350ldWEEENjPpU7scMl2TD+IEcg9aYtbLuS5Wc5HOPOq61IBJieo8qatMyzB2r6daDQyB6W5btXWW+pa1cBVwFyB5j2iaDesurm2WUleCOGXpFFu2lMGc+tEfK7iB6Qpj1+lan9mdbEIgnz/WpKREtAA6CmLlnbHCnyNCZSOgEZzimsNBAxAyo9h71F4YNsxBmOKOEDsWYiMdDXPauGCEuCV4IifOlV2ForryFkZWAIgwIrzV3+8Npe6AZLVu3MTlR9f4o96ye82OWWcbgPOaN2dbLdo25thljcGInaduPv2rP5TqXIphjehm7q7fZtnTow3ulsDaDl8QT6UFO1NXqFVdE+msqD4mu3AoBPST/ABTz9mL2xqbga81vYMKoENnyPWl9D/SusF+dZusInPh7wHPofpXN5Yq/Ls31kul0LN27rLJuWbxs3YxNs7gfUEVrv6Q7Q1+uuXdVqHUq0ABBJERSfbXYKXuywNyHUA4dVIMYx59KuP6I7NHZ1hkuuruSSSBHPSs2bJjlj12VjDInvooO3D29p9ReKP8A7YNuFwDIXpIqXYt0a5Z1ek7R1jkwH/EbVH/xE+fnWx1NvddKlAykbTNL6fQfh4NoWQgP5TP04qEfKjxpo96bu0yq06tZvoqWdU0k+IgyIiQQDB5HGPKrrutW9hhfm3IhYAJX3nB9qs9NIU4UdAB0FS1RHdkGDUZZVdoP9FKtgX7X+oVKKhBNsbQ3MnnHT9Kyn9WXbNyzZfSakXV7yGM5J2mPcdK1muuXfw7rptMl/edrW4kbesjrz86zX9YC13mn04tBOTtWBtjr/wDo10/Ey3miZsuP9tlDoLtwAqrMACDHtPWrK7fHdLB/MTiY3Hr86STT92VCjEYPr9xXtveFJuDaATI6muzNcpWYYqlQwF7uJDeI5iRE5j9KU1gAfADATyM0zvZUJkhuSGiT5/f80kwZ7heCVA6/fqanVuxwS+G4N6/OjLBOBk8YOaCW6kCfP4VJb+VKiPpSNjIZkrdQLnaQ0Y8+M15cuqnhJbaScOvUkn9c80N2ZU8Iz7R9/ClmLElv3xNa0jM9B9/g2tlCQYLf5oNsENnqZyM/vRd4PBBHE0TRWmu6q2rCCXIiCZOTGBR6CiD3IlkPPGAfvpQ/xtwuNzMW5EdDU7iEorePKgyRBOPOhLbLNmQZwQKKoLR7daUlmDTGKDo7ly1qZn/TAieCJxj4A0a4sWh/cRyRQ/E2n3q7K1picjBxIHvIFS8lJ4w4nUzQ6cPoNUNzgF/EuIj4/rWm0erFxJCwyrEc1nfxS6+1YLECUWR1B8/XkfOn+z7raXUhboOxl8OflXzubHe/k7GOVoe1TwwLiS2BPHxp/sshWWP7ok1mP6k7RbTJpBaXfee4zgE8LEZ+J+R8qS7N/qt0v/61t1gyI5HpUf005QtFfVh7Wz6MbW6+Q2W5wKiLYIiKoezP6i1XaGpDWdDeu2+t2NoA+tXr3hZci4Np8+AKzZMMo6oRSQVJUY4qF0s0kxFduJSc+1BZmDlJlegNBY2wNoXF5FvoqnJmvnmv1z9odr6q6xi2h7tBjAGJ/WT8a139S6ltFoXuKc+Y6GRHzNYCzc2HdPiM8r8673/PwpXMw+RPqJb6VBHdeGDwF4n0/Wps+xyCsQMY+dJjUSwHi88mp94WeZPkYMSa3dkD268L4THPIoKk7SygZwf5qJuSxxuzk+Veqk24GOmTFFIIK5+Zo6jHmKmbRUL4j5QBP7V6nIU8LiJpqy0yxz6nApZIKKxrigqJAx4sgTU9sp+U5PnUrdu45LMSP/tx8693HIMyMdP0q6kTcSCW4E7pA4ORFWXZMfjdNbW5dQtcAlFyCeoPnmkihdQ3JgzJz/mmNJd7jVWLohjbuBgvpOad9AUSLsNoOAGRTHEkAT6xQ5RjMZKyTTeu0wtBVJ3FEAgxukdfrQF7ruufFx8etImPxAauO6kGAcCKSMvpzbkkNdAj02mY9cUbUk5WcA4oNq5sd28kk+oBH0mnyK8TJfzNB2M6rqShju0uhEAMjJA6+Wf0q51VpdVrtHp7Y2K264SDgIOKqOz2FpLb29p2qWcgZJ2g/X50x2hfZnVzCqdGLVs9CzgYn4/KuNONyOjjdIS7WA11hdcABZtAW0I6AtjJ9DJqv0Ddnd//ALiydUFOcxx0wMj+K2fZ/ZejPYZ0152vo5AeRkAGQD1mdwPwpG1ptRpibNhtOEU4Pd4MkxUpZaXFFoQ5O2O9lf1NpLI7gaXVraTm4LRgLgfsDNaHT6zTdo6JDZeUbwgx+n1qj0KajvEN51uKfzbVCkfeKDobdnsjti5uZ7encC9bXkHn54pIvknGgTiou0zQ6a5dt2j3qjvFB8PQ+1Q74XoZTuIjMdOlDu37neC7bWGL48iJBkehE1O7sHdXwvgZ4I4Cg5o+lUSXPZS/1NZ7zsXWMcHbuEycDxfSsKlslg29RI5ifpWq/rHWXLZTQ27g7q4JuJOQFiPgfpWe0lgT4Z3ERBH39mun4seOLZkySuYPYAw8QiOvHPFEgqATPhGZMc8Cpi2AASzZOfFAn7ivFRNufPy+56VTlR6heUkiTHGDg+VM2lUqNjc8ZzQ2sJMd4ofkhp/UxTCKyqZCKsDB6+sTRUgNAXVgxiV8xMmvFbIljMTk4Pt/1RRBgAeuZGOtTKuoAU8njMCvMVM7R2m7lm/KMEk4gUG4g3koJMysdB7U/pkjTXEDbVWOfv2pIEtcgKbhGZn6U0WVcSSDw+IApA/KZmKC4JVlJMf20ZyWYAkswXnPT0obrAPhJA5AGaNnqoY1mp7xQQNrn5+dKKy4gTiDPHzrzvWtvLMoMHDECRQtVfs/mN5MiIGeaKroDsXuuCTn2pZ7xsuCDDmVjzBGajdukk9yFA6SZzS2AQJmMk1aUtUjPwd2zQ9iam0791dvFTdPdli2AScH9x8BVsBZ1g1Vkws23tom6AYyPnNYu0zAltx9ZzMVa2LhK94S1ty25doyM81zcmOma4TNl2C86yCwFu4FuXZbDEqDI+tDt6pU16LKm3dtKyru/uxj50j2e1xdb+DdtnhdLN3ErtIKzHuw9jHlVhouy27lr2n2XLtm4W1FoYKnIYge5mPKs7xxTsup2XNvUG3tBXbvM7+R8PiaRYPq0sXHCtfsmVji4s5+dF01q9fNstc3oFjZMweZ9a62+zVXdJdt7+7hsEhwD1Xz9R/NIojMsNTtstpktZUv3fh4EY/evbNxb63LfhHKgxwPWhXimvsd3dchXYlbyCNh9fITzVF27rtT2OjoV4UDvVbMnBMcxMfrT1bpE60ZrtrVLqu1dTfSRbNzainJgHE/OmNHbcklV3CTPWPrS2o0F7QrptQu69pr1sOLiGY8wfWm9Bq4QoySg4YNxFb4pVSMm1LYW7ZZhuCjafMxnyoH4ZgYIYkGPCQc/ZqxTU2UH+oYHEqP260vccv+VRGFOJx5EfxSFBI7HlWBKAlmcc/GpI7BVhIAPU85jp95ot2PzsGDAQpP39aC9wKAwEELgnnijaFaDSCDAME9KmUUAsu2FyM54HrULzq4k4zkbT196PYlxBk4Ind9/ZphWH0a/wCyuyCGZwAsxPw/WkLD2pvNcDG2BGJ68evQ0W04s6W8pgFoABj78q87P0xu2dWHuDJtNMAkjcw8sjI+VKnRooWuXntCVRfCMqwA5HMVX3tddJZbdvaOfCZ+8zVidKqF1GDks4EEH4c/Cf4TuIRZO1FcyfFJyY5yaPI9RTsWQkspmYgnioB2ZifCDOKaW0xY97b2gHMRRF0iswKtHpR5i8LE14GJIxIoRHi45xTd2wyWiIPMhiOKUYMCT659KKmCUGERMGTRrbNacoJZXWJORP8ANBRtjZmJolvxGIMTINM1yRLo0Dat711LltmW6GDAgHAP+Z+zWpTX7b2h1KoF1N26lnUImN48/wBBPyrGaLWpbtGy9skOcEGINWinUXii2bjKoyAozJxJPkKyTVM1w2rRrezyNRft29OYS3cILD/irGI+HyNT11tE7U1OqZv9ullVdd22SJyD0IHt8OQh2Wt3QaV4ZptruOMtbjp7frXL2muq0roF322Ztyk5PQfCIqF0Vqyzt6oWrb3CrXULG2DI8frj0zVP2jbbX2dbfYb+9tbLSjjaOv61Xtq9VrFTTW0HeGUuqphT5k+4Aq90lg2bGxvE6pB9/wCKhklwd2MoWjEdh9qnQMbGqLvobjS6zm2f+S+VWvaehs/6d3T3UQXRNnVWwNtwEYV46+tV3aWmXTay5YggFgQfME/zNF7H19vTu2g1Qf8ABaiIDDKEjDA9Aa3N2lKJkSq4y6Ezeu2rzpcQrcU5UrGT19qdslrtvc9uB0EAZq91XYiay13WpALIYS6hCtHQ5+/as/qtDq9Dqpk3kThxO6PUffFMsil/oPTcXondLKxBkRzn79KGSrAqqMSPJTjGZg0W3dlmgNJzGOfrT1hVLC3AED2jyP358U930K0VtixdIIYbcj29vlTmntsguKQDK5AHOf8ANEXcvgPAHM9a47dxkiep6yKIlFWtxmAloJzt4J/mm9PeOnZnIMOhVhG3dOfPzA/SlbWE/MI5288UYafaw2TiG/LHQfzQZoQHVC9fMqcj/wB09fX6VBDtQBlhvLoaYC7Y348X9ryaKXsEFXGR0Jn5UkmUiivCKoYHO7rSmbbl7REdUBwatjprb5QsPbM0je0bFiQQYzBkUthaBjUIQBdG0E+cwaa09qzvJKBt5yDSD23UEXAy9J6GpW27oRuJXofKizyf2ParsJXT8RphuT/j/wAfhSK9k31lkJAB8qs+ze0WtXAZj0PBHrWiCW9Xa3WoDxkedTeSUB/TjIwwsXF8Y8+ByD7VedldpPZK27tsMWhWJjxDrXazQNbLXEU4glf1rrKL3e8gSpwfKi8imiaxuD0N6btW9uDXAAi3C6+YnlfY0TshC1y5btIw3NuXA8I6fIRXum7P/FttHhTqD1q/0lizoNP3VsY6zyxrLmyx+C8E0KaHS29K7KgJBMkk8mi2r0O4mDn2FTvQ1wAgQaF4FfIG71rI3eypQdvWy2ttXBMsIjjjIP71DT6BO01OjdgmoRS1gnh+pQz74qx7fZbdtLhhtp+lUh1Ztlb1md9pgydK6GFtwRkyJKRoOxdXcbSBL7sblrwlm5jpP30pphvuSp8c4aB99aDr7CfibOs04hNSv+oFPBPDfT9PWusE7oJMxkUQAbuistqWEd331stb28Kw5EeX3ikrlq9au7b9shgOXJg/cc1ZattlhgpyrBlB88T8opjSFtfZXvrPeKD4SDEexq0GSkiu8DLuVwT0xz8+aXcGDMH2wKttV2NcT/0zG4Odp5qtFp0v93cYoSDhgffy9KopWTaKFNU9tY2qyno0wPnVtp1F6wGICnbPhAFdXUzKIX1XiuZz9mlokSeQcV1dU2OgRuutyAeSBT9vO0+czXV1TZWJMqrp4lB3TOKrO1NLat2y9sbSGAgcH4V1dXl2NLorbLnf0kD61p+zLrlEbdDTyK6uoZAYi71QFxEdh4mwY64qrS0nekRjy+FdXVlfbKof0rFLnhMQKNcdtnPBkV1dUn2Fk7bs11Nxnj968u4viMY6fCurqmwoq/6g8WilsmRWeRiQRJwP4rq6t/jewzZ/ejVdj3Gu9k2Q/wDbAHoKKpi+RXV1N8gYK+P90g6Ng+uCaa0rlAwWAFbAiva6qokww1N1WkNkGke0Xa7fDMcgxPpXV1MhT//Z</t>
+  </si>
+  <si>
+    <t>data:image/webp;base64,UklGRtYUAABXRUJQVlA4IMoUAAAwgACdASo4ATgBPu1ysVIppySrp7Q52XAdiWVuZn4R785W8VdMRmoez3hjiHZLY/oPXg4N/jd0j3M/vOelDC5Vspzng/duip/+PCTI3nbIOsmDECYHn7YdKSpNBMVxegvhBdq1Y+1ycH3fuHy/bgk78VD1MH1nXTvOlJ7ZepXuOmp/sMP/QbJlUXZvO/Wn1c7xw8iQv+dhdUWJ9TqBrME3AZAofdqo+QOe4jeEcsEPWUWWNZ1RHrSPkpnxxUsqGV41KEVhHtcLHmzKpzTPMk+2D55tImx5nsNlBifa9djJU21d2FgW1RGGtuIV52T/33E9b/nLUM0wheVe/qw2Yf8Dsvesh9+KNdam0rT6ryXRuWPEv35TRPDzfvEoFpf0k6GRb+RNK2j0n/zZLlibg9jHQj+DmhH6xjL5jLzdH9y5d7z5DlUdqVO31iqMBUlxm6QL3L9W7wvWOij+LHKWbU6x28DGX7NvcuFke+pJzor3Kwx+iHDPabd6BilRS7kwNQzgXS8N6B6u84aymvhJW3Qg/9l25QBkDO6mG4eSpiQr4BQmhFBkWHRbe+cn6vywlAakdknYzyaxT7mcW+imgKSmdkk4gaHXDohQjuLckLGKB4x6E0yQCg2bUCT0m98AZ+5q+IzX7L4mZvzy8AvMuXbzRH1+woCWbHNJ7t429ID2RaWq5gnhBtF+qtB5oPK88xQDN/nAlNXbjiLD2AK9i+KdiCnQplLmZfW6DKxMPI40dtxuFnmDtYcR3SimKXMsD6O1caG4yqbIOsOyNqR7v2NA3CC4NXrdVrjpR8AB2351WqhCJU7MY/Dws7Gk1TJYfeVuoGPX58W5zU9wwyeL8OSa/MhbxOq8dGIlKyeZ4SDpaJ4STx3XMddT8THoWTd/jadaE1+n609XGJcWwKzbuJiZygsrVwqszaT6u+v7knzRQ9a7kIHdres7la+QyeoNZfUhWIWtF34sv68t//RRVdXHsIWgedb+RIdak7TAWKbsCH8bx2Wel1U1+l0jYvIpLFPZHlwzvbW8WtrgVJm69n4a8MBFcNhz7015cacyHFR571Vh1aeL9IQFfIZiwisNttUuCiP6POJTGPbdOVJ/tsyZqTlKBPjaJaEB/T0l6c8Zp2e2DcILFtUcE7p9nxxtVLLPZDCkpeTR2JbL10zV3+e7rLtJhrDpHK3GsMe+yL5qL+7DUGg88+PD7gLnFYlTE46u5zuLfz67U1lNw+Vh1+KGRmuWZRssY6pXXAWL/aYCQCowl0pgbkXfAy1n9LVUUBgKyc+lJvLoqCzQedT4M16J/+ThnN+pbzG10BF90kctycZzhH2GzH9P7esargKvBTB17GosFKeZ0Q/UOqqbsXDg787xJuDXNKcsgAD+5Qa7Ye2eL+vWnr6KnJJIJnr8xBp3HhGShLA4BjGlmktizGm5tCB0qqrP3KR3WtbGnhwwhREf1qKoi2XRm++Iz63Ee1U7Wo7yhy7OOSg1Kj9az1wTLczI85+PyCdT41N8WkszqjyKj24KnC0QBDmwdS0LJ9/bzgGCLAuYFB9/svt0+GuGxtAN15FSn3Gkzc090orsf11x8/9Gls3U5wfIYwZGxb5VISPm1Od2gmhK5dC0g48DTtdWz151gZ2+eWkJz22bJ31Mhsw/Vo3whaPLqxr+v6Fpe609fnzX4oh5XR+jpu1Jps9sEVTx1rf8bY+rbU2MJghLpIFPNa7MzhRsGlcml9xzK90fEdqXAXExF6tZtyM5vy/KX1MUeQgqMR7YXOVUhm0TThC3Gw7uwSa4RL/f4Yda5eImI1xr7Q9q2KVMBYKdgt0PPB17asL6QF7XdQACt3R+yb2TIxdP8a5iSVrG3TiZ8MAgcIUV/nZdBsnezKgUKq5tSN5/gGlI6Yh9qI33Q5RJ21T3Ilh27WwZQlGay/U1aLn9VlHwF5tu3uta9D5CmNS3JA1xp8jsrSkaBbKxFCufw5bgBfJkze3hnAa45VGe7FvJgSdJFVFF6dBdpbC/K2CF1JEf0G9DkT5y1UyFH+aai/v8qUcIZkvOw8/ysVMqG9smZkUzxkvmGHQ1sjvMtQrRNSG6tujIEZ9QNC/FWC3JOlLOEFqnsPFAOb1PYGdcCl+OTLyp8ydI7ELQzg0sh8+z/8RdgbiGmsEKfdLP/B4QSWPz3T7OReWOhJWzrZAQ2RxHX+AIYibKwnG7GVTWjNiPCyl8O4//uv+Q5hXMBs86AAc9uuQWt5RZqBII6juvu752RJBEGXOfPOET5iQ33L63ibG+YpvvFQD4dS9vHoHzig9LPAgCy3thOSmmeMLJm0CSIiHU8XUw8GRwqSDQlIrzyx7iYXagYSweSXqm0ckYcNf243d3aEdKhtTbBsxiBuh6je/4ptI/qs5/KsppLNRKhpnqWcjC7U/y85MA0db6PxHbkcBHZ+LVwOh+qVGyZY82ghY3uFAR85emDXfIyHR5e+1bLTPeNjNUr93M7pQQOhUOVGFtLVZaidPTDgILCk77njpYR6gA/bhy/NhLFghxCdTkVhbR10L+/Y0SvT0edTRASqL/RFRvWE52svOkatax5VoaU4N3cY6o6Mg/k6BoBjutZhuRCZS0al/tELW+NbhyPjg5OofCxph/QUYM9FTc7ZLPXuzWzxgFNGK0PYYPtWm/wQKaeW/it48fsr3I1JzQP5nDc2T9A0yqZkzppHpDV15qMj81Uzjj83rS73On5oQIsdT937EXbeMe9xn60SM1tZ12etCJaSp5z1auYOgc9klpODt4AaAyVi4xEbQvRCpyC1jYPa94kVu1idxhN5acPAlR+CAd7u4T5DOlmu3mBGod9WjO1Qwl0Yu7863c4g8NctF/L9sUUyljSo8ZD+sAiPhg1po9UokgtPZh7Bq6DL0LqKX469iIIUFf62bwspybWqzFBSVf2MGUxaQG7C4+yxTHTYqu5ogewuOx9iesSY451269C98nO9gC+7EE7uB+zPZVMP+I45SfGjwN9QEM21qqBACX+Rtgo3Io7MAZ04ERgvyYR+bTTF7oP4XFMMqBbJled71+X+BckoYkY3mT5nnjltC452SlOfrMoiyZfoPmL+d6PENrMtCdVVe8+17WtfM33rT6Vf2K5NKhr40xaLRwWNKVSRnk3KTCyu3G8dyll8+9hYFOfE6EzykH6tSbdjZkWwS2120OGTMWtcBsWOaomCu0dQHcXa0GCtcptSU2cEWEsGdubvaPZswM7aC8W1gcrgnmkHUTE7lRu5DlMpER+HWl+eS/kqKzr6m1iXM5Sppo8Xx18DgnehG7r9fsxMHmp4dGZdPYKpy3kV5tXcjyL6IvjNvsJhne1w6hoYDkk5GeI2ZlgwwyX/DdV4YNiXhXQrLS9nQ5wVqqjveRlEvIJ9erc9l7XGWA2juHVt6+yRCcupdbO5+ZtVLXAuJwE57g9Ji5RgyefsvUMDOePNAWn1V6uG8Ip7E2+Gin5/tB+vDRG+0DXb9cZ2kpQI2r71GSkoGAWP817l2Q76Nhepe+m24nP7EGx4OlO4eCfqMedBDAb5u8/u1XKK7I4YhrOPN36foRFwkqzC5L72gqh/bmn3e5hzyKlXSeYkGb3oYgfz8IpHJgk66dSoJDXeVV1jEJyymt0QqSFFbtV4uPS7q6EQ7IsxqxIrx61C4TraFkgNV5QX0NDaxgZwEANhBfB+dtC5dkqYPUApVVbpgWX6uMTyYracouUkUJhXTHxEhFcNFSbtgaPs9bxllTcZL2NhndeYcmo29iO84okDeceIEQh/tt6wgN8FevHezIgf8QgeEn2r9Uol7FqVDKi0Y5nTCnSyrNNpjSIBC7ULd+rSLFBOe+6u51seIA6S48EtSIjl9YELJ1fjm/c+m2qCC64MhL2FXJJeJWzWqDy/6TLicimq1GZTf8pTq9vwm91EuymQEre40oO8Unt4uEoib1WS+0u96LRR9p1+Jf6izWLV27PpmZOk7XQaItTPXhQtEIq2gRwvJqzqdI6eM4QKAI+w7sRFv9bH0h/UlEolBpyE4OZ4L3+kzeV4UVFhpT3UrZ56tsti0LsR8D2Z6wLkfMo0yZ3RmlRDJb6AlatqYoEca55KaHRNKEkuYcyixgNE2zkpRK3elLqR0eXYeELlQD9O5Od3fjiH97+DUrHva4FI7jX6VyUy/0d6I8mwY24dHPv+nJsKS5dJwrjZdewt4E09gDlNDbBnFUPhYbInf4jE4+4ElzGs3PAC8KuqrkuloRJtF2lceHE8wWFFquEsw9hMaRqbEr4QIBBNEfQvfXoH7brzShth8CcyU1XoJT4GbdeyQ1izSgZD8co2qfC+D39yNaTamfzAaeDqjpIb0JOKlSuqc2/f/PgaY+pWoCHqeiJG90NqCqQ5YrR2hpZiCNY2VrYZCGFZ/Zun0o2fJddtA/bsMLx+xCRLcdeM/QshhWc/lIrwIqoxure+898XBJMg4SI3QLGup0n2C1Im2fmuRrCb4hqGQE422oETpQ5/HlCMNi8Q4jXMWnTNNmkRwxgV0/TiI7tCLrIOor9C4YtYfXu4PhiXUgAEzx+lAvh18O3E28+y9tKpsCYDTdehgMGn7CcbxKufZ9H260kiM9ZY64QlO+8E1GTsxV0lxlYikoHkD7pcyscDeQs8X5CZyc2AG+x3IUEHe1aap3Gm0ZdLRMHrifGLWiw0VdmXsx5D+PanFdBFCU825wBMmv1bFYWGwDTsLBNgv4FDBvwyGFbiur3+Wt4dWjnjndZB7/zwpWbqBdwPb1KL6x+ZqqQ0azQNJctllRIkGrjzpZrzBSNxA9Ha7BS/TI0Lv8+x9t9KoaFx+NxV/2jD414w/PbGj7r0ctE5rIZ86M6hEVIMh+jFp78jt0C+3NiFk3TVa6XQ14gvGBZt0c4v/cKqvUiSVl5tgAqcYZRsrxudOWGBY1zaqp7v1kdeRFthreu9YtsMVZ1ys2kRNFAbWI0gCM4ZBopyh6IuFe9PJ+NSJyJMtc3ZIgksoR88EpO4USvdUF57Rd+0Pe66WpQdGPpdfjVhgtEiMncP9zaGmroH5i6ynLA9TX6SbQ6IuQP1KM3+mGVHoM4A914y+oJt3rw4bwCx6IidGQ8KBDDfARRb/p0IOcHCKh5s98zy6D4qzm2sMD22GMH8a6vqD87Vqc9p5R7kAE64slVsqcahnUPqhQlbgiUl11icTMwxSUJ18kR0/+pPVhm3uQPwvMox6Cp96KRuFymJ00YU+l7cIgQz0fEQekxZoxvyqSJhlv52Nrx+oKZf/dhwAzKQ7pQAIHgqTqxlFLZpj5g8WIcistJMmelPJc/6jopo+2a9xuU/faHrXbhOqMbM0NbMyfDxgaC2lHYnrFgYU81H7JYtePtCPVdQ0d8xo19QHJvxja6qeWdqCG15efzBuotMciFFjnOBW6d36lWAqRt+w6objLjreJqhbPszNgBXcvr4zAFrnfrLLyIrdkQFslYYNi2uaRhedLRxhkQcWTS9bVXcVmgNeLLIKQz1RB5Jmf9G+J7deMTGPbEz+ji5psuJGjUDG0XdKIW5TwWvSZBALG2XdViNeSsCGQCOguLJcaPShsOZSl0fpgxIwvfDpbN3oezuXAaxbzY/8ybZy9o0EwflahjehIOK3iV5eg/fGUgC+USrMnBp44k5MTLKDeeIUZJ8zG9vCX/u6mZ7PbpAFP+iwGVtAaZLY8fQ2NpxCEHjbDs7jzbQTov5ojYx1Lawks/QZKzKiXC1uJyinwsNKLnIXPZBopzug0do/hcV17HMX1J7YDQxfDN4U1nMWhjB9jC5SrTQYpbXsbT0jBZNOqZDszyU4LET0D4v9xb90V6gZIV+ot973sJ4UP2d/d6StL1hKfWvcHZwfAAgasD2zy96rz+1dHTThCU06nImqhw9M3xf/b8X+/ve9iaruI4XRQg2nw81bH5s80ZIs8Dg0+I5q7RdZBhfBlggTwc3l35bO5bAyVvuG1mQWIkDZ0NI3FfHNaBekYnjCjXogAiUDNt5CeFozv6GcbuA4H8MW1eIQw2gtZKGtk0m5ahXu3VZZjWho4jFHnHMHnuXMAkF6PW3lZhc8MV4hfC+2lTfI0QU4Qd16hGuyBNQGubTd2g0eJ2WbRZpT0mKRqXuZVUyNhS9DwOvkbiDmqJZbBGEsjLbSMUHjbG/v8RTxbuzuiAQcCl2ScSc6ynOj6TeBrhrxqERZ6spxCpHGv1Nz23su83nviN7Pma9R3TxpF9DopHMU/2iLmFNKHVNwQUuBiDmVSJDK2wYjR1gwBfWdf//SJky07ls7JzAPG/yvD0N8iL0+mYaH0uE1Q1sv6dFLCN8pZCHbNGRqV1DH57Gy2ddcw6NnMWwb2Yp4hpvei1NQVandP6cmLwqH+Z+RjYlsDk4PXUM75xEK06g5qYl/virdfVMpw0a/nGbHGAM31W831YowDgan8mqQ75yJTpVPBuMXxBTR1Vvh2Ran8aWUIQnwhdwqjuGiiET2FsZkCiya/X/wrV8/EuIh3CVe54kPVByXooeJRNdKqTrLlrqe0lve98mP1HFpORVunCEI4V/XvoR1i4sReAyrQjkt/I0OE4nIwHb8IMgu8d8hSdJKQylhaI/RH6JINb821OnRfwROsHnNMD2ykrlg48SVArbuIMLhgTLBZP5V6v4KEbot98iq/Yau9soQkOLaq1CEIPaIrPtceGiphbvu2dGh0PgnxjordDn9eG7Uxy+seEWKq00ySQd1WbMAcNbE5rlmLw1bf88FamKrc3xtkiYbrbb5V68gBOH9Apga4vms04kuQtob3k0nJnadmk+/Fr+Qpntynp7mBHqctAHiBmjOo371gC9b6L0lvrhg7+qU8abKrJrBv/PGjJsNK/LH1cKJEMIKuAMiROovpQfM6jVJ2NnSW1+A3pDST3hMyc2gtaTbUvtQoMJXGmLdUt7gIxaarIGM72mYETgH8vuXH38L1Ha3b80lTNG1fFfxIU7cUnY/XIS8UMdgVer1zqZOFlyKdmdpoUFeCQLMO1SRChxLONaEDVrYUnLnt9XDEDSX5/X9g0950rWj/nh3o+v87c3cSCKayYUpjOqDjL33BwRNFrB/UD65YwHre9vrcN7IbYncAAAA=</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1288,6 +1333,28 @@
       <family val="3"/>
       <charset val="204"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1310,7 +1377,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1351,6 +1418,19 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Гиперссылка" xfId="1" builtinId="8"/>
@@ -1632,7 +1712,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C162"/>
+  <dimension ref="A1:C168"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="255.5703125" customWidth="1"/>
@@ -3137,6 +3217,40 @@
       <c r="C162" t="s">
         <v>228</v>
       </c>
+    </row>
+    <row r="163" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A163" s="11" t="s">
+        <v>389</v>
+      </c>
+      <c r="B163" s="18" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+      <c r="A164" s="11" t="s">
+        <v>390</v>
+      </c>
+      <c r="B164" s="22" t="s">
+        <v>392</v>
+      </c>
+      <c r="C164" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B165" s="19"/>
+      <c r="C165" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B166" s="20"/>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B167" s="21"/>
+    </row>
+    <row r="168" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B168" s="20"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/database.xlsx
+++ b/database.xlsx
@@ -1228,6 +1228,13 @@
     <t>Платон</t>
   </si>
   <si>
+    <t xml:space="preserve">Платон заложил онтологический фундамент стратегии, обосновав необходимость долгосрочного планирования через несовершенство мира.
+Владимир Квинт выделяет две ключевые платоновские идеи:
+• Несовершенство мира как стимул: Так как текущая реальность несовершенна, возникает потребность в её улучшении — это и есть главная цель любой стратегии.
+• Вторичность текущих фактов: Настоящее мимолётно, поэтому стратег должен смотреть сквозь сегодняшние проблемы, ориентируясь на глобальные тренды будущего.
+</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">В теории и методологии стратегирования академика Владимира Квинта идеи нобелевского лауреата </t>
     </r>
@@ -1250,21 +1257,14 @@
         <charset val="204"/>
         <scheme val="minor"/>
       </rPr>
-      <t>. В. Л. Квинт активно интегрирует поведенческую экономику в свою общую теорию стратегии. [1, 2, 3, 4]</t>
+      <t xml:space="preserve">. В. Л. Квинт активно интегрирует поведенческую экономику в свою общую теорию стратегии. </t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Платон заложил онтологический фундамент стратегии, обосновав необходимость долгосрочного планирования через несовершенство мира.
-Владимир Квинт выделяет две ключевые платоновские идеи:
-• Несовершенство мира как стимул: Так как текущая реальность несовершенна, возникает потребность в её улучшении — это и есть главная цель любой стратегии.
-• Вторичность текущих фактов: Настоящее мимолётно, поэтому стратег должен смотреть сквозь сегодняшние проблемы, ориентируясь на глобальные тренды будущего.
-</t>
-  </si>
-  <si>
-    <t>data:image/jpeg;base64,/9j/4AAQSkZJRgABAQAAAQABAAD/2wCEAAkGBwgHBgkIBwgKCgkLDRYPDQwMDRsUFRAWIB0iIiAdHx8kKDQsJCYxJx8fLT0tMTU3Ojo6Iys/RD84QzQ5OjcBCgoKDQwNGg8PGjclHyU3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3Nzc3N//AABEIAJQAwAMBIgACEQEDEQH/xAAbAAACAwEBAQAAAAAAAAAAAAADBAIFBgABB//EADoQAAIBAwMBBgQFAwQABwAAAAECEQADIQQSMUEFEyJRYXGBocHwFDKRsdEGQuEjJFLxFTM0YnKCov/EABoBAAMBAQEBAAAAAAAAAAAAAAECAwQFAAb/xAAnEQACAgICAQQBBQEAAAAAAAAAAQIRAyESMQQTMkFRIhQjQmFxBf/aAAwDAQACEQMRAD8AoS0nIHwqBbaRA946VxQjMMfFUQu5tshd7QGJML6mOlbmyKJ2lVxLKuOaY2DG0wOOaUsGfzcnpTNsienxqTHJrJGfzTMHiukDjpmPOos22Bn3oTGTuErPlI9qRs9QZSm7xGfIj79q9A3kozlTkjbmBUEZdvg2g+rRUJVCpkO5acHnzFTb+xqHbaKqB7eIOTHHl/NGJJLADcOfaPsVCwvg3Mcf3E9J86DpRe19i6l0XBZe4u24AFG2PygDqTFLPMorQ8cbb2MI9nv+7tMrR8R+1OW9El8QpYzInjM4Geab7P0GnUWzbVO8eGxEQI/zVhfCXdK2w7WtECUwJif2rm5fMlf4muGCKWyvsdm94Bd74SCZXZkc9Zor9jd5kXoPAxgY8qvNPYt20W4ACLi7iDyVkn5TQtbbFjUaa7bEoX2OpzE+Xxj9TSR8zJ8s88MTL6rsTUjxW0m34RAMgefwpcaNLIc3FgkkYIO2cj6edbW6iJqHtgc5iKS1/ZqX7e5NiXFxkYYx1rbh8u3+RCWGujILZK7jIMQIBwwGfWlLts2bkhhtM7SvA61c6vTORLrsZI8QP5fgfbn1pS7bVxsAMEY9IgT68itqku10Qa+xENPiwcQBBzUSWMmFMxEEHp6V2xrV8WrgCkYn9j+9RuHOCQCMRj/ui4qxD3eJ8SAKBkERHoKKB4fBj186UWYaT9flR7Rh4ORUpYx0ydxtuY8ceU1JAx5UQfTmvXG9t4M9eetMIgRFkcdPv41GSpFAFy1aIfa7MAJORAzQHAVQRBPkPeiaVt1m/DSRbmPiOaB3viBJJEZ9a6CdmcGqw8zzRUHP93pQVuB2kSPSio23PrStBs9vHA8RM0AGFIKgH9qLcdGzIWCaCG3GMD0NKkGwyMxH5+M1xvpsa7l2TlTIg9F+/pSty73aM0wQZg8enzqenuJ/4XaUZcaglgQCfy4Pvmo5dDw2Xeo04/29rUOTZFoX7+MPJzPmcAR/3VpZsm9bs27Y23Lp3MvGwRgewO35+tLW1R+zz3xl7d1AT5oJIX9SaaDd8Si3O7ubdu9V3CY52yJPxrmzdmuOhsbrWsuXh/5OmtQAOpiNv3501ZtlNKbdzw39V0GdoP8AA+dS09mFRCU7udxWQWY+ZA4AppdPcbUXntLDd5h9s7QAOJ9ZrHOSovEKl9B3YUyLcjzk4x8q9CrcW5cvMEto4JI4EZP8fCoabsxltgXSwY5JQ5mjX9O2zaVJVfyrPh+PnU00ns899CZ1YOpBueG5eO9V52pwJ9/pXu6LkTDE8n3x9+lcLW64XgtcY/3nippZ8ZCcjBxifL1q3NNaE409iHamja7prmosqe9tjxBP7gPTzrKi5uDPaJOZKqMz7Vt2vLo0JY5YEQTI9vrWL7W017RdtX9OkiWlCAJAYSP3rq+HPmuJkzR47AAIWfaTBkmf8dar7rNuYGcfOnkYC4N5AdRO5Wn0ih6i1glSdwggxA4rd8kGKiAZzMRgc0VFAlysRIFc6zLKDHOenlNEttIhuPOOtTmz0UcEZgpX1p20ZtL6xz5Cho4eNuDPnzRYOTPSIqDLFdpgPw2sddsIqA8yAW5pJ3JJBM+tNaVWTS6wuANyofaGH69KVa3JMZWcVuWjOzlPiJ85ijIxIwSF45pdR4oMx6UzbVIAfI5imZ5EGkQVJ3TzQzIgNyfUGmAJHgABHE0JkAMnn9c0FE9YtqQbihZyMgRTWkt2hp9Ogup3t1ySpB9InHPPtNL3LioviTdIwIrtNqPwNzx3LilwHGCJkTPXzP71k8hO9FcTVGxs6Syume4rDxFVYMYM8gQfIQT71LSK9u5tsAsclienvP0qt7JYXrJYuWYnBbyqxtveGRdJU4IDYkVyZquzoxVo12iAPiYjdGYFOWjOBxWc7M1RssqXWgHAM8GtDpyv4g2t2RBHrNY5aZRqhsZGRQ3Q7SRSNvWou5bhIM9OtHt6u23Bx5E0ZceIiTsV1VkOhV0waWtpcC21sMLhPWCSIwZHM1Zs6OMZzERVdrbd+1B0ybyTna+w/sZpcUt8WGXViL6bVm+biohU5krMTOcH2qn7b03cXkv3C9wvyzf3MOkHgY+VaCzpzaF65fuKdQSW3W7rMVPkZAxxwKz/APUGoJ06i6rC1ug5BAJn/HWur41xypGTK7hZUEIXwGhgAcTP89aldTurR71iWjMjHFC0Vg94zb3AyJnlulNaq0LjWt2YIBJAPlOK6c9OjJHYgxBkx+U5xEc/fxqCuN8rO2RkjimdRZJt7skGTLHjHH350ldWEEENjPpU7scMl2TD+IEcg9aYtbLuS5Wc5HOPOq61IBJieo8qatMyzB2r6daDQyB6W5btXWW+pa1cBVwFyB5j2iaDesurm2WUleCOGXpFFu2lMGc+tEfK7iB6Qpj1+lan9mdbEIgnz/WpKREtAA6CmLlnbHCnyNCZSOgEZzimsNBAxAyo9h71F4YNsxBmOKOEDsWYiMdDXPauGCEuCV4IifOlV2ForryFkZWAIgwIrzV3+8Npe6AZLVu3MTlR9f4o96ye82OWWcbgPOaN2dbLdo25thljcGInaduPv2rP5TqXIphjehm7q7fZtnTow3ulsDaDl8QT6UFO1NXqFVdE+msqD4mu3AoBPST/ABTz9mL2xqbga81vYMKoENnyPWl9D/SusF+dZusInPh7wHPofpXN5Yq/Ls31kul0LN27rLJuWbxs3YxNs7gfUEVrv6Q7Q1+uuXdVqHUq0ABBJERSfbXYKXuywNyHUA4dVIMYx59KuP6I7NHZ1hkuuruSSSBHPSs2bJjlj12VjDInvooO3D29p9ReKP8A7YNuFwDIXpIqXYt0a5Z1ek7R1jkwH/EbVH/xE+fnWx1NvddKlAykbTNL6fQfh4NoWQgP5TP04qEfKjxpo96bu0yq06tZvoqWdU0k+IgyIiQQDB5HGPKrrutW9hhfm3IhYAJX3nB9qs9NIU4UdAB0FS1RHdkGDUZZVdoP9FKtgX7X+oVKKhBNsbQ3MnnHT9Kyn9WXbNyzZfSakXV7yGM5J2mPcdK1muuXfw7rptMl/edrW4kbesjrz86zX9YC13mn04tBOTtWBtjr/wDo10/Ey3miZsuP9tlDoLtwAqrMACDHtPWrK7fHdLB/MTiY3Hr86STT92VCjEYPr9xXtveFJuDaATI6muzNcpWYYqlQwF7uJDeI5iRE5j9KU1gAfADATyM0zvZUJkhuSGiT5/f80kwZ7heCVA6/fqanVuxwS+G4N6/OjLBOBk8YOaCW6kCfP4VJb+VKiPpSNjIZkrdQLnaQ0Y8+M15cuqnhJbaScOvUkn9c80N2ZU8Iz7R9/ClmLElv3xNa0jM9B9/g2tlCQYLf5oNsENnqZyM/vRd4PBBHE0TRWmu6q2rCCXIiCZOTGBR6CiD3IlkPPGAfvpQ/xtwuNzMW5EdDU7iEorePKgyRBOPOhLbLNmQZwQKKoLR7daUlmDTGKDo7ly1qZn/TAieCJxj4A0a4sWh/cRyRQ/E2n3q7K1picjBxIHvIFS8lJ4w4nUzQ6cPoNUNzgF/EuIj4/rWm0erFxJCwyrEc1nfxS6+1YLECUWR1B8/XkfOn+z7raXUhboOxl8OflXzubHe/k7GOVoe1TwwLiS2BPHxp/sshWWP7ok1mP6k7RbTJpBaXfee4zgE8LEZ+J+R8qS7N/qt0v/61t1gyI5HpUf005QtFfVh7Wz6MbW6+Q2W5wKiLYIiKoezP6i1XaGpDWdDeu2+t2NoA+tXr3hZci4Np8+AKzZMMo6oRSQVJUY4qF0s0kxFduJSc+1BZmDlJlegNBY2wNoXF5FvoqnJmvnmv1z9odr6q6xi2h7tBjAGJ/WT8a139S6ltFoXuKc+Y6GRHzNYCzc2HdPiM8r8673/PwpXMw+RPqJb6VBHdeGDwF4n0/Wps+xyCsQMY+dJjUSwHi88mp94WeZPkYMSa3dkD268L4THPIoKk7SygZwf5qJuSxxuzk+Veqk24GOmTFFIIK5+Zo6jHmKmbRUL4j5QBP7V6nIU8LiJpqy0yxz6nApZIKKxrigqJAx4sgTU9sp+U5PnUrdu45LMSP/tx8693HIMyMdP0q6kTcSCW4E7pA4ORFWXZMfjdNbW5dQtcAlFyCeoPnmkihdQ3JgzJz/mmNJd7jVWLohjbuBgvpOad9AUSLsNoOAGRTHEkAT6xQ5RjMZKyTTeu0wtBVJ3FEAgxukdfrQF7ruufFx8etImPxAauO6kGAcCKSMvpzbkkNdAj02mY9cUbUk5WcA4oNq5sd28kk+oBH0mnyK8TJfzNB2M6rqShju0uhEAMjJA6+Wf0q51VpdVrtHp7Y2K264SDgIOKqOz2FpLb29p2qWcgZJ2g/X50x2hfZnVzCqdGLVs9CzgYn4/KuNONyOjjdIS7WA11hdcABZtAW0I6AtjJ9DJqv0Ddnd//ALiydUFOcxx0wMj+K2fZ/ZejPYZ0152vo5AeRkAGQD1mdwPwpG1ptRpibNhtOEU4Pd4MkxUpZaXFFoQ5O2O9lf1NpLI7gaXVraTm4LRgLgfsDNaHT6zTdo6JDZeUbwgx+n1qj0KajvEN51uKfzbVCkfeKDobdnsjti5uZ7encC9bXkHn54pIvknGgTiou0zQ6a5dt2j3qjvFB8PQ+1Q74XoZTuIjMdOlDu37neC7bWGL48iJBkehE1O7sHdXwvgZ4I4Cg5o+lUSXPZS/1NZ7zsXWMcHbuEycDxfSsKlslg29RI5ifpWq/rHWXLZTQ27g7q4JuJOQFiPgfpWe0lgT4Z3ERBH39mun4seOLZkySuYPYAw8QiOvHPFEgqATPhGZMc8Cpi2AASzZOfFAn7ivFRNufPy+56VTlR6heUkiTHGDg+VM2lUqNjc8ZzQ2sJMd4ofkhp/UxTCKyqZCKsDB6+sTRUgNAXVgxiV8xMmvFbIljMTk4Pt/1RRBgAeuZGOtTKuoAU8njMCvMVM7R2m7lm/KMEk4gUG4g3koJMysdB7U/pkjTXEDbVWOfv2pIEtcgKbhGZn6U0WVcSSDw+IApA/KZmKC4JVlJMf20ZyWYAkswXnPT0obrAPhJA5AGaNnqoY1mp7xQQNrn5+dKKy4gTiDPHzrzvWtvLMoMHDECRQtVfs/mN5MiIGeaKroDsXuuCTn2pZ7xsuCDDmVjzBGajdukk9yFA6SZzS2AQJmMk1aUtUjPwd2zQ9iam0791dvFTdPdli2AScH9x8BVsBZ1g1Vkws23tom6AYyPnNYu0zAltx9ZzMVa2LhK94S1ty25doyM81zcmOma4TNl2C86yCwFu4FuXZbDEqDI+tDt6pU16LKm3dtKyru/uxj50j2e1xdb+DdtnhdLN3ErtIKzHuw9jHlVhouy27lr2n2XLtm4W1FoYKnIYge5mPKs7xxTsup2XNvUG3tBXbvM7+R8PiaRYPq0sXHCtfsmVji4s5+dF01q9fNstc3oFjZMweZ9a62+zVXdJdt7+7hsEhwD1Xz9R/NIojMsNTtstpktZUv3fh4EY/evbNxb63LfhHKgxwPWhXimvsd3dchXYlbyCNh9fITzVF27rtT2OjoV4UDvVbMnBMcxMfrT1bpE60ZrtrVLqu1dTfSRbNzainJgHE/OmNHbcklV3CTPWPrS2o0F7QrptQu69pr1sOLiGY8wfWm9Bq4QoySg4YNxFb4pVSMm1LYW7ZZhuCjafMxnyoH4ZgYIYkGPCQc/ZqxTU2UH+oYHEqP260vccv+VRGFOJx5EfxSFBI7HlWBKAlmcc/GpI7BVhIAPU85jp95ot2PzsGDAQpP39aC9wKAwEELgnnijaFaDSCDAME9KmUUAsu2FyM54HrULzq4k4zkbT196PYlxBk4Ind9/ZphWH0a/wCyuyCGZwAsxPw/WkLD2pvNcDG2BGJ68evQ0W04s6W8pgFoABj78q87P0xu2dWHuDJtNMAkjcw8sjI+VKnRooWuXntCVRfCMqwA5HMVX3tddJZbdvaOfCZ+8zVidKqF1GDks4EEH4c/Cf4TuIRZO1FcyfFJyY5yaPI9RTsWQkspmYgnioB2ZifCDOKaW0xY97b2gHMRRF0iswKtHpR5i8LE14GJIxIoRHi45xTd2wyWiIPMhiOKUYMCT659KKmCUGERMGTRrbNacoJZXWJORP8ANBRtjZmJolvxGIMTINM1yRLo0Dat711LltmW6GDAgHAP+Z+zWpTX7b2h1KoF1N26lnUImN48/wBBPyrGaLWpbtGy9skOcEGINWinUXii2bjKoyAozJxJPkKyTVM1w2rRrezyNRft29OYS3cILD/irGI+HyNT11tE7U1OqZv9ullVdd22SJyD0IHt8OQh2Wt3QaV4ZptruOMtbjp7frXL2muq0roF322Ztyk5PQfCIqF0Vqyzt6oWrb3CrXULG2DI8frj0zVP2jbbX2dbfYb+9tbLSjjaOv61Xtq9VrFTTW0HeGUuqphT5k+4Aq90lg2bGxvE6pB9/wCKhklwd2MoWjEdh9qnQMbGqLvobjS6zm2f+S+VWvaehs/6d3T3UQXRNnVWwNtwEYV46+tV3aWmXTay5YggFgQfME/zNF7H19vTu2g1Qf8ABaiIDDKEjDA9Aa3N2lKJkSq4y6Ezeu2rzpcQrcU5UrGT19qdslrtvc9uB0EAZq91XYiay13WpALIYS6hCtHQ5+/as/qtDq9Dqpk3kThxO6PUffFMsil/oPTcXondLKxBkRzn79KGSrAqqMSPJTjGZg0W3dlmgNJzGOfrT1hVLC3AED2jyP358U930K0VtixdIIYbcj29vlTmntsguKQDK5AHOf8ANEXcvgPAHM9a47dxkiep6yKIlFWtxmAloJzt4J/mm9PeOnZnIMOhVhG3dOfPzA/SlbWE/MI5288UYafaw2TiG/LHQfzQZoQHVC9fMqcj/wB09fX6VBDtQBlhvLoaYC7Y348X9ryaKXsEFXGR0Jn5UkmUiivCKoYHO7rSmbbl7REdUBwatjprb5QsPbM0je0bFiQQYzBkUthaBjUIQBdG0E+cwaa09qzvJKBt5yDSD23UEXAy9J6GpW27oRuJXofKizyf2ParsJXT8RphuT/j/wAfhSK9k31lkJAB8qs+ze0WtXAZj0PBHrWiCW9Xa3WoDxkedTeSUB/TjIwwsXF8Y8+ByD7VedldpPZK27tsMWhWJjxDrXazQNbLXEU4glf1rrKL3e8gSpwfKi8imiaxuD0N6btW9uDXAAi3C6+YnlfY0TshC1y5btIw3NuXA8I6fIRXum7P/FttHhTqD1q/0lizoNP3VsY6zyxrLmyx+C8E0KaHS29K7KgJBMkk8mi2r0O4mDn2FTvQ1wAgQaF4FfIG71rI3eypQdvWy2ttXBMsIjjjIP71DT6BO01OjdgmoRS1gnh+pQz74qx7fZbdtLhhtp+lUh1Ztlb1md9pgydK6GFtwRkyJKRoOxdXcbSBL7sblrwlm5jpP30pphvuSp8c4aB99aDr7CfibOs04hNSv+oFPBPDfT9PWusE7oJMxkUQAbuistqWEd331stb28Kw5EeX3ikrlq9au7b9shgOXJg/cc1ZattlhgpyrBlB88T8opjSFtfZXvrPeKD4SDEexq0GSkiu8DLuVwT0xz8+aXcGDMH2wKttV2NcT/0zG4Odp5qtFp0v93cYoSDhgffy9KopWTaKFNU9tY2qyno0wPnVtp1F6wGICnbPhAFdXUzKIX1XiuZz9mlokSeQcV1dU2OgRuutyAeSBT9vO0+czXV1TZWJMqrp4lB3TOKrO1NLat2y9sbSGAgcH4V1dXl2NLorbLnf0kD61p+zLrlEbdDTyK6uoZAYi71QFxEdh4mwY64qrS0nekRjy+FdXVlfbKof0rFLnhMQKNcdtnPBkV1dUn2Fk7bs11Nxnj968u4viMY6fCurqmwoq/6g8WilsmRWeRiQRJwP4rq6t/jewzZ/ejVdj3Gu9k2Q/wDbAHoKKpi+RXV1N8gYK+P90g6Ng+uCaa0rlAwWAFbAiva6qokww1N1WkNkGke0Xa7fDMcgxPpXV1MhT//Z</t>
-  </si>
-  <si>
-    <t>data:image/webp;base64,UklGRtYUAABXRUJQVlA4IMoUAAAwgACdASo4ATgBPu1ysVIppySrp7Q52XAdiWVuZn4R785W8VdMRmoez3hjiHZLY/oPXg4N/jd0j3M/vOelDC5Vspzng/duip/+PCTI3nbIOsmDECYHn7YdKSpNBMVxegvhBdq1Y+1ycH3fuHy/bgk78VD1MH1nXTvOlJ7ZepXuOmp/sMP/QbJlUXZvO/Wn1c7xw8iQv+dhdUWJ9TqBrME3AZAofdqo+QOe4jeEcsEPWUWWNZ1RHrSPkpnxxUsqGV41KEVhHtcLHmzKpzTPMk+2D55tImx5nsNlBifa9djJU21d2FgW1RGGtuIV52T/33E9b/nLUM0wheVe/qw2Yf8Dsvesh9+KNdam0rT6ryXRuWPEv35TRPDzfvEoFpf0k6GRb+RNK2j0n/zZLlibg9jHQj+DmhH6xjL5jLzdH9y5d7z5DlUdqVO31iqMBUlxm6QL3L9W7wvWOij+LHKWbU6x28DGX7NvcuFke+pJzor3Kwx+iHDPabd6BilRS7kwNQzgXS8N6B6u84aymvhJW3Qg/9l25QBkDO6mG4eSpiQr4BQmhFBkWHRbe+cn6vywlAakdknYzyaxT7mcW+imgKSmdkk4gaHXDohQjuLckLGKB4x6E0yQCg2bUCT0m98AZ+5q+IzX7L4mZvzy8AvMuXbzRH1+woCWbHNJ7t429ID2RaWq5gnhBtF+qtB5oPK88xQDN/nAlNXbjiLD2AK9i+KdiCnQplLmZfW6DKxMPI40dtxuFnmDtYcR3SimKXMsD6O1caG4yqbIOsOyNqR7v2NA3CC4NXrdVrjpR8AB2351WqhCJU7MY/Dws7Gk1TJYfeVuoGPX58W5zU9wwyeL8OSa/MhbxOq8dGIlKyeZ4SDpaJ4STx3XMddT8THoWTd/jadaE1+n609XGJcWwKzbuJiZygsrVwqszaT6u+v7knzRQ9a7kIHdres7la+QyeoNZfUhWIWtF34sv68t//RRVdXHsIWgedb+RIdak7TAWKbsCH8bx2Wel1U1+l0jYvIpLFPZHlwzvbW8WtrgVJm69n4a8MBFcNhz7015cacyHFR571Vh1aeL9IQFfIZiwisNttUuCiP6POJTGPbdOVJ/tsyZqTlKBPjaJaEB/T0l6c8Zp2e2DcILFtUcE7p9nxxtVLLPZDCkpeTR2JbL10zV3+e7rLtJhrDpHK3GsMe+yL5qL+7DUGg88+PD7gLnFYlTE46u5zuLfz67U1lNw+Vh1+KGRmuWZRssY6pXXAWL/aYCQCowl0pgbkXfAy1n9LVUUBgKyc+lJvLoqCzQedT4M16J/+ThnN+pbzG10BF90kctycZzhH2GzH9P7esargKvBTB17GosFKeZ0Q/UOqqbsXDg787xJuDXNKcsgAD+5Qa7Ye2eL+vWnr6KnJJIJnr8xBp3HhGShLA4BjGlmktizGm5tCB0qqrP3KR3WtbGnhwwhREf1qKoi2XRm++Iz63Ee1U7Wo7yhy7OOSg1Kj9az1wTLczI85+PyCdT41N8WkszqjyKj24KnC0QBDmwdS0LJ9/bzgGCLAuYFB9/svt0+GuGxtAN15FSn3Gkzc090orsf11x8/9Gls3U5wfIYwZGxb5VISPm1Od2gmhK5dC0g48DTtdWz151gZ2+eWkJz22bJ31Mhsw/Vo3whaPLqxr+v6Fpe609fnzX4oh5XR+jpu1Jps9sEVTx1rf8bY+rbU2MJghLpIFPNa7MzhRsGlcml9xzK90fEdqXAXExF6tZtyM5vy/KX1MUeQgqMR7YXOVUhm0TThC3Gw7uwSa4RL/f4Yda5eImI1xr7Q9q2KVMBYKdgt0PPB17asL6QF7XdQACt3R+yb2TIxdP8a5iSVrG3TiZ8MAgcIUV/nZdBsnezKgUKq5tSN5/gGlI6Yh9qI33Q5RJ21T3Ilh27WwZQlGay/U1aLn9VlHwF5tu3uta9D5CmNS3JA1xp8jsrSkaBbKxFCufw5bgBfJkze3hnAa45VGe7FvJgSdJFVFF6dBdpbC/K2CF1JEf0G9DkT5y1UyFH+aai/v8qUcIZkvOw8/ysVMqG9smZkUzxkvmGHQ1sjvMtQrRNSG6tujIEZ9QNC/FWC3JOlLOEFqnsPFAOb1PYGdcCl+OTLyp8ydI7ELQzg0sh8+z/8RdgbiGmsEKfdLP/B4QSWPz3T7OReWOhJWzrZAQ2RxHX+AIYibKwnG7GVTWjNiPCyl8O4//uv+Q5hXMBs86AAc9uuQWt5RZqBII6juvu752RJBEGXOfPOET5iQ33L63ibG+YpvvFQD4dS9vHoHzig9LPAgCy3thOSmmeMLJm0CSIiHU8XUw8GRwqSDQlIrzyx7iYXagYSweSXqm0ckYcNf243d3aEdKhtTbBsxiBuh6je/4ptI/qs5/KsppLNRKhpnqWcjC7U/y85MA0db6PxHbkcBHZ+LVwOh+qVGyZY82ghY3uFAR85emDXfIyHR5e+1bLTPeNjNUr93M7pQQOhUOVGFtLVZaidPTDgILCk77njpYR6gA/bhy/NhLFghxCdTkVhbR10L+/Y0SvT0edTRASqL/RFRvWE52svOkatax5VoaU4N3cY6o6Mg/k6BoBjutZhuRCZS0al/tELW+NbhyPjg5OofCxph/QUYM9FTc7ZLPXuzWzxgFNGK0PYYPtWm/wQKaeW/it48fsr3I1JzQP5nDc2T9A0yqZkzppHpDV15qMj81Uzjj83rS73On5oQIsdT937EXbeMe9xn60SM1tZ12etCJaSp5z1auYOgc9klpODt4AaAyVi4xEbQvRCpyC1jYPa94kVu1idxhN5acPAlR+CAd7u4T5DOlmu3mBGod9WjO1Qwl0Yu7863c4g8NctF/L9sUUyljSo8ZD+sAiPhg1po9UokgtPZh7Bq6DL0LqKX469iIIUFf62bwspybWqzFBSVf2MGUxaQG7C4+yxTHTYqu5ogewuOx9iesSY451269C98nO9gC+7EE7uB+zPZVMP+I45SfGjwN9QEM21qqBACX+Rtgo3Io7MAZ04ERgvyYR+bTTF7oP4XFMMqBbJled71+X+BckoYkY3mT5nnjltC452SlOfrMoiyZfoPmL+d6PENrMtCdVVe8+17WtfM33rT6Vf2K5NKhr40xaLRwWNKVSRnk3KTCyu3G8dyll8+9hYFOfE6EzykH6tSbdjZkWwS2120OGTMWtcBsWOaomCu0dQHcXa0GCtcptSU2cEWEsGdubvaPZswM7aC8W1gcrgnmkHUTE7lRu5DlMpER+HWl+eS/kqKzr6m1iXM5Sppo8Xx18DgnehG7r9fsxMHmp4dGZdPYKpy3kV5tXcjyL6IvjNvsJhne1w6hoYDkk5GeI2ZlgwwyX/DdV4YNiXhXQrLS9nQ5wVqqjveRlEvIJ9erc9l7XGWA2juHVt6+yRCcupdbO5+ZtVLXAuJwE57g9Ji5RgyefsvUMDOePNAWn1V6uG8Ip7E2+Gin5/tB+vDRG+0DXb9cZ2kpQI2r71GSkoGAWP817l2Q76Nhepe+m24nP7EGx4OlO4eCfqMedBDAb5u8/u1XKK7I4YhrOPN36foRFwkqzC5L72gqh/bmn3e5hzyKlXSeYkGb3oYgfz8IpHJgk66dSoJDXeVV1jEJyymt0QqSFFbtV4uPS7q6EQ7IsxqxIrx61C4TraFkgNV5QX0NDaxgZwEANhBfB+dtC5dkqYPUApVVbpgWX6uMTyYracouUkUJhXTHxEhFcNFSbtgaPs9bxllTcZL2NhndeYcmo29iO84okDeceIEQh/tt6wgN8FevHezIgf8QgeEn2r9Uol7FqVDKi0Y5nTCnSyrNNpjSIBC7ULd+rSLFBOe+6u51seIA6S48EtSIjl9YELJ1fjm/c+m2qCC64MhL2FXJJeJWzWqDy/6TLicimq1GZTf8pTq9vwm91EuymQEre40oO8Unt4uEoib1WS+0u96LRR9p1+Jf6izWLV27PpmZOk7XQaItTPXhQtEIq2gRwvJqzqdI6eM4QKAI+w7sRFv9bH0h/UlEolBpyE4OZ4L3+kzeV4UVFhpT3UrZ56tsti0LsR8D2Z6wLkfMo0yZ3RmlRDJb6AlatqYoEca55KaHRNKEkuYcyixgNE2zkpRK3elLqR0eXYeELlQD9O5Od3fjiH97+DUrHva4FI7jX6VyUy/0d6I8mwY24dHPv+nJsKS5dJwrjZdewt4E09gDlNDbBnFUPhYbInf4jE4+4ElzGs3PAC8KuqrkuloRJtF2lceHE8wWFFquEsw9hMaRqbEr4QIBBNEfQvfXoH7brzShth8CcyU1XoJT4GbdeyQ1izSgZD8co2qfC+D39yNaTamfzAaeDqjpIb0JOKlSuqc2/f/PgaY+pWoCHqeiJG90NqCqQ5YrR2hpZiCNY2VrYZCGFZ/Zun0o2fJddtA/bsMLx+xCRLcdeM/QshhWc/lIrwIqoxure+898XBJMg4SI3QLGup0n2C1Im2fmuRrCb4hqGQE422oETpQ5/HlCMNi8Q4jXMWnTNNmkRwxgV0/TiI7tCLrIOor9C4YtYfXu4PhiXUgAEzx+lAvh18O3E28+y9tKpsCYDTdehgMGn7CcbxKufZ9H260kiM9ZY64QlO+8E1GTsxV0lxlYikoHkD7pcyscDeQs8X5CZyc2AG+x3IUEHe1aap3Gm0ZdLRMHrifGLWiw0VdmXsx5D+PanFdBFCU825wBMmv1bFYWGwDTsLBNgv4FDBvwyGFbiur3+Wt4dWjnjndZB7/zwpWbqBdwPb1KL6x+ZqqQ0azQNJctllRIkGrjzpZrzBSNxA9Ha7BS/TI0Lv8+x9t9KoaFx+NxV/2jD414w/PbGj7r0ctE5rIZ86M6hEVIMh+jFp78jt0C+3NiFk3TVa6XQ14gvGBZt0c4v/cKqvUiSVl5tgAqcYZRsrxudOWGBY1zaqp7v1kdeRFthreu9YtsMVZ1ys2kRNFAbWI0gCM4ZBopyh6IuFe9PJ+NSJyJMtc3ZIgksoR88EpO4USvdUF57Rd+0Pe66WpQdGPpdfjVhgtEiMncP9zaGmroH5i6ynLA9TX6SbQ6IuQP1KM3+mGVHoM4A914y+oJt3rw4bwCx6IidGQ8KBDDfARRb/p0IOcHCKh5s98zy6D4qzm2sMD22GMH8a6vqD87Vqc9p5R7kAE64slVsqcahnUPqhQlbgiUl11icTMwxSUJ18kR0/+pPVhm3uQPwvMox6Cp96KRuFymJ00YU+l7cIgQz0fEQekxZoxvyqSJhlv52Nrx+oKZf/dhwAzKQ7pQAIHgqTqxlFLZpj5g8WIcistJMmelPJc/6jopo+2a9xuU/faHrXbhOqMbM0NbMyfDxgaC2lHYnrFgYU81H7JYtePtCPVdQ0d8xo19QHJvxja6qeWdqCG15efzBuotMciFFjnOBW6d36lWAqRt+w6objLjreJqhbPszNgBXcvr4zAFrnfrLLyIrdkQFslYYNi2uaRhedLRxhkQcWTS9bVXcVmgNeLLIKQz1RB5Jmf9G+J7deMTGPbEz+ji5psuJGjUDG0XdKIW5TwWvSZBALG2XdViNeSsCGQCOguLJcaPShsOZSl0fpgxIwvfDpbN3oezuXAaxbzY/8ybZy9o0EwflahjehIOK3iV5eg/fGUgC+USrMnBp44k5MTLKDeeIUZJ8zG9vCX/u6mZ7PbpAFP+iwGVtAaZLY8fQ2NpxCEHjbDs7jzbQTov5ojYx1Lawks/QZKzKiXC1uJyinwsNKLnIXPZBopzug0do/hcV17HMX1J7YDQxfDN4U1nMWhjB9jC5SrTQYpbXsbT0jBZNOqZDszyU4LET0D4v9xb90V6gZIV+ot973sJ4UP2d/d6StL1hKfWvcHZwfAAgasD2zy96rz+1dHTThCU06nImqhw9M3xf/b8X+/ve9iaruI4XRQg2nw81bH5s80ZIs8Dg0+I5q7RdZBhfBlggTwc3l35bO5bAyVvuG1mQWIkDZ0NI3FfHNaBekYnjCjXogAiUDNt5CeFozv6GcbuA4H8MW1eIQw2gtZKGtk0m5ahXu3VZZjWho4jFHnHMHnuXMAkF6PW3lZhc8MV4hfC+2lTfI0QU4Qd16hGuyBNQGubTd2g0eJ2WbRZpT0mKRqXuZVUyNhS9DwOvkbiDmqJZbBGEsjLbSMUHjbG/v8RTxbuzuiAQcCl2ScSc6ynOj6TeBrhrxqERZ6spxCpHGv1Nz23su83nviN7Pma9R3TxpF9DopHMU/2iLmFNKHVNwQUuBiDmVSJDK2wYjR1gwBfWdf//SJky07ls7JzAPG/yvD0N8iL0+mYaH0uE1Q1sv6dFLCN8pZCHbNGRqV1DH57Gy2ddcw6NnMWwb2Yp4hpvei1NQVandP6cmLwqH+Z+RjYlsDk4PXUM75xEK06g5qYl/virdfVMpw0a/nGbHGAM31W831YowDgan8mqQ75yJTpVPBuMXxBTR1Vvh2Ran8aWUIQnwhdwqjuGiiET2FsZkCiya/X/wrV8/EuIh3CVe54kPVByXooeJRNdKqTrLlrqe0lve98mP1HFpORVunCEI4V/XvoR1i4sReAyrQjkt/I0OE4nIwHb8IMgu8d8hSdJKQylhaI/RH6JINb821OnRfwROsHnNMD2ykrlg48SVArbuIMLhgTLBZP5V6v4KEbot98iq/Yau9soQkOLaq1CEIPaIrPtceGiphbvu2dGh0PgnxjordDn9eG7Uxy+seEWKq00ySQd1WbMAcNbE5rlmLw1bf88FamKrc3xtkiYbrbb5V68gBOH9Apga4vms04kuQtob3k0nJnadmk+/Fr+Qpntynp7mBHqctAHiBmjOo371gC9b6L0lvrhg7+qU8abKrJrBv/PGjJsNK/LH1cKJEMIKuAMiROovpQfM6jVJ2NnSW1+A3pDST3hMyc2gtaTbUvtQoMJXGmLdUt7gIxaarIGM72mYETgH8vuXH38L1Ha3b80lTNG1fFfxIU7cUnY/XIS8UMdgVer1zqZOFlyKdmdpoUFeCQLMO1SRChxLONaEDVrYUnLnt9XDEDSX5/X9g0950rWj/nh3o+v87c3cSCKayYUpjOqDjL33BwRNFrB/UD65YwHre9vrcN7IbYncAAAA=</t>
+    <t>https://big-i.ru/upload/iblock/ab8/6dvndikgf1wemean11mg8echpemsfjkp.jpg</t>
+  </si>
+  <si>
+    <t>https://ru.wikipedia.org/wiki/%D0%9F%D0%BB%D0%B0%D1%82%D0%BE%D0%BD#/media/%D0%A4%D0%B0%D0%B9%D0%BB:Plato_Silanion_Musei_Capitolini_MC1377.jpg</t>
   </si>
 </sst>
 </file>
@@ -3223,7 +3223,10 @@
         <v>389</v>
       </c>
       <c r="B163" s="18" t="s">
-        <v>391</v>
+        <v>392</v>
+      </c>
+      <c r="C163" t="s">
+        <v>393</v>
       </c>
     </row>
     <row r="164" spans="1:3" ht="75" x14ac:dyDescent="0.25">
@@ -3231,17 +3234,14 @@
         <v>390</v>
       </c>
       <c r="B164" s="22" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C164" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B165" s="19"/>
-      <c r="C165" t="s">
-        <v>394</v>
-      </c>
     </row>
     <row r="166" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B166" s="20"/>
